--- a/mlb_weather_professional_v4_1_2026_07_17.xlsx
+++ b/mlb_weather_professional_v4_1_2026_07_17.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1862" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1862" uniqueCount="370">
   <si>
     <t>Date</t>
   </si>
@@ -464,7 +464,7 @@
     <t>Overcast</t>
   </si>
   <si>
-    <t>🟡 6.2 mph Cross (LF → RF)</t>
+    <t>🟡 6.1 mph Cross (LF → RF)</t>
   </si>
   <si>
     <t>⚪ Light Variable</t>
@@ -503,18 +503,18 @@
     <t>ESE</t>
   </si>
   <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>SW</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
     <t>SSW</t>
   </si>
   <si>
-    <t>SW</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
     <t>FORECAST MODEL</t>
   </si>
   <si>
@@ -542,7 +542,7 @@
     <t>Density 66 | Wind 53 | Temp 52 | Altitude 59 | Confidence 93%</t>
   </si>
   <si>
-    <t>Density 71 | Wind 50 | Temp 63 | Altitude 63 | Confidence 81%</t>
+    <t>Density 72 | Wind 50 | Temp 64 | Altitude 64 | Confidence 82%</t>
   </si>
   <si>
     <t>Density 72 | Wind 71 | Temp 62 | Altitude 63 | Confidence 83%</t>
@@ -584,9 +584,6 @@
     <t>IMPROVING</t>
   </si>
   <si>
-    <t>WORSENING</t>
-  </si>
-  <si>
     <t>IMPROVING RAPIDLY</t>
   </si>
   <si>
@@ -599,40 +596,46 @@
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>2026-07-16 09:38:47 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 09:38:48 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 09:38:49 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 09:38:50 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 09:38:55 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 09:38:56 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 09:38:57 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 09:38:58 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 09:38:59 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 09:39:00 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 09:39:01 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 09:39:02 PM PDT</t>
+    <t>2026-07-16 09:51:43 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 09:51:45 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 09:51:47 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 09:51:48 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 09:51:52 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 09:51:54 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 09:51:55 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 09:51:56 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 09:51:57 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 09:51:59 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 09:52:00 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 09:52:01 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 09:52:02 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 09:52:04 PM PDT</t>
   </si>
   <si>
     <t>Period</t>
@@ -977,40 +980,46 @@
     <t>10:10 PM PDT</t>
   </si>
   <si>
-    <t>2026-07-17 04:38:47 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 04:38:48 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 04:38:49 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 04:38:50 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 04:38:55 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 04:38:56 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 04:38:57 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 04:38:58 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 04:38:59 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 04:39:00 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 04:39:01 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 04:39:02 UTC</t>
+    <t>2026-07-17 04:51:43 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 04:51:45 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 04:51:47 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 04:51:48 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 04:51:52 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 04:51:54 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 04:51:55 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 04:51:56 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 04:51:57 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 04:51:59 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 04:52:00 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 04:52:01 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 04:52:02 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 04:52:04 UTC</t>
   </si>
   <si>
     <t>2026-07-16T19:01:48+00:00</t>
@@ -1022,10 +1031,10 @@
     <t>2026-07-16T20:16:40+00:00</t>
   </si>
   <si>
-    <t>2026-07-16T22:52:38+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-17T01:37:15+00:00</t>
+    <t>2026-07-17T04:37:01+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-17T04:32:01+00:00</t>
   </si>
   <si>
     <t>2026-07-17T03:21:22+00:00</t>
@@ -1812,13 +1821,13 @@
         <v>83</v>
       </c>
       <c r="L2">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="M2" t="s">
         <v>147</v>
       </c>
       <c r="N2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="O2" t="s">
         <v>156</v>
@@ -1830,10 +1839,10 @@
         <v>3.5</v>
       </c>
       <c r="R2">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="S2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="U2" t="s">
         <v>164</v>
@@ -1860,7 +1869,7 @@
         <v>2.9</v>
       </c>
       <c r="AC2">
-        <v>89.90000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="AD2" t="s">
         <v>182</v>
@@ -1878,28 +1887,28 @@
         <v>0</v>
       </c>
       <c r="AI2">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="AJ2">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK2">
         <v>1.1632</v>
       </c>
       <c r="AL2">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="AM2">
-        <v>1012.8</v>
+        <v>1012.9</v>
       </c>
       <c r="AN2">
-        <v>45.9</v>
+        <v>46.5</v>
       </c>
       <c r="AO2">
         <v>84.2</v>
       </c>
       <c r="AP2">
-        <v>28.4</v>
+        <v>28.7</v>
       </c>
       <c r="AQ2" t="s">
         <v>184</v>
@@ -1914,22 +1923,22 @@
         <v>0</v>
       </c>
       <c r="AU2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AV2">
         <v>0</v>
       </c>
       <c r="AW2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="AY2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AZ2">
-        <v>577</v>
+        <v>589.9</v>
       </c>
       <c r="BA2">
         <v>5</v>
@@ -2063,7 +2072,7 @@
         <v>185</v>
       </c>
       <c r="AR3">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
       <c r="AS3">
         <v>0</v>
@@ -2072,13 +2081,13 @@
         <v>0</v>
       </c>
       <c r="AU3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AV3">
         <v>0.2</v>
       </c>
       <c r="AW3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX3">
         <v>7.7</v>
@@ -2087,7 +2096,7 @@
         <v>192</v>
       </c>
       <c r="AZ3">
-        <v>357.4</v>
+        <v>370.4</v>
       </c>
       <c r="BA3">
         <v>5</v>
@@ -2218,10 +2227,10 @@
         <v>37.5</v>
       </c>
       <c r="AQ4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AR4">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="AS4">
         <v>0</v>
@@ -2230,22 +2239,22 @@
         <v>0</v>
       </c>
       <c r="AU4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AV4">
         <v>0</v>
       </c>
       <c r="AW4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX4">
         <v>10.7</v>
       </c>
       <c r="AY4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AZ4">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="BA4">
         <v>5</v>
@@ -2376,10 +2385,10 @@
         <v>50.8</v>
       </c>
       <c r="AQ5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AR5">
-        <v>-3.2</v>
+        <v>-1.4</v>
       </c>
       <c r="AS5">
         <v>0</v>
@@ -2388,22 +2397,22 @@
         <v>0</v>
       </c>
       <c r="AU5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AV5">
         <v>13.7</v>
       </c>
       <c r="AW5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX5">
         <v>11.9</v>
       </c>
       <c r="AY5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AZ5">
-        <v>502.2</v>
+        <v>515.1</v>
       </c>
       <c r="BA5">
         <v>5</v>
@@ -2534,10 +2543,10 @@
         <v>75.90000000000001</v>
       </c>
       <c r="AQ6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AR6">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="AS6">
         <v>0</v>
@@ -2546,22 +2555,22 @@
         <v>0</v>
       </c>
       <c r="AU6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AV6">
         <v>38.7</v>
       </c>
       <c r="AW6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX6">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="AY6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AZ6">
-        <v>346.2</v>
+        <v>14.8</v>
       </c>
       <c r="BA6">
         <v>5</v>
@@ -2695,7 +2704,7 @@
         <v>186</v>
       </c>
       <c r="AR7">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AS7">
         <v>0</v>
@@ -2704,19 +2713,19 @@
         <v>0</v>
       </c>
       <c r="AU7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AV7">
         <v>3.7</v>
       </c>
       <c r="AW7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX7">
         <v>1.8</v>
       </c>
       <c r="AY7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AZ7">
         <v>0</v>
@@ -2757,16 +2766,16 @@
         <v>143</v>
       </c>
       <c r="K8">
-        <v>87</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="L8">
-        <v>59.3</v>
+        <v>58.5</v>
       </c>
       <c r="M8" t="s">
         <v>150</v>
       </c>
       <c r="N8">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="O8" t="s">
         <v>160</v>
@@ -2787,7 +2796,7 @@
         <v>164</v>
       </c>
       <c r="V8">
-        <v>21.5</v>
+        <v>19.3</v>
       </c>
       <c r="W8">
         <v>50</v>
@@ -2808,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="AC8">
-        <v>80.8</v>
+        <v>82</v>
       </c>
       <c r="AD8" t="s">
         <v>182</v>
@@ -2832,10 +2841,10 @@
         <v>0.8</v>
       </c>
       <c r="AK8">
-        <v>1.1536</v>
+        <v>1.153</v>
       </c>
       <c r="AL8">
-        <v>1831</v>
+        <v>1850</v>
       </c>
       <c r="AM8">
         <v>987.5</v>
@@ -2844,40 +2853,40 @@
         <v>70.5</v>
       </c>
       <c r="AO8">
-        <v>84.7</v>
+        <v>85.2</v>
       </c>
       <c r="AP8">
-        <v>62.9</v>
+        <v>62</v>
       </c>
       <c r="AQ8" t="s">
+        <v>187</v>
+      </c>
+      <c r="AR8">
+        <v>6.1</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>189</v>
+      </c>
+      <c r="AV8">
+        <v>27.7</v>
+      </c>
+      <c r="AW8" t="s">
         <v>188</v>
       </c>
-      <c r="AR8">
-        <v>6</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="s">
-        <v>190</v>
-      </c>
-      <c r="AV8">
-        <v>28.5</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>189</v>
-      </c>
       <c r="AX8">
-        <v>15.1</v>
+        <v>13.1</v>
       </c>
       <c r="AY8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AZ8">
-        <v>181.7</v>
+        <v>19.9</v>
       </c>
       <c r="BA8">
         <v>5</v>
@@ -3008,10 +3017,10 @@
         <v>66.59999999999999</v>
       </c>
       <c r="AQ9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AR9">
-        <v>10.1</v>
+        <v>8.6</v>
       </c>
       <c r="AS9">
         <v>0</v>
@@ -3020,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="AU9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AV9">
         <v>29.6</v>
       </c>
       <c r="AW9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AX9">
         <v>21.8</v>
@@ -3035,7 +3044,7 @@
         <v>197</v>
       </c>
       <c r="AZ9">
-        <v>77.59999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="BA9">
         <v>5</v>
@@ -3085,7 +3094,7 @@
         <v>7</v>
       </c>
       <c r="O10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -3166,7 +3175,7 @@
         <v>68.8</v>
       </c>
       <c r="AQ10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AR10">
         <v>10.6</v>
@@ -3178,13 +3187,13 @@
         <v>0</v>
       </c>
       <c r="AU10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AV10">
         <v>12.9</v>
       </c>
       <c r="AW10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX10">
         <v>15.8</v>
@@ -3193,7 +3202,7 @@
         <v>198</v>
       </c>
       <c r="AZ10">
-        <v>52.5</v>
+        <v>65.5</v>
       </c>
       <c r="BA10">
         <v>5</v>
@@ -3324,10 +3333,10 @@
         <v>61.1</v>
       </c>
       <c r="AQ11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AR11">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS11">
         <v>0</v>
@@ -3336,13 +3345,13 @@
         <v>0</v>
       </c>
       <c r="AU11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AV11">
         <v>22.5</v>
       </c>
       <c r="AW11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX11">
         <v>13.5</v>
@@ -3351,7 +3360,7 @@
         <v>199</v>
       </c>
       <c r="AZ11">
-        <v>26.8</v>
+        <v>39.8</v>
       </c>
       <c r="BA11">
         <v>5</v>
@@ -3401,7 +3410,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="O12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P12">
         <v>4</v>
@@ -3482,25 +3491,25 @@
         <v>20.5</v>
       </c>
       <c r="AQ12" t="s">
+        <v>187</v>
+      </c>
+      <c r="AR12">
+        <v>7.8</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="s">
         <v>188</v>
-      </c>
-      <c r="AR12">
-        <v>7</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="s">
-        <v>189</v>
       </c>
       <c r="AV12">
         <v>1.8</v>
       </c>
       <c r="AW12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX12">
         <v>8.6</v>
@@ -3509,7 +3518,7 @@
         <v>200</v>
       </c>
       <c r="AZ12">
-        <v>592.6</v>
+        <v>605.6</v>
       </c>
       <c r="BA12">
         <v>5</v>
@@ -3559,7 +3568,7 @@
         <v>8</v>
       </c>
       <c r="O13" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="P13">
         <v>6.8</v>
@@ -3640,34 +3649,34 @@
         <v>72.09999999999999</v>
       </c>
       <c r="AQ13" t="s">
+        <v>187</v>
+      </c>
+      <c r="AR13">
+        <v>4.2</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="s">
         <v>188</v>
-      </c>
-      <c r="AR13">
-        <v>5.9</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="s">
-        <v>189</v>
       </c>
       <c r="AV13">
         <v>1.3</v>
       </c>
       <c r="AW13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX13">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="AY13" t="s">
         <v>201</v>
       </c>
       <c r="AZ13">
-        <v>52.7</v>
+        <v>65.7</v>
       </c>
       <c r="BA13">
         <v>5</v>
@@ -3717,7 +3726,7 @@
         <v>10.8</v>
       </c>
       <c r="O14" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="P14">
         <v>10.2</v>
@@ -3798,25 +3807,25 @@
         <v>39.2</v>
       </c>
       <c r="AQ14" t="s">
+        <v>187</v>
+      </c>
+      <c r="AR14">
+        <v>11.3</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="s">
         <v>188</v>
       </c>
-      <c r="AR14">
-        <v>14.2</v>
-      </c>
-      <c r="AS14">
-        <v>0</v>
-      </c>
-      <c r="AT14">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="s">
-        <v>189</v>
-      </c>
       <c r="AV14">
         <v>0</v>
       </c>
       <c r="AW14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX14">
         <v>7.1</v>
@@ -3825,7 +3834,7 @@
         <v>202</v>
       </c>
       <c r="AZ14">
-        <v>458.1</v>
+        <v>471.1</v>
       </c>
       <c r="BA14">
         <v>5</v>
@@ -3875,7 +3884,7 @@
         <v>3</v>
       </c>
       <c r="O15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P15">
         <v>1.5</v>
@@ -3956,10 +3965,10 @@
         <v>69.5</v>
       </c>
       <c r="AQ15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AR15">
-        <v>-3.2</v>
+        <v>-0.6</v>
       </c>
       <c r="AS15">
         <v>0</v>
@@ -3968,22 +3977,22 @@
         <v>0</v>
       </c>
       <c r="AU15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AV15">
         <v>16.3</v>
       </c>
       <c r="AW15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AX15">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AY15" t="s">
         <v>203</v>
       </c>
       <c r="AZ15">
-        <v>345.6</v>
+        <v>358.6</v>
       </c>
       <c r="BA15">
         <v>5</v>
@@ -4117,7 +4126,7 @@
         <v>185</v>
       </c>
       <c r="AR16">
-        <v>1</v>
+        <v>-0.2</v>
       </c>
       <c r="AS16">
         <v>0</v>
@@ -4126,22 +4135,22 @@
         <v>0</v>
       </c>
       <c r="AU16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AV16">
         <v>0.2</v>
       </c>
       <c r="AW16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AX16">
         <v>18.1</v>
       </c>
       <c r="AY16" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AZ16">
-        <v>463.8</v>
+        <v>476.8</v>
       </c>
       <c r="BA16">
         <v>5</v>
@@ -4266,223 +4275,223 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>52</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="BZ1" s="1" t="s">
         <v>49</v>
@@ -4491,16 +4500,16 @@
         <v>48</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:83">
@@ -4517,40 +4526,40 @@
         <v>119</v>
       </c>
       <c r="E2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F2" t="s">
         <v>107</v>
       </c>
       <c r="G2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="J2">
-        <v>577</v>
+        <v>589.9</v>
       </c>
       <c r="K2">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="L2">
         <v>5</v>
       </c>
       <c r="M2">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="N2">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="Q2">
         <v>1.3</v>
@@ -4562,22 +4571,22 @@
         <v>0</v>
       </c>
       <c r="T2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="V2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="W2">
         <v>0.5833</v>
       </c>
       <c r="X2">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="Y2">
-        <v>88.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="Z2">
         <v>62.6</v>
@@ -4601,19 +4610,19 @@
         <v>83</v>
       </c>
       <c r="AG2">
-        <v>80.40000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="AH2">
-        <v>46.3</v>
+        <v>46.6</v>
       </c>
       <c r="AI2">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="AJ2">
-        <v>1012.9</v>
+        <v>1013.1</v>
       </c>
       <c r="AK2">
-        <v>1015.1</v>
+        <v>1015.4</v>
       </c>
       <c r="AL2">
         <v>42.9</v>
@@ -4625,13 +4634,13 @@
         <v>0</v>
       </c>
       <c r="AO2">
-        <v>153.7</v>
+        <v>153</v>
       </c>
       <c r="AP2">
         <v>2</v>
       </c>
       <c r="AQ2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="AR2">
         <v>16.4</v>
@@ -4640,13 +4649,13 @@
         <v>156</v>
       </c>
       <c r="AT2">
-        <v>280.7</v>
+        <v>280.3</v>
       </c>
       <c r="AU2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AV2">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="AW2">
         <v>7.1</v>
@@ -4658,10 +4667,10 @@
         <v>-0.1</v>
       </c>
       <c r="AZ2">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BA2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="BB2">
         <v>3.1</v>
@@ -4682,13 +4691,13 @@
         <v>0.14</v>
       </c>
       <c r="BH2">
-        <v>1.1658</v>
+        <v>1.166</v>
       </c>
       <c r="BI2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ2">
-        <v>1595</v>
+        <v>1589</v>
       </c>
       <c r="BK2" t="s">
         <v>133</v>
@@ -4718,10 +4727,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="BT2">
-        <v>61.3</v>
+        <v>61.4</v>
       </c>
       <c r="BU2">
-        <v>58.6</v>
+        <v>58.5</v>
       </c>
       <c r="BV2">
         <v>52.7</v>
@@ -4733,25 +4742,25 @@
         <v>0</v>
       </c>
       <c r="BY2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="CA2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB2">
         <v>82</v>
       </c>
       <c r="CC2">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="CD2">
         <v>7</v>
       </c>
       <c r="CE2">
-        <v>10.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:83">
@@ -4768,31 +4777,31 @@
         <v>119</v>
       </c>
       <c r="E3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="J3">
-        <v>577</v>
+        <v>589.9</v>
       </c>
       <c r="K3">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="L3">
         <v>5</v>
       </c>
       <c r="M3">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="N3">
         <v>2.68</v>
@@ -4801,10 +4810,10 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="Q3">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="R3">
         <v>100</v>
@@ -4813,25 +4822,25 @@
         <v>0</v>
       </c>
       <c r="T3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U3" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="V3" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="W3">
         <v>0.5833</v>
       </c>
       <c r="X3">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="Y3">
-        <v>90.7</v>
+        <v>90.8</v>
       </c>
       <c r="Z3">
-        <v>66.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AA3">
         <v>0.88</v>
@@ -4852,19 +4861,19 @@
         <v>84.5</v>
       </c>
       <c r="AG3">
-        <v>81.3</v>
+        <v>81.5</v>
       </c>
       <c r="AH3">
-        <v>46.1</v>
+        <v>46.6</v>
       </c>
       <c r="AI3">
-        <v>28.2</v>
+        <v>28.5</v>
       </c>
       <c r="AJ3">
-        <v>1012.7</v>
+        <v>1012.9</v>
       </c>
       <c r="AK3">
-        <v>1014.9</v>
+        <v>1015.1</v>
       </c>
       <c r="AL3">
         <v>25.3</v>
@@ -4876,7 +4885,7 @@
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="AP3">
         <v>3</v>
@@ -4891,13 +4900,13 @@
         <v>156</v>
       </c>
       <c r="AT3">
-        <v>262</v>
+        <v>261.2</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="AV3">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AW3">
         <v>7.9</v>
@@ -4912,7 +4921,7 @@
         <v>6</v>
       </c>
       <c r="BA3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BB3">
         <v>4.6</v>
@@ -4933,13 +4942,13 @@
         <v>0.14</v>
       </c>
       <c r="BH3">
-        <v>1.1623</v>
+        <v>1.1624</v>
       </c>
       <c r="BI3" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ3">
-        <v>1703</v>
+        <v>1697</v>
       </c>
       <c r="BK3" t="s">
         <v>133</v>
@@ -4948,13 +4957,13 @@
         <v>135</v>
       </c>
       <c r="BM3">
-        <v>68</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="BN3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO3">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="BP3">
         <v>0.3</v>
@@ -4966,31 +4975,31 @@
         <v>1.043</v>
       </c>
       <c r="BS3">
-        <v>69.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="BT3">
-        <v>65.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="BU3">
         <v>59.1</v>
       </c>
       <c r="BV3">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
       <c r="BW3">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
       <c r="BX3">
         <v>0</v>
       </c>
       <c r="BY3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ3">
         <v>4.6</v>
       </c>
       <c r="CA3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB3">
         <v>84</v>
@@ -5019,43 +5028,43 @@
         <v>119</v>
       </c>
       <c r="E4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I4" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="J4">
-        <v>577</v>
+        <v>589.9</v>
       </c>
       <c r="K4">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="L4">
         <v>5</v>
       </c>
       <c r="M4">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="N4">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -5064,25 +5073,25 @@
         <v>0</v>
       </c>
       <c r="T4" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U4" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="V4" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="W4">
         <v>0.5833</v>
       </c>
       <c r="X4">
-        <v>14.1</v>
+        <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>91.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="Z4">
-        <v>66.2</v>
+        <v>66.3</v>
       </c>
       <c r="AA4">
         <v>0.88</v>
@@ -5100,19 +5109,19 @@
         <v>141</v>
       </c>
       <c r="AF4">
-        <v>85.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="AG4">
-        <v>81</v>
+        <v>81.5</v>
       </c>
       <c r="AH4">
-        <v>45.5</v>
+        <v>46.3</v>
       </c>
       <c r="AI4">
-        <v>27</v>
+        <v>27.5</v>
       </c>
       <c r="AJ4">
-        <v>1012.7</v>
+        <v>1012.6</v>
       </c>
       <c r="AK4">
         <v>1014.9</v>
@@ -5127,31 +5136,31 @@
         <v>0</v>
       </c>
       <c r="AO4">
-        <v>165.2</v>
+        <v>158.7</v>
       </c>
       <c r="AP4">
         <v>4</v>
       </c>
       <c r="AQ4">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="AR4">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="AS4" t="s">
         <v>156</v>
       </c>
       <c r="AT4">
-        <v>262.8</v>
+        <v>261.9</v>
       </c>
       <c r="AU4">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AV4">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AW4">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="AX4">
         <v>5</v>
@@ -5163,7 +5172,7 @@
         <v>5.9</v>
       </c>
       <c r="BA4">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BB4">
         <v>4.4</v>
@@ -5184,13 +5193,13 @@
         <v>0.14</v>
       </c>
       <c r="BH4">
-        <v>1.1606</v>
+        <v>1.1604</v>
       </c>
       <c r="BI4" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ4">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="BK4" t="s">
         <v>133</v>
@@ -5208,7 +5217,7 @@
         <v>10.9</v>
       </c>
       <c r="BP4">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="BQ4">
         <v>0</v>
@@ -5217,7 +5226,7 @@
         <v>1.043</v>
       </c>
       <c r="BS4">
-        <v>69.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="BT4">
         <v>65.2</v>
@@ -5226,7 +5235,7 @@
         <v>59.1</v>
       </c>
       <c r="BV4">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
       <c r="BW4">
         <v>58.1</v>
@@ -5235,25 +5244,25 @@
         <v>0</v>
       </c>
       <c r="BY4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ4">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="CA4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB4">
         <v>85</v>
       </c>
       <c r="CC4">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
       <c r="CD4">
         <v>8</v>
       </c>
       <c r="CE4">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:83">
@@ -5270,25 +5279,25 @@
         <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I5" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="J5">
-        <v>577</v>
+        <v>589.9</v>
       </c>
       <c r="K5">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -5297,16 +5306,16 @@
         <v>1.58</v>
       </c>
       <c r="N5">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>9</v>
+        <v>10.1</v>
       </c>
       <c r="Q5">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -5315,25 +5324,25 @@
         <v>0</v>
       </c>
       <c r="T5" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U5" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="V5" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="W5">
         <v>0.5833</v>
       </c>
       <c r="X5">
-        <v>12.6</v>
+        <v>11.9</v>
       </c>
       <c r="Y5">
-        <v>92.09999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="Z5">
-        <v>65.8</v>
+        <v>66</v>
       </c>
       <c r="AA5">
         <v>0.88</v>
@@ -5354,19 +5363,19 @@
         <v>85.40000000000001</v>
       </c>
       <c r="AG5">
-        <v>79.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="AH5">
-        <v>44.7</v>
+        <v>45.8</v>
       </c>
       <c r="AI5">
-        <v>26.3</v>
+        <v>26.9</v>
       </c>
       <c r="AJ5">
-        <v>1012.4</v>
+        <v>1012.5</v>
       </c>
       <c r="AK5">
-        <v>1014.6</v>
+        <v>1014.7</v>
       </c>
       <c r="AL5">
         <v>11.8</v>
@@ -5378,49 +5387,49 @@
         <v>0</v>
       </c>
       <c r="AO5">
-        <v>168.5</v>
+        <v>162</v>
       </c>
       <c r="AP5">
         <v>4</v>
       </c>
       <c r="AQ5">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="AR5">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="AS5" t="s">
         <v>156</v>
       </c>
       <c r="AT5">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AU5">
         <v>5.8</v>
       </c>
       <c r="AV5">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AW5">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="AX5">
         <v>4.8</v>
       </c>
       <c r="AY5">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AZ5">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BA5">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BB5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC5">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="BD5">
         <v>0.78</v>
@@ -5435,13 +5444,13 @@
         <v>0.14</v>
       </c>
       <c r="BH5">
-        <v>1.1603</v>
+        <v>1.1602</v>
       </c>
       <c r="BI5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ5">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="BK5" t="s">
         <v>133</v>
@@ -5450,16 +5459,16 @@
         <v>135</v>
       </c>
       <c r="BM5">
-        <v>67.2</v>
+        <v>67.3</v>
       </c>
       <c r="BN5">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="BO5">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="BP5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="BQ5">
         <v>0</v>
@@ -5471,13 +5480,13 @@
         <v>68.59999999999999</v>
       </c>
       <c r="BT5">
-        <v>64.59999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="BU5">
         <v>59</v>
       </c>
       <c r="BV5">
-        <v>53.5</v>
+        <v>53.6</v>
       </c>
       <c r="BW5">
         <v>58.1</v>
@@ -5486,13 +5495,13 @@
         <v>0</v>
       </c>
       <c r="BY5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ5">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="CA5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB5">
         <v>85</v>
@@ -5504,7 +5513,7 @@
         <v>8</v>
       </c>
       <c r="CE5">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="6" spans="1:83">
@@ -5521,25 +5530,25 @@
         <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F6" t="s">
         <v>108</v>
       </c>
       <c r="G6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H6" t="s">
         <v>192</v>
       </c>
       <c r="I6" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="J6">
-        <v>357.4</v>
+        <v>370.4</v>
       </c>
       <c r="K6">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -5566,13 +5575,13 @@
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U6" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="V6" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="W6">
         <v>0.0833</v>
@@ -5689,7 +5698,7 @@
         <v>1.156</v>
       </c>
       <c r="BI6" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ6">
         <v>1880</v>
@@ -5737,13 +5746,13 @@
         <v>0.2</v>
       </c>
       <c r="BY6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ6">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="CA6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB6">
         <v>87</v>
@@ -5772,25 +5781,25 @@
         <v>120</v>
       </c>
       <c r="E7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G7" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H7" t="s">
         <v>192</v>
       </c>
       <c r="I7" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="J7">
-        <v>357.4</v>
+        <v>370.4</v>
       </c>
       <c r="K7">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -5817,13 +5826,13 @@
         <v>56.2</v>
       </c>
       <c r="T7" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U7" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="V7" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="W7">
         <v>0.0833</v>
@@ -5832,7 +5841,7 @@
         <v>10.5</v>
       </c>
       <c r="Y7">
-        <v>91</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Z7">
         <v>49.1</v>
@@ -5892,7 +5901,7 @@
         <v>7</v>
       </c>
       <c r="AS7" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AT7">
         <v>75.59999999999999</v>
@@ -5940,7 +5949,7 @@
         <v>1.1612</v>
       </c>
       <c r="BI7" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ7">
         <v>1705</v>
@@ -5988,13 +5997,13 @@
         <v>0.2</v>
       </c>
       <c r="BY7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ7">
         <v>7.7</v>
       </c>
       <c r="CA7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB7">
         <v>84</v>
@@ -6023,25 +6032,25 @@
         <v>120</v>
       </c>
       <c r="E8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G8" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H8" t="s">
         <v>192</v>
       </c>
       <c r="I8" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="J8">
-        <v>357.4</v>
+        <v>370.4</v>
       </c>
       <c r="K8">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="L8">
         <v>5</v>
@@ -6068,13 +6077,13 @@
         <v>75</v>
       </c>
       <c r="T8" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U8" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="V8" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="W8">
         <v>0.0833</v>
@@ -6191,7 +6200,7 @@
         <v>1.169</v>
       </c>
       <c r="BI8" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ8">
         <v>1415</v>
@@ -6239,13 +6248,13 @@
         <v>0.2</v>
       </c>
       <c r="BY8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ8">
         <v>4.7</v>
       </c>
       <c r="CA8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB8">
         <v>80</v>
@@ -6274,25 +6283,25 @@
         <v>120</v>
       </c>
       <c r="E9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H9" t="s">
         <v>192</v>
       </c>
       <c r="I9" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="J9">
-        <v>357.4</v>
+        <v>370.4</v>
       </c>
       <c r="K9">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="L9">
         <v>5</v>
@@ -6319,13 +6328,13 @@
         <v>100</v>
       </c>
       <c r="T9" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U9" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="V9" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="W9">
         <v>0.0833</v>
@@ -6394,7 +6403,7 @@
         <v>9.4</v>
       </c>
       <c r="AS9" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AT9">
         <v>150.3</v>
@@ -6442,7 +6451,7 @@
         <v>1.1726</v>
       </c>
       <c r="BI9" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ9">
         <v>1288</v>
@@ -6490,13 +6499,13 @@
         <v>0.2</v>
       </c>
       <c r="BY9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ9">
         <v>6.5</v>
       </c>
       <c r="CA9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB9">
         <v>79</v>
@@ -6525,25 +6534,25 @@
         <v>119</v>
       </c>
       <c r="E10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F10" t="s">
         <v>109</v>
       </c>
       <c r="G10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I10" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="J10">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="K10">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="L10">
         <v>5</v>
@@ -6570,13 +6579,13 @@
         <v>25</v>
       </c>
       <c r="T10" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U10" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="V10" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="W10">
         <v>0.1667</v>
@@ -6693,7 +6702,7 @@
         <v>1.1688</v>
       </c>
       <c r="BI10" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ10">
         <v>1505</v>
@@ -6741,13 +6750,13 @@
         <v>0</v>
       </c>
       <c r="BY10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ10">
         <v>7.9</v>
       </c>
       <c r="CA10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB10">
         <v>80</v>
@@ -6776,25 +6785,25 @@
         <v>119</v>
       </c>
       <c r="E11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I11" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="J11">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="K11">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="L11">
         <v>5</v>
@@ -6821,13 +6830,13 @@
         <v>81.2</v>
       </c>
       <c r="T11" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U11" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="V11" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="W11">
         <v>0.1667</v>
@@ -6896,7 +6905,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="AS11" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AT11">
         <v>316.6</v>
@@ -6944,7 +6953,7 @@
         <v>1.1761</v>
       </c>
       <c r="BI11" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ11">
         <v>1275</v>
@@ -6992,13 +7001,13 @@
         <v>0</v>
       </c>
       <c r="BY11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ11">
         <v>10.4</v>
       </c>
       <c r="CA11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB11">
         <v>77</v>
@@ -7027,25 +7036,25 @@
         <v>119</v>
       </c>
       <c r="E12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F12" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G12" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="J12">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="K12">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="L12">
         <v>5</v>
@@ -7072,13 +7081,13 @@
         <v>81.2</v>
       </c>
       <c r="T12" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U12" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="V12" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="W12">
         <v>0.1667</v>
@@ -7147,7 +7156,7 @@
         <v>7.4</v>
       </c>
       <c r="AS12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AT12">
         <v>89.09999999999999</v>
@@ -7195,7 +7204,7 @@
         <v>1.1831</v>
       </c>
       <c r="BI12" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ12">
         <v>1049</v>
@@ -7243,13 +7252,13 @@
         <v>0</v>
       </c>
       <c r="BY12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ12">
         <v>10.7</v>
       </c>
       <c r="CA12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB12">
         <v>75</v>
@@ -7278,25 +7287,25 @@
         <v>119</v>
       </c>
       <c r="E13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I13" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="J13">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="K13">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="L13">
         <v>5</v>
@@ -7323,13 +7332,13 @@
         <v>81.2</v>
       </c>
       <c r="T13" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U13" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="V13" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="W13">
         <v>0.1667</v>
@@ -7398,7 +7407,7 @@
         <v>7.2</v>
       </c>
       <c r="AS13" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AT13">
         <v>144.5</v>
@@ -7446,7 +7455,7 @@
         <v>1.189</v>
       </c>
       <c r="BI13" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ13">
         <v>873</v>
@@ -7494,13 +7503,13 @@
         <v>0</v>
       </c>
       <c r="BY13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ13">
         <v>8.199999999999999</v>
       </c>
       <c r="CA13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB13">
         <v>72</v>
@@ -7529,25 +7538,25 @@
         <v>121</v>
       </c>
       <c r="E14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F14" t="s">
         <v>109</v>
       </c>
       <c r="G14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I14" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J14">
-        <v>502.2</v>
+        <v>515.1</v>
       </c>
       <c r="K14">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="L14">
         <v>5</v>
@@ -7574,13 +7583,13 @@
         <v>56.2</v>
       </c>
       <c r="T14" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U14" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="V14" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="W14">
         <v>0.1667</v>
@@ -7697,7 +7706,7 @@
         <v>1.1393</v>
       </c>
       <c r="BI14" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ14">
         <v>2273</v>
@@ -7745,13 +7754,13 @@
         <v>3.9</v>
       </c>
       <c r="BY14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ14">
         <v>3</v>
       </c>
       <c r="CA14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB14">
         <v>85</v>
@@ -7780,25 +7789,25 @@
         <v>121</v>
       </c>
       <c r="E15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H15" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J15">
-        <v>502.2</v>
+        <v>515.1</v>
       </c>
       <c r="K15">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="L15">
         <v>5</v>
@@ -7825,13 +7834,13 @@
         <v>56.2</v>
       </c>
       <c r="T15" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U15" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="V15" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="W15">
         <v>0.1667</v>
@@ -7900,7 +7909,7 @@
         <v>5.8</v>
       </c>
       <c r="AS15" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AT15">
         <v>78.2</v>
@@ -7948,7 +7957,7 @@
         <v>1.1418</v>
       </c>
       <c r="BI15" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ15">
         <v>2187</v>
@@ -7996,13 +8005,13 @@
         <v>13.7</v>
       </c>
       <c r="BY15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ15">
         <v>6</v>
       </c>
       <c r="CA15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB15">
         <v>83</v>
@@ -8031,25 +8040,25 @@
         <v>121</v>
       </c>
       <c r="E16" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F16" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G16" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I16" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J16">
-        <v>502.2</v>
+        <v>515.1</v>
       </c>
       <c r="K16">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="L16">
         <v>5</v>
@@ -8076,13 +8085,13 @@
         <v>56.2</v>
       </c>
       <c r="T16" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U16" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="V16" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="W16">
         <v>0.1667</v>
@@ -8151,7 +8160,7 @@
         <v>6</v>
       </c>
       <c r="AS16" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AT16">
         <v>133.6</v>
@@ -8199,7 +8208,7 @@
         <v>1.1467</v>
       </c>
       <c r="BI16" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ16">
         <v>2033</v>
@@ -8247,13 +8256,13 @@
         <v>11.6</v>
       </c>
       <c r="BY16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ16">
         <v>8</v>
       </c>
       <c r="CA16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB16">
         <v>80</v>
@@ -8282,25 +8291,25 @@
         <v>121</v>
       </c>
       <c r="E17" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G17" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I17" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J17">
-        <v>502.2</v>
+        <v>515.1</v>
       </c>
       <c r="K17">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="L17">
         <v>5</v>
@@ -8327,13 +8336,13 @@
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U17" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="V17" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="W17">
         <v>0.1667</v>
@@ -8402,7 +8411,7 @@
         <v>7.6</v>
       </c>
       <c r="AS17" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AT17">
         <v>169.9</v>
@@ -8450,7 +8459,7 @@
         <v>1.1488</v>
       </c>
       <c r="BI17" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ17">
         <v>1977</v>
@@ -8498,13 +8507,13 @@
         <v>2.5</v>
       </c>
       <c r="BY17" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ17">
         <v>11.9</v>
       </c>
       <c r="CA17" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB17">
         <v>79</v>
@@ -8533,25 +8542,25 @@
         <v>122</v>
       </c>
       <c r="E18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F18" t="s">
         <v>110</v>
       </c>
       <c r="G18" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I18" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="J18">
-        <v>346.2</v>
+        <v>14.8</v>
       </c>
       <c r="K18">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="L18">
         <v>5</v>
@@ -8578,13 +8587,13 @@
         <v>0</v>
       </c>
       <c r="T18" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U18" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="V18" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="W18">
         <v>0.25</v>
@@ -8701,7 +8710,7 @@
         <v>1.123</v>
       </c>
       <c r="BI18" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ18">
         <v>2642</v>
@@ -8749,13 +8758,13 @@
         <v>38.7</v>
       </c>
       <c r="BY18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BZ18">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="CA18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB18">
         <v>84</v>
@@ -8784,25 +8793,25 @@
         <v>122</v>
       </c>
       <c r="E19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F19" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G19" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I19" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="J19">
-        <v>346.2</v>
+        <v>14.8</v>
       </c>
       <c r="K19">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="L19">
         <v>5</v>
@@ -8829,13 +8838,13 @@
         <v>0</v>
       </c>
       <c r="T19" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U19" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="V19" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="W19">
         <v>0.25</v>
@@ -8886,7 +8895,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="AM19">
-        <v>20.2</v>
+        <v>21.6</v>
       </c>
       <c r="AN19">
         <v>0.002</v>
@@ -8952,7 +8961,7 @@
         <v>1.1261</v>
       </c>
       <c r="BI19" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ19">
         <v>2547</v>
@@ -8997,16 +9006,16 @@
         <v>54.2</v>
       </c>
       <c r="BX19">
-        <v>24</v>
+        <v>24.8</v>
       </c>
       <c r="BY19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BZ19">
         <v>2.8</v>
       </c>
       <c r="CA19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB19">
         <v>82</v>
@@ -9035,25 +9044,25 @@
         <v>122</v>
       </c>
       <c r="E20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F20" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G20" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H20" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I20" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="J20">
-        <v>346.2</v>
+        <v>14.8</v>
       </c>
       <c r="K20">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="L20">
         <v>5</v>
@@ -9080,13 +9089,13 @@
         <v>0</v>
       </c>
       <c r="T20" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U20" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="V20" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="W20">
         <v>0.25</v>
@@ -9137,7 +9146,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="AM20">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AN20">
         <v>0</v>
@@ -9155,7 +9164,7 @@
         <v>14.4</v>
       </c>
       <c r="AS20" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AT20">
         <v>305.7</v>
@@ -9203,7 +9212,7 @@
         <v>1.1303</v>
       </c>
       <c r="BI20" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ20">
         <v>2417</v>
@@ -9248,7 +9257,7 @@
         <v>56.8</v>
       </c>
       <c r="BX20">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="BY20" t="s">
         <v>189</v>
@@ -9257,7 +9266,7 @@
         <v>3.6</v>
       </c>
       <c r="CA20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB20">
         <v>80</v>
@@ -9286,25 +9295,25 @@
         <v>122</v>
       </c>
       <c r="E21" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F21" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G21" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I21" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="J21">
-        <v>346.2</v>
+        <v>14.8</v>
       </c>
       <c r="K21">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -9331,13 +9340,13 @@
         <v>0</v>
       </c>
       <c r="T21" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U21" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="V21" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="W21">
         <v>0.25</v>
@@ -9388,7 +9397,7 @@
         <v>94</v>
       </c>
       <c r="AM21">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AN21">
         <v>0</v>
@@ -9406,7 +9415,7 @@
         <v>12.1</v>
       </c>
       <c r="AS21" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AT21">
         <v>307.5</v>
@@ -9454,7 +9463,7 @@
         <v>1.1347</v>
       </c>
       <c r="BI21" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ21">
         <v>2283</v>
@@ -9499,16 +9508,16 @@
         <v>59</v>
       </c>
       <c r="BX21">
-        <v>16.3</v>
+        <v>17.1</v>
       </c>
       <c r="BY21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ21">
         <v>2.7</v>
       </c>
       <c r="CA21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB21">
         <v>78</v>
@@ -9537,22 +9546,22 @@
         <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F22" t="s">
         <v>110</v>
       </c>
       <c r="G22" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H22" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="L22">
         <v>4</v>
@@ -9579,13 +9588,13 @@
         <v>0</v>
       </c>
       <c r="T22" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U22" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="V22" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="W22">
         <v>0.25</v>
@@ -9702,7 +9711,7 @@
         <v>1.171</v>
       </c>
       <c r="BI22" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ22">
         <v>1338</v>
@@ -9750,13 +9759,13 @@
         <v>1.2</v>
       </c>
       <c r="BY22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ22">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="CA22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CC22">
         <v>74.59999999999999</v>
@@ -9782,22 +9791,22 @@
         <v>123</v>
       </c>
       <c r="E23" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F23" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G23" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="L23">
         <v>4</v>
@@ -9824,13 +9833,13 @@
         <v>56.2</v>
       </c>
       <c r="T23" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U23" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="V23" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="W23">
         <v>0.25</v>
@@ -9899,7 +9908,7 @@
         <v>7.1</v>
       </c>
       <c r="AS23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AT23">
         <v>94.90000000000001</v>
@@ -9947,7 +9956,7 @@
         <v>1.1724</v>
       </c>
       <c r="BI23" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ23">
         <v>1295</v>
@@ -9995,13 +10004,13 @@
         <v>1.7</v>
       </c>
       <c r="BY23" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ23">
         <v>1.6</v>
       </c>
       <c r="CA23" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CC23">
         <v>73.8</v>
@@ -10027,22 +10036,22 @@
         <v>123</v>
       </c>
       <c r="E24" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F24" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G24" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="L24">
         <v>4</v>
@@ -10069,13 +10078,13 @@
         <v>56.2</v>
       </c>
       <c r="T24" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U24" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="V24" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="W24">
         <v>0.25</v>
@@ -10144,7 +10153,7 @@
         <v>6.4</v>
       </c>
       <c r="AS24" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AT24">
         <v>86.59999999999999</v>
@@ -10192,7 +10201,7 @@
         <v>1.1749</v>
       </c>
       <c r="BI24" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ24">
         <v>1218</v>
@@ -10240,13 +10249,13 @@
         <v>2.6</v>
       </c>
       <c r="BY24" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ24">
         <v>1.7</v>
       </c>
       <c r="CA24" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CC24">
         <v>72.59999999999999</v>
@@ -10272,22 +10281,22 @@
         <v>123</v>
       </c>
       <c r="E25" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F25" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G25" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H25" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="L25">
         <v>4</v>
@@ -10314,13 +10323,13 @@
         <v>56.2</v>
       </c>
       <c r="T25" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U25" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="V25" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="W25">
         <v>0.25</v>
@@ -10389,7 +10398,7 @@
         <v>5.7</v>
       </c>
       <c r="AS25" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AT25">
         <v>76.8</v>
@@ -10437,7 +10446,7 @@
         <v>1.1748</v>
       </c>
       <c r="BI25" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ25">
         <v>1226</v>
@@ -10485,13 +10494,13 @@
         <v>3.7</v>
       </c>
       <c r="BY25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ25">
         <v>1.8</v>
       </c>
       <c r="CA25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CC25">
         <v>72.59999999999999</v>
@@ -10517,25 +10526,25 @@
         <v>124</v>
       </c>
       <c r="E26" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F26" t="s">
         <v>111</v>
       </c>
       <c r="G26" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H26" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I26" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J26">
-        <v>181.7</v>
+        <v>19.9</v>
       </c>
       <c r="K26">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="L26">
         <v>5</v>
@@ -10562,13 +10571,13 @@
         <v>100</v>
       </c>
       <c r="T26" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U26" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="V26" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="W26">
         <v>0.6667</v>
@@ -10577,10 +10586,10 @@
         <v>26.3</v>
       </c>
       <c r="Y26">
-        <v>82.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="Z26">
-        <v>53.2</v>
+        <v>53.3</v>
       </c>
       <c r="AA26">
         <v>0.82</v>
@@ -10598,7 +10607,7 @@
         <v>143</v>
       </c>
       <c r="AF26">
-        <v>87</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="AG26">
         <v>96.40000000000001</v>
@@ -10607,7 +10616,7 @@
         <v>71.2</v>
       </c>
       <c r="AI26">
-        <v>59.3</v>
+        <v>58.5</v>
       </c>
       <c r="AJ26">
         <v>987.7</v>
@@ -10619,7 +10628,7 @@
         <v>60.3</v>
       </c>
       <c r="AM26">
-        <v>21.5</v>
+        <v>19.3</v>
       </c>
       <c r="AN26">
         <v>0.008999999999999999</v>
@@ -10631,7 +10640,7 @@
         <v>1910</v>
       </c>
       <c r="AQ26">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="AR26">
         <v>11.5</v>
@@ -10640,7 +10649,7 @@
         <v>160</v>
       </c>
       <c r="AT26">
-        <v>207.1</v>
+        <v>190.9</v>
       </c>
       <c r="AU26">
         <v>-0</v>
@@ -10685,7 +10694,7 @@
         <v>1.1896</v>
       </c>
       <c r="BI26" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ26">
         <v>858</v>
@@ -10733,22 +10742,22 @@
         <v>0</v>
       </c>
       <c r="BY26" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="BZ26">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
       <c r="CA26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB26">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="CC26">
         <v>87</v>
       </c>
       <c r="CD26">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="CE26">
         <v>6</v>
@@ -10768,25 +10777,25 @@
         <v>124</v>
       </c>
       <c r="E27" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F27" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G27" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H27" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I27" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J27">
-        <v>181.7</v>
+        <v>19.9</v>
       </c>
       <c r="K27">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="L27">
         <v>5</v>
@@ -10813,13 +10822,13 @@
         <v>100</v>
       </c>
       <c r="T27" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U27" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="V27" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="W27">
         <v>0.6667</v>
@@ -10828,10 +10837,10 @@
         <v>33</v>
       </c>
       <c r="Y27">
-        <v>76.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="Z27">
-        <v>56.8</v>
+        <v>57</v>
       </c>
       <c r="AA27">
         <v>0.82</v>
@@ -10846,10 +10855,10 @@
         <v>0.5</v>
       </c>
       <c r="AE27" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AF27">
-        <v>84.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="AG27">
         <v>89.09999999999999</v>
@@ -10858,7 +10867,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="AI27">
-        <v>62</v>
+        <v>61.1</v>
       </c>
       <c r="AJ27">
         <v>987.5</v>
@@ -10870,7 +10879,7 @@
         <v>75</v>
       </c>
       <c r="AM27">
-        <v>16.1</v>
+        <v>14.7</v>
       </c>
       <c r="AN27">
         <v>0.019</v>
@@ -10933,13 +10942,13 @@
         <v>0.1</v>
       </c>
       <c r="BH27">
-        <v>1.1268</v>
+        <v>1.126</v>
       </c>
       <c r="BI27" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ27">
-        <v>2568</v>
+        <v>2596</v>
       </c>
       <c r="BK27" t="s">
         <v>133</v>
@@ -10948,10 +10957,10 @@
         <v>136</v>
       </c>
       <c r="BM27">
-        <v>58.9</v>
+        <v>59</v>
       </c>
       <c r="BN27">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BO27">
         <v>-0.9</v>
@@ -10966,34 +10975,34 @@
         <v>1.021</v>
       </c>
       <c r="BS27">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="BT27">
-        <v>61.7</v>
+        <v>61.8</v>
       </c>
       <c r="BU27">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
       <c r="BV27">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="BW27">
-        <v>53.7</v>
+        <v>53.2</v>
       </c>
       <c r="BX27">
-        <v>28.5</v>
+        <v>27.7</v>
       </c>
       <c r="BY27" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BZ27">
-        <v>15.1</v>
+        <v>13.1</v>
       </c>
       <c r="CA27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB27">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="CC27">
         <v>85.09999999999999</v>
@@ -11019,25 +11028,25 @@
         <v>124</v>
       </c>
       <c r="E28" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F28" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G28" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H28" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I28" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J28">
-        <v>181.7</v>
+        <v>19.9</v>
       </c>
       <c r="K28">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="L28">
         <v>5</v>
@@ -11064,13 +11073,13 @@
         <v>0</v>
       </c>
       <c r="T28" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U28" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="V28" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="W28">
         <v>0.6667</v>
@@ -11079,10 +11088,10 @@
         <v>27.5</v>
       </c>
       <c r="Y28">
-        <v>80.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="Z28">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
       <c r="AA28">
         <v>0.82</v>
@@ -11097,10 +11106,10 @@
         <v>0.5</v>
       </c>
       <c r="AE28" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AF28">
-        <v>82.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="AG28">
         <v>87.09999999999999</v>
@@ -11109,7 +11118,7 @@
         <v>70.2</v>
       </c>
       <c r="AI28">
-        <v>67.5</v>
+        <v>66.7</v>
       </c>
       <c r="AJ28">
         <v>987.2</v>
@@ -11121,7 +11130,7 @@
         <v>72.7</v>
       </c>
       <c r="AM28">
-        <v>8.800000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="AN28">
         <v>0.008999999999999999</v>
@@ -11184,13 +11193,13 @@
         <v>0.1</v>
       </c>
       <c r="BH28">
-        <v>1.1311</v>
+        <v>1.1303</v>
       </c>
       <c r="BI28" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ28">
-        <v>2428</v>
+        <v>2455</v>
       </c>
       <c r="BK28" t="s">
         <v>133</v>
@@ -11199,10 +11208,10 @@
         <v>136</v>
       </c>
       <c r="BM28">
-        <v>60.5</v>
+        <v>60.6</v>
       </c>
       <c r="BN28">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="BO28">
         <v>1.1</v>
@@ -11226,25 +11235,25 @@
         <v>58.5</v>
       </c>
       <c r="BV28">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="BW28">
-        <v>56.6</v>
+        <v>56.1</v>
       </c>
       <c r="BX28">
-        <v>20.5</v>
+        <v>21.2</v>
       </c>
       <c r="BY28" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BZ28">
-        <v>12.7</v>
+        <v>12.2</v>
       </c>
       <c r="CA28" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB28">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="CC28">
         <v>82.59999999999999</v>
@@ -11270,25 +11279,25 @@
         <v>124</v>
       </c>
       <c r="E29" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F29" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G29" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I29" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J29">
-        <v>181.7</v>
+        <v>19.9</v>
       </c>
       <c r="K29">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="L29">
         <v>5</v>
@@ -11315,13 +11324,13 @@
         <v>0</v>
       </c>
       <c r="T29" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U29" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="V29" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="W29">
         <v>0.6667</v>
@@ -11330,10 +11339,10 @@
         <v>22.6</v>
       </c>
       <c r="Y29">
-        <v>84.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Z29">
-        <v>59.4</v>
+        <v>59.6</v>
       </c>
       <c r="AA29">
         <v>0.82</v>
@@ -11351,7 +11360,7 @@
         <v>140</v>
       </c>
       <c r="AF29">
-        <v>80.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="AG29">
         <v>86.8</v>
@@ -11360,7 +11369,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="AI29">
-        <v>71.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="AJ29">
         <v>987.2</v>
@@ -11372,7 +11381,7 @@
         <v>68.90000000000001</v>
       </c>
       <c r="AM29">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="AN29">
         <v>0.001</v>
@@ -11435,13 +11444,13 @@
         <v>0.1</v>
       </c>
       <c r="BH29">
-        <v>1.1348</v>
+        <v>1.133</v>
       </c>
       <c r="BI29" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ29">
-        <v>2316</v>
+        <v>2371</v>
       </c>
       <c r="BK29" t="s">
         <v>133</v>
@@ -11450,10 +11459,10 @@
         <v>136</v>
       </c>
       <c r="BM29">
-        <v>61.2</v>
+        <v>61.4</v>
       </c>
       <c r="BN29">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BO29">
         <v>2.1</v>
@@ -11468,34 +11477,34 @@
         <v>1.027</v>
       </c>
       <c r="BS29">
-        <v>58.8</v>
+        <v>59</v>
       </c>
       <c r="BT29">
-        <v>63.4</v>
+        <v>63.5</v>
       </c>
       <c r="BU29">
-        <v>58.2</v>
+        <v>58.3</v>
       </c>
       <c r="BV29">
-        <v>53.1</v>
+        <v>53.3</v>
       </c>
       <c r="BW29">
-        <v>58.9</v>
+        <v>58</v>
       </c>
       <c r="BX29">
-        <v>13.1</v>
+        <v>13.9</v>
       </c>
       <c r="BY29" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ29">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA29" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB29">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="CC29">
         <v>81.09999999999999</v>
@@ -11521,25 +11530,25 @@
         <v>125</v>
       </c>
       <c r="E30" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F30" t="s">
         <v>112</v>
       </c>
       <c r="G30" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H30" t="s">
         <v>197</v>
       </c>
       <c r="I30" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="J30">
-        <v>77.59999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="K30">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="L30">
         <v>5</v>
@@ -11566,13 +11575,13 @@
         <v>0</v>
       </c>
       <c r="T30" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U30" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="V30" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="W30">
         <v>0.0833</v>
@@ -11689,7 +11698,7 @@
         <v>1.1497</v>
       </c>
       <c r="BI30" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ30">
         <v>1889</v>
@@ -11737,13 +11746,13 @@
         <v>29.6</v>
       </c>
       <c r="BY30" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BZ30">
         <v>21.8</v>
       </c>
       <c r="CA30" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="CB30">
         <v>86</v>
@@ -11772,25 +11781,25 @@
         <v>125</v>
       </c>
       <c r="E31" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F31" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G31" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H31" t="s">
         <v>197</v>
       </c>
       <c r="I31" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="J31">
-        <v>77.59999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="K31">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="L31">
         <v>5</v>
@@ -11817,13 +11826,13 @@
         <v>0</v>
       </c>
       <c r="T31" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U31" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="V31" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="W31">
         <v>0.0833</v>
@@ -11940,7 +11949,7 @@
         <v>1.1518</v>
       </c>
       <c r="BI31" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ31">
         <v>1821</v>
@@ -11988,13 +11997,13 @@
         <v>25.6</v>
       </c>
       <c r="BY31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BZ31">
         <v>3.9</v>
       </c>
       <c r="CA31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB31">
         <v>84</v>
@@ -12023,25 +12032,25 @@
         <v>125</v>
       </c>
       <c r="E32" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F32" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G32" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H32" t="s">
         <v>197</v>
       </c>
       <c r="I32" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="J32">
-        <v>77.59999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="K32">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="L32">
         <v>5</v>
@@ -12068,13 +12077,13 @@
         <v>0</v>
       </c>
       <c r="T32" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U32" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="V32" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="W32">
         <v>0.0833</v>
@@ -12191,7 +12200,7 @@
         <v>1.1537</v>
       </c>
       <c r="BI32" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ32">
         <v>1747</v>
@@ -12239,13 +12248,13 @@
         <v>23.1</v>
       </c>
       <c r="BY32" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BZ32">
         <v>8.1</v>
       </c>
       <c r="CA32" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB32">
         <v>83</v>
@@ -12274,25 +12283,25 @@
         <v>125</v>
       </c>
       <c r="E33" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F33" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G33" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H33" t="s">
         <v>197</v>
       </c>
       <c r="I33" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="J33">
-        <v>77.59999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="K33">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="L33">
         <v>5</v>
@@ -12319,13 +12328,13 @@
         <v>0</v>
       </c>
       <c r="T33" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U33" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="V33" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="W33">
         <v>0.0833</v>
@@ -12352,7 +12361,7 @@
         <v>1.8</v>
       </c>
       <c r="AE33" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="AF33">
         <v>81.09999999999999</v>
@@ -12442,7 +12451,7 @@
         <v>1.1564</v>
       </c>
       <c r="BI33" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ33">
         <v>1654</v>
@@ -12490,13 +12499,13 @@
         <v>19.7</v>
       </c>
       <c r="BY33" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ33">
         <v>7.8</v>
       </c>
       <c r="CA33" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB33">
         <v>81</v>
@@ -12525,25 +12534,25 @@
         <v>126</v>
       </c>
       <c r="E34" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F34" t="s">
         <v>113</v>
       </c>
       <c r="G34" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H34" t="s">
         <v>198</v>
       </c>
       <c r="I34" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J34">
-        <v>52.5</v>
+        <v>65.5</v>
       </c>
       <c r="K34">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="L34">
         <v>5</v>
@@ -12570,13 +12579,13 @@
         <v>0</v>
       </c>
       <c r="T34" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U34" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="V34" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="W34">
         <v>0.1667</v>
@@ -12645,7 +12654,7 @@
         <v>12.2</v>
       </c>
       <c r="AS34" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AT34">
         <v>170.5</v>
@@ -12693,7 +12702,7 @@
         <v>1.1896</v>
       </c>
       <c r="BI34" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ34">
         <v>858</v>
@@ -12741,13 +12750,13 @@
         <v>0</v>
       </c>
       <c r="BY34" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="BZ34">
         <v>13</v>
       </c>
       <c r="CA34" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB34">
         <v>90</v>
@@ -12776,25 +12785,25 @@
         <v>126</v>
       </c>
       <c r="E35" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F35" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G35" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H35" t="s">
         <v>198</v>
       </c>
       <c r="I35" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J35">
-        <v>52.5</v>
+        <v>65.5</v>
       </c>
       <c r="K35">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="L35">
         <v>5</v>
@@ -12821,13 +12830,13 @@
         <v>0</v>
       </c>
       <c r="T35" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U35" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="V35" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="W35">
         <v>0.1667</v>
@@ -12839,7 +12848,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="Z35">
-        <v>66.2</v>
+        <v>66.3</v>
       </c>
       <c r="AA35">
         <v>0.76</v>
@@ -12896,7 +12905,7 @@
         <v>11.4</v>
       </c>
       <c r="AS35" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AT35">
         <v>171.9</v>
@@ -12944,7 +12953,7 @@
         <v>1.1575</v>
       </c>
       <c r="BI35" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ35">
         <v>1621</v>
@@ -12992,13 +13001,13 @@
         <v>12.9</v>
       </c>
       <c r="BY35" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ35">
         <v>15.8</v>
       </c>
       <c r="CA35" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB35">
         <v>88</v>
@@ -13027,25 +13036,25 @@
         <v>126</v>
       </c>
       <c r="E36" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F36" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G36" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H36" t="s">
         <v>198</v>
       </c>
       <c r="I36" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J36">
-        <v>52.5</v>
+        <v>65.5</v>
       </c>
       <c r="K36">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="L36">
         <v>5</v>
@@ -13072,13 +13081,13 @@
         <v>0</v>
       </c>
       <c r="T36" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U36" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="V36" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="W36">
         <v>0.1667</v>
@@ -13147,7 +13156,7 @@
         <v>11.1</v>
       </c>
       <c r="AS36" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AT36">
         <v>169.9</v>
@@ -13195,7 +13204,7 @@
         <v>1.1622</v>
       </c>
       <c r="BI36" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ36">
         <v>1467</v>
@@ -13243,13 +13252,13 @@
         <v>12.5</v>
       </c>
       <c r="BY36" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ36">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="CA36" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB36">
         <v>85</v>
@@ -13278,25 +13287,25 @@
         <v>126</v>
       </c>
       <c r="E37" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F37" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G37" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H37" t="s">
         <v>198</v>
       </c>
       <c r="I37" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J37">
-        <v>52.5</v>
+        <v>65.5</v>
       </c>
       <c r="K37">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="L37">
         <v>5</v>
@@ -13323,13 +13332,13 @@
         <v>0</v>
       </c>
       <c r="T37" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U37" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="V37" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="W37">
         <v>0.1667</v>
@@ -13398,7 +13407,7 @@
         <v>10.9</v>
       </c>
       <c r="AS37" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AT37">
         <v>175.5</v>
@@ -13446,7 +13455,7 @@
         <v>1.1646</v>
       </c>
       <c r="BI37" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ37">
         <v>1385</v>
@@ -13494,13 +13503,13 @@
         <v>12.9</v>
       </c>
       <c r="BY37" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ37">
         <v>10.8</v>
       </c>
       <c r="CA37" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB37">
         <v>84</v>
@@ -13529,25 +13538,25 @@
         <v>127</v>
       </c>
       <c r="E38" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F38" t="s">
         <v>113</v>
       </c>
       <c r="G38" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H38" t="s">
         <v>199</v>
       </c>
       <c r="I38" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J38">
-        <v>26.8</v>
+        <v>39.8</v>
       </c>
       <c r="K38">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="L38">
         <v>5</v>
@@ -13574,13 +13583,13 @@
         <v>0</v>
       </c>
       <c r="T38" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U38" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="V38" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="W38">
         <v>0.1667</v>
@@ -13697,7 +13706,7 @@
         <v>1.1173</v>
       </c>
       <c r="BI38" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ38">
         <v>2873</v>
@@ -13745,13 +13754,13 @@
         <v>22.5</v>
       </c>
       <c r="BY38" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BZ38">
         <v>11.9</v>
       </c>
       <c r="CA38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB38">
         <v>89</v>
@@ -13780,25 +13789,25 @@
         <v>127</v>
       </c>
       <c r="E39" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F39" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G39" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H39" t="s">
         <v>199</v>
       </c>
       <c r="I39" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J39">
-        <v>26.8</v>
+        <v>39.8</v>
       </c>
       <c r="K39">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="L39">
         <v>5</v>
@@ -13825,13 +13834,13 @@
         <v>0</v>
       </c>
       <c r="T39" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U39" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="V39" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="W39">
         <v>0.1667</v>
@@ -13900,7 +13909,7 @@
         <v>20.3</v>
       </c>
       <c r="AS39" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AT39">
         <v>203.6</v>
@@ -13948,7 +13957,7 @@
         <v>1.1216</v>
       </c>
       <c r="BI39" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ39">
         <v>2731</v>
@@ -13996,13 +14005,13 @@
         <v>18.7</v>
       </c>
       <c r="BY39" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ39">
         <v>12.5</v>
       </c>
       <c r="CA39" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB39">
         <v>87</v>
@@ -14031,25 +14040,25 @@
         <v>127</v>
       </c>
       <c r="E40" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F40" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G40" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H40" t="s">
         <v>199</v>
       </c>
       <c r="I40" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J40">
-        <v>26.8</v>
+        <v>39.8</v>
       </c>
       <c r="K40">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="L40">
         <v>5</v>
@@ -14076,13 +14085,13 @@
         <v>0</v>
       </c>
       <c r="T40" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U40" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="V40" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="W40">
         <v>0.1667</v>
@@ -14151,7 +14160,7 @@
         <v>14.5</v>
       </c>
       <c r="AS40" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AT40">
         <v>199.1</v>
@@ -14199,7 +14208,7 @@
         <v>1.1259</v>
       </c>
       <c r="BI40" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ40">
         <v>2592</v>
@@ -14247,13 +14256,13 @@
         <v>15.1</v>
       </c>
       <c r="BY40" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ40">
         <v>13.5</v>
       </c>
       <c r="CA40" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB40">
         <v>85</v>
@@ -14282,25 +14291,25 @@
         <v>127</v>
       </c>
       <c r="E41" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F41" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G41" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H41" t="s">
         <v>199</v>
       </c>
       <c r="I41" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J41">
-        <v>26.8</v>
+        <v>39.8</v>
       </c>
       <c r="K41">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="L41">
         <v>5</v>
@@ -14327,13 +14336,13 @@
         <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U41" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="V41" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="W41">
         <v>0.1667</v>
@@ -14402,7 +14411,7 @@
         <v>13.8</v>
       </c>
       <c r="AS41" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AT41">
         <v>202.4</v>
@@ -14450,7 +14459,7 @@
         <v>1.13</v>
       </c>
       <c r="BI41" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ41">
         <v>2461</v>
@@ -14498,13 +14507,13 @@
         <v>11.6</v>
       </c>
       <c r="BY41" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ41">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="CA41" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB41">
         <v>83</v>
@@ -14533,25 +14542,25 @@
         <v>128</v>
       </c>
       <c r="E42" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F42" t="s">
         <v>114</v>
       </c>
       <c r="G42" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H42" t="s">
         <v>200</v>
       </c>
       <c r="I42" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J42">
-        <v>592.6</v>
+        <v>605.6</v>
       </c>
       <c r="K42">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="L42">
         <v>5</v>
@@ -14578,13 +14587,13 @@
         <v>75</v>
       </c>
       <c r="T42" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U42" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="V42" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="W42">
         <v>0.6667</v>
@@ -14653,7 +14662,7 @@
         <v>17.1</v>
       </c>
       <c r="AS42" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AT42">
         <v>88.8</v>
@@ -14701,7 +14710,7 @@
         <v>0.9556</v>
       </c>
       <c r="BI42" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="BJ42">
         <v>8309</v>
@@ -14749,13 +14758,13 @@
         <v>1.8</v>
       </c>
       <c r="BY42" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ42">
         <v>4.3</v>
       </c>
       <c r="CA42" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB42">
         <v>92</v>
@@ -14784,25 +14793,25 @@
         <v>128</v>
       </c>
       <c r="E43" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F43" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G43" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H43" t="s">
         <v>200</v>
       </c>
       <c r="I43" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J43">
-        <v>592.6</v>
+        <v>605.6</v>
       </c>
       <c r="K43">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="L43">
         <v>5</v>
@@ -14829,13 +14838,13 @@
         <v>75</v>
       </c>
       <c r="T43" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U43" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="V43" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="W43">
         <v>0.6667</v>
@@ -14952,7 +14961,7 @@
         <v>0.9583</v>
       </c>
       <c r="BI43" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="BJ43">
         <v>8204</v>
@@ -15000,13 +15009,13 @@
         <v>1.1</v>
       </c>
       <c r="BY43" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ43">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="CA43" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB43">
         <v>91</v>
@@ -15035,25 +15044,25 @@
         <v>128</v>
       </c>
       <c r="E44" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F44" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G44" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H44" t="s">
         <v>200</v>
       </c>
       <c r="I44" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J44">
-        <v>592.6</v>
+        <v>605.6</v>
       </c>
       <c r="K44">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="L44">
         <v>5</v>
@@ -15080,13 +15089,13 @@
         <v>0</v>
       </c>
       <c r="T44" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U44" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="V44" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="W44">
         <v>0.6667</v>
@@ -15203,7 +15212,7 @@
         <v>0.9641999999999999</v>
       </c>
       <c r="BI44" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="BJ44">
         <v>7979</v>
@@ -15251,13 +15260,13 @@
         <v>1.5</v>
       </c>
       <c r="BY44" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ44">
         <v>8.6</v>
       </c>
       <c r="CA44" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB44">
         <v>87</v>
@@ -15286,25 +15295,25 @@
         <v>128</v>
       </c>
       <c r="E45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F45" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G45" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H45" t="s">
         <v>200</v>
       </c>
       <c r="I45" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J45">
-        <v>592.6</v>
+        <v>605.6</v>
       </c>
       <c r="K45">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="L45">
         <v>5</v>
@@ -15331,13 +15340,13 @@
         <v>0</v>
       </c>
       <c r="T45" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U45" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="V45" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="W45">
         <v>0.6667</v>
@@ -15406,7 +15415,7 @@
         <v>19.4</v>
       </c>
       <c r="AS45" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AT45">
         <v>132.2</v>
@@ -15454,7 +15463,7 @@
         <v>0.9697</v>
       </c>
       <c r="BI45" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="BJ45">
         <v>7772</v>
@@ -15502,13 +15511,13 @@
         <v>0.8</v>
       </c>
       <c r="BY45" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ45">
         <v>7.2</v>
       </c>
       <c r="CA45" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB45">
         <v>84</v>
@@ -15537,25 +15546,25 @@
         <v>129</v>
       </c>
       <c r="E46" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F46" t="s">
         <v>115</v>
       </c>
       <c r="G46" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H46" t="s">
         <v>201</v>
       </c>
       <c r="I46" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="J46">
-        <v>52.7</v>
+        <v>65.7</v>
       </c>
       <c r="K46">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="L46">
         <v>5</v>
@@ -15582,13 +15591,13 @@
         <v>0</v>
       </c>
       <c r="T46" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U46" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="V46" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="W46">
         <v>0.6333</v>
@@ -15657,7 +15666,7 @@
         <v>13.4</v>
       </c>
       <c r="AS46" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AT46">
         <v>190.8</v>
@@ -15705,7 +15714,7 @@
         <v>1.1717</v>
       </c>
       <c r="BI46" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ46">
         <v>1281</v>
@@ -15753,13 +15762,13 @@
         <v>1.3</v>
       </c>
       <c r="BY46" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ46">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="CA46" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB46">
         <v>79</v>
@@ -15788,25 +15797,25 @@
         <v>129</v>
       </c>
       <c r="E47" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F47" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G47" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H47" t="s">
         <v>201</v>
       </c>
       <c r="I47" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="J47">
-        <v>52.7</v>
+        <v>65.7</v>
       </c>
       <c r="K47">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="L47">
         <v>5</v>
@@ -15833,13 +15842,13 @@
         <v>0</v>
       </c>
       <c r="T47" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U47" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="V47" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="W47">
         <v>0.6333</v>
@@ -15908,7 +15917,7 @@
         <v>12.8</v>
       </c>
       <c r="AS47" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AT47">
         <v>189.3</v>
@@ -15956,7 +15965,7 @@
         <v>1.1783</v>
       </c>
       <c r="BI47" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ47">
         <v>1087</v>
@@ -16004,13 +16013,13 @@
         <v>1.3</v>
       </c>
       <c r="BY47" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ47">
         <v>13.3</v>
       </c>
       <c r="CA47" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB47">
         <v>76</v>
@@ -16039,25 +16048,25 @@
         <v>129</v>
       </c>
       <c r="E48" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F48" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G48" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H48" t="s">
         <v>201</v>
       </c>
       <c r="I48" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="J48">
-        <v>52.7</v>
+        <v>65.7</v>
       </c>
       <c r="K48">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="L48">
         <v>5</v>
@@ -16084,13 +16093,13 @@
         <v>0</v>
       </c>
       <c r="T48" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U48" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="V48" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="W48">
         <v>0.6333</v>
@@ -16159,7 +16168,7 @@
         <v>11.7</v>
       </c>
       <c r="AS48" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AT48">
         <v>188.5</v>
@@ -16207,7 +16216,7 @@
         <v>1.1839</v>
       </c>
       <c r="BI48" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ48">
         <v>917</v>
@@ -16255,13 +16264,13 @@
         <v>1.3</v>
       </c>
       <c r="BY48" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ48">
         <v>8.5</v>
       </c>
       <c r="CA48" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB48">
         <v>73</v>
@@ -16290,25 +16299,25 @@
         <v>129</v>
       </c>
       <c r="E49" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F49" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G49" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H49" t="s">
         <v>201</v>
       </c>
       <c r="I49" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="J49">
-        <v>52.7</v>
+        <v>65.7</v>
       </c>
       <c r="K49">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="L49">
         <v>5</v>
@@ -16335,13 +16344,13 @@
         <v>0</v>
       </c>
       <c r="T49" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U49" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="V49" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="W49">
         <v>0.6333</v>
@@ -16410,7 +16419,7 @@
         <v>10.7</v>
       </c>
       <c r="AS49" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AT49">
         <v>186.4</v>
@@ -16458,7 +16467,7 @@
         <v>1.1875</v>
       </c>
       <c r="BI49" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ49">
         <v>808</v>
@@ -16506,13 +16515,13 @@
         <v>1.3</v>
       </c>
       <c r="BY49" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ49">
         <v>4.6</v>
       </c>
       <c r="CA49" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB49">
         <v>71</v>
@@ -16541,25 +16550,25 @@
         <v>130</v>
       </c>
       <c r="E50" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F50" t="s">
         <v>116</v>
       </c>
       <c r="G50" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H50" t="s">
         <v>202</v>
       </c>
       <c r="I50" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J50">
-        <v>458.1</v>
+        <v>471.1</v>
       </c>
       <c r="K50">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="L50">
         <v>5</v>
@@ -16586,13 +16595,13 @@
         <v>0</v>
       </c>
       <c r="T50" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U50" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="V50" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="W50">
         <v>0.6667</v>
@@ -16661,7 +16670,7 @@
         <v>21.3</v>
       </c>
       <c r="AS50" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AT50">
         <v>210.6</v>
@@ -16709,7 +16718,7 @@
         <v>1.157</v>
       </c>
       <c r="BI50" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ50">
         <v>1846</v>
@@ -16757,13 +16766,13 @@
         <v>0</v>
       </c>
       <c r="BY50" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ50">
         <v>7.1</v>
       </c>
       <c r="CA50" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB50">
         <v>84</v>
@@ -16792,25 +16801,25 @@
         <v>130</v>
       </c>
       <c r="E51" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F51" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G51" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H51" t="s">
         <v>202</v>
       </c>
       <c r="I51" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J51">
-        <v>458.1</v>
+        <v>471.1</v>
       </c>
       <c r="K51">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="L51">
         <v>5</v>
@@ -16837,13 +16846,13 @@
         <v>0</v>
       </c>
       <c r="T51" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U51" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="V51" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="W51">
         <v>0.6667</v>
@@ -16912,7 +16921,7 @@
         <v>22.5</v>
       </c>
       <c r="AS51" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AT51">
         <v>209.2</v>
@@ -16960,7 +16969,7 @@
         <v>1.1689</v>
       </c>
       <c r="BI51" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ51">
         <v>1474</v>
@@ -17008,13 +17017,13 @@
         <v>0</v>
       </c>
       <c r="BY51" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ51">
         <v>4.8</v>
       </c>
       <c r="CA51" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB51">
         <v>78</v>
@@ -17043,25 +17052,25 @@
         <v>130</v>
       </c>
       <c r="E52" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F52" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G52" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H52" t="s">
         <v>202</v>
       </c>
       <c r="I52" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J52">
-        <v>458.1</v>
+        <v>471.1</v>
       </c>
       <c r="K52">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="L52">
         <v>5</v>
@@ -17088,13 +17097,13 @@
         <v>0</v>
       </c>
       <c r="T52" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U52" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="V52" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="W52">
         <v>0.6667</v>
@@ -17163,7 +17172,7 @@
         <v>23.5</v>
       </c>
       <c r="AS52" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AT52">
         <v>206.4</v>
@@ -17211,7 +17220,7 @@
         <v>1.1815</v>
       </c>
       <c r="BI52" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ52">
         <v>1092</v>
@@ -17259,13 +17268,13 @@
         <v>0</v>
       </c>
       <c r="BY52" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ52">
         <v>5.5</v>
       </c>
       <c r="CA52" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB52">
         <v>72</v>
@@ -17294,25 +17303,25 @@
         <v>130</v>
       </c>
       <c r="E53" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F53" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G53" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H53" t="s">
         <v>202</v>
       </c>
       <c r="I53" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J53">
-        <v>458.1</v>
+        <v>471.1</v>
       </c>
       <c r="K53">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="L53">
         <v>5</v>
@@ -17339,13 +17348,13 @@
         <v>0</v>
       </c>
       <c r="T53" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U53" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="V53" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="W53">
         <v>0.6667</v>
@@ -17414,7 +17423,7 @@
         <v>23.6</v>
       </c>
       <c r="AS53" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AT53">
         <v>204.5</v>
@@ -17462,7 +17471,7 @@
         <v>1.1915</v>
       </c>
       <c r="BI53" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ53">
         <v>794</v>
@@ -17510,13 +17519,13 @@
         <v>0</v>
       </c>
       <c r="BY53" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ53">
         <v>3.5</v>
       </c>
       <c r="CA53" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB53">
         <v>68</v>
@@ -17545,25 +17554,25 @@
         <v>131</v>
       </c>
       <c r="E54" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F54" t="s">
         <v>117</v>
       </c>
       <c r="G54" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H54" t="s">
         <v>203</v>
       </c>
       <c r="I54" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="J54">
-        <v>345.6</v>
+        <v>358.6</v>
       </c>
       <c r="K54">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="L54">
         <v>5</v>
@@ -17590,13 +17599,13 @@
         <v>81.2</v>
       </c>
       <c r="T54" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U54" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="V54" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="W54">
         <v>0.6667</v>
@@ -17665,7 +17674,7 @@
         <v>6.5</v>
       </c>
       <c r="AS54" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AT54">
         <v>89.7</v>
@@ -17713,7 +17722,7 @@
         <v>1.1072</v>
       </c>
       <c r="BI54" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ54">
         <v>3121</v>
@@ -17761,13 +17770,13 @@
         <v>16.3</v>
       </c>
       <c r="BY54" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ54">
         <v>20.3</v>
       </c>
       <c r="CA54" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="CB54">
         <v>90</v>
@@ -17796,25 +17805,25 @@
         <v>131</v>
       </c>
       <c r="E55" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F55" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G55" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H55" t="s">
         <v>203</v>
       </c>
       <c r="I55" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="J55">
-        <v>345.6</v>
+        <v>358.6</v>
       </c>
       <c r="K55">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="L55">
         <v>5</v>
@@ -17841,13 +17850,13 @@
         <v>25</v>
       </c>
       <c r="T55" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U55" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="V55" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="W55">
         <v>0.6667</v>
@@ -17964,7 +17973,7 @@
         <v>1.1089</v>
       </c>
       <c r="BI55" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ55">
         <v>3058</v>
@@ -18012,13 +18021,13 @@
         <v>15.8</v>
       </c>
       <c r="BY55" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ55">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="CA55" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="CB55">
         <v>89</v>
@@ -18047,25 +18056,25 @@
         <v>131</v>
       </c>
       <c r="E56" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F56" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G56" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H56" t="s">
         <v>203</v>
       </c>
       <c r="I56" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="J56">
-        <v>345.6</v>
+        <v>358.6</v>
       </c>
       <c r="K56">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="L56">
         <v>5</v>
@@ -18092,13 +18101,13 @@
         <v>25</v>
       </c>
       <c r="T56" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U56" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="V56" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="W56">
         <v>0.6667</v>
@@ -18215,7 +18224,7 @@
         <v>1.1111</v>
       </c>
       <c r="BI56" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ56">
         <v>2992</v>
@@ -18263,13 +18272,13 @@
         <v>14.7</v>
       </c>
       <c r="BY56" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ56">
         <v>21.9</v>
       </c>
       <c r="CA56" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="CB56">
         <v>88</v>
@@ -18298,25 +18307,25 @@
         <v>131</v>
       </c>
       <c r="E57" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F57" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G57" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H57" t="s">
         <v>203</v>
       </c>
       <c r="I57" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="J57">
-        <v>345.6</v>
+        <v>358.6</v>
       </c>
       <c r="K57">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="L57">
         <v>5</v>
@@ -18343,13 +18352,13 @@
         <v>25</v>
       </c>
       <c r="T57" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U57" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="V57" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="W57">
         <v>0.6667</v>
@@ -18466,7 +18475,7 @@
         <v>1.1131</v>
       </c>
       <c r="BI57" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="BJ57">
         <v>2928</v>
@@ -18514,13 +18523,13 @@
         <v>14.1</v>
       </c>
       <c r="BY57" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ57">
         <v>21.2</v>
       </c>
       <c r="CA57" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="CB57">
         <v>87</v>
@@ -18549,25 +18558,25 @@
         <v>132</v>
       </c>
       <c r="E58" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F58" t="s">
         <v>118</v>
       </c>
       <c r="G58" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H58" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I58" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J58">
-        <v>463.8</v>
+        <v>476.8</v>
       </c>
       <c r="K58">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="L58">
         <v>5</v>
@@ -18594,13 +18603,13 @@
         <v>56.2</v>
       </c>
       <c r="T58" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U58" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="V58" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="W58">
         <v>0.1667</v>
@@ -18717,7 +18726,7 @@
         <v>1.1875</v>
       </c>
       <c r="BI58" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ58">
         <v>885</v>
@@ -18765,13 +18774,13 @@
         <v>0.2</v>
       </c>
       <c r="BY58" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ58">
         <v>16.9</v>
       </c>
       <c r="CA58" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB58">
         <v>75</v>
@@ -18800,25 +18809,25 @@
         <v>132</v>
       </c>
       <c r="E59" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F59" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G59" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I59" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J59">
-        <v>463.8</v>
+        <v>476.8</v>
       </c>
       <c r="K59">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="L59">
         <v>5</v>
@@ -18845,13 +18854,13 @@
         <v>56.2</v>
       </c>
       <c r="T59" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U59" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="V59" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="W59">
         <v>0.1667</v>
@@ -18920,7 +18929,7 @@
         <v>9.4</v>
       </c>
       <c r="AS59" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AT59">
         <v>325.1</v>
@@ -18968,7 +18977,7 @@
         <v>1.1931</v>
       </c>
       <c r="BI59" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ59">
         <v>720</v>
@@ -19016,13 +19025,13 @@
         <v>0.2</v>
       </c>
       <c r="BY59" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ59">
         <v>18.1</v>
       </c>
       <c r="CA59" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="CB59">
         <v>73</v>
@@ -19051,25 +19060,25 @@
         <v>132</v>
       </c>
       <c r="E60" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F60" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G60" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H60" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I60" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J60">
-        <v>463.8</v>
+        <v>476.8</v>
       </c>
       <c r="K60">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="L60">
         <v>5</v>
@@ -19096,13 +19105,13 @@
         <v>56.2</v>
       </c>
       <c r="T60" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U60" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="V60" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="W60">
         <v>0.1667</v>
@@ -19171,7 +19180,7 @@
         <v>8.6</v>
       </c>
       <c r="AS60" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AT60">
         <v>332.6</v>
@@ -19219,7 +19228,7 @@
         <v>1.2008</v>
       </c>
       <c r="BI60" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ60">
         <v>497</v>
@@ -19267,13 +19276,13 @@
         <v>0.2</v>
       </c>
       <c r="BY60" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ60">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="CA60" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB60">
         <v>69</v>
@@ -19302,25 +19311,25 @@
         <v>132</v>
       </c>
       <c r="E61" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F61" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G61" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H61" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I61" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J61">
-        <v>463.8</v>
+        <v>476.8</v>
       </c>
       <c r="K61">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="L61">
         <v>5</v>
@@ -19347,13 +19356,13 @@
         <v>56.2</v>
       </c>
       <c r="T61" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="U61" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="V61" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="W61">
         <v>0.1667</v>
@@ -19422,7 +19431,7 @@
         <v>6.8</v>
       </c>
       <c r="AS61" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AT61">
         <v>341.2</v>
@@ -19470,7 +19479,7 @@
         <v>1.2065</v>
       </c>
       <c r="BI61" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BJ61">
         <v>335</v>
@@ -19518,13 +19527,13 @@
         <v>0.2</v>
       </c>
       <c r="BY61" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ61">
         <v>12.9</v>
       </c>
       <c r="CA61" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB61">
         <v>66</v>
@@ -19670,7 +19679,7 @@
         <v>133</v>
       </c>
       <c r="P2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q2">
         <v>5</v>
@@ -19723,7 +19732,7 @@
         <v>133</v>
       </c>
       <c r="P3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -19776,7 +19785,7 @@
         <v>133</v>
       </c>
       <c r="P4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q4">
         <v>5</v>
@@ -19829,7 +19838,7 @@
         <v>133</v>
       </c>
       <c r="P5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q5">
         <v>5</v>
@@ -19882,7 +19891,7 @@
         <v>133</v>
       </c>
       <c r="P6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q6">
         <v>5</v>
@@ -19935,7 +19944,7 @@
         <v>133</v>
       </c>
       <c r="P7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -19961,7 +19970,7 @@
         <v>165</v>
       </c>
       <c r="G8">
-        <v>89.90000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H8">
         <v>6</v>
@@ -19982,13 +19991,13 @@
         <v>84.2</v>
       </c>
       <c r="N8">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="O8" t="s">
         <v>133</v>
       </c>
       <c r="P8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q8">
         <v>5</v>
@@ -20041,7 +20050,7 @@
         <v>133</v>
       </c>
       <c r="P9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q9">
         <v>5</v>
@@ -20094,7 +20103,7 @@
         <v>133</v>
       </c>
       <c r="P10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -20147,7 +20156,7 @@
         <v>133</v>
       </c>
       <c r="P11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -20200,7 +20209,7 @@
         <v>133</v>
       </c>
       <c r="P12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q12">
         <v>4</v>
@@ -20253,7 +20262,7 @@
         <v>133</v>
       </c>
       <c r="P13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q13">
         <v>5</v>
@@ -20306,7 +20315,7 @@
         <v>133</v>
       </c>
       <c r="P14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q14">
         <v>5</v>
@@ -20332,7 +20341,7 @@
         <v>165</v>
       </c>
       <c r="G15">
-        <v>80.8</v>
+        <v>82</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -20350,16 +20359,16 @@
         <v>182</v>
       </c>
       <c r="M15">
-        <v>84.7</v>
+        <v>85.2</v>
       </c>
       <c r="N15">
-        <v>1831</v>
+        <v>1850</v>
       </c>
       <c r="O15" t="s">
         <v>134</v>
       </c>
       <c r="P15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -20412,7 +20421,7 @@
         <v>134</v>
       </c>
       <c r="P16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q16">
         <v>5</v>

--- a/mlb_weather_professional_v4_1_2026_07_17.xlsx
+++ b/mlb_weather_professional_v4_1_2026_07_17.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1862" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1862" uniqueCount="369">
   <si>
     <t>Date</t>
   </si>
@@ -587,9 +587,6 @@
     <t>IMPROVING RAPIDLY</t>
   </si>
   <si>
-    <t>WORSENING</t>
-  </si>
-  <si>
     <t>LOW</t>
   </si>
   <si>
@@ -599,49 +596,43 @@
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>2026-07-16 10:55:03 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 10:55:05 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 10:55:06 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 10:55:08 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 10:55:09 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 10:55:14 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 10:55:16 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 10:55:17 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 10:55:18 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 10:55:19 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 10:55:20 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 10:55:22 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 10:55:23 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 10:55:24 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 10:55:26 PM PDT</t>
+    <t>2026-07-16 11:19:57 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:19:58 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:19:59 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:20:00 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:20:04 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:20:09 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:20:10 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:20:11 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:20:12 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:20:13 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:20:14 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:20:15 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:20:16 PM PDT</t>
   </si>
   <si>
     <t>Period</t>
@@ -986,49 +977,43 @@
     <t>10:10 PM PDT</t>
   </si>
   <si>
-    <t>2026-07-17 05:55:03 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 05:55:05 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 05:55:06 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 05:55:08 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 05:55:09 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 05:55:14 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 05:55:16 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 05:55:17 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 05:55:18 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 05:55:19 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 05:55:20 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 05:55:22 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 05:55:23 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 05:55:24 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 05:55:26 UTC</t>
+    <t>2026-07-17 06:19:57 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:19:58 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:19:59 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:20:00 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:20:04 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:20:09 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:20:10 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:20:11 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:20:12 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:20:13 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:20:14 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:20:15 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:20:16 UTC</t>
   </si>
   <si>
     <t>2026-07-17T05:23:49+00:00</t>
@@ -1881,7 +1866,7 @@
         <v>2.2</v>
       </c>
       <c r="AC2">
-        <v>91.2</v>
+        <v>91.3</v>
       </c>
       <c r="AD2" t="s">
         <v>182</v>
@@ -1935,22 +1920,22 @@
         <v>0</v>
       </c>
       <c r="AU2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AV2">
         <v>0</v>
       </c>
       <c r="AW2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX2">
         <v>7.1</v>
       </c>
       <c r="AY2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AZ2">
-        <v>31.2</v>
+        <v>56.1</v>
       </c>
       <c r="BA2">
         <v>5</v>
@@ -2093,22 +2078,22 @@
         <v>0</v>
       </c>
       <c r="AU3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AV3">
         <v>0.2</v>
       </c>
       <c r="AW3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX3">
         <v>7.6</v>
       </c>
       <c r="AY3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AZ3">
-        <v>433.7</v>
+        <v>458.6</v>
       </c>
       <c r="BA3">
         <v>5</v>
@@ -2242,7 +2227,7 @@
         <v>185</v>
       </c>
       <c r="AR4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AS4">
         <v>0</v>
@@ -2251,22 +2236,22 @@
         <v>0</v>
       </c>
       <c r="AU4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AV4">
         <v>0.9</v>
       </c>
       <c r="AW4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX4">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AZ4">
-        <v>31.3</v>
+        <v>56.2</v>
       </c>
       <c r="BA4">
         <v>5</v>
@@ -2355,7 +2340,7 @@
         <v>2.4</v>
       </c>
       <c r="AC5">
-        <v>93.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="AD5" t="s">
         <v>182</v>
@@ -2409,22 +2394,22 @@
         <v>0</v>
       </c>
       <c r="AU5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AV5">
         <v>13.7</v>
       </c>
       <c r="AW5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX5">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="AY5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AZ5">
-        <v>578.5</v>
+        <v>603.3</v>
       </c>
       <c r="BA5">
         <v>5</v>
@@ -2492,7 +2477,7 @@
         <v>164</v>
       </c>
       <c r="V6">
-        <v>34.8</v>
+        <v>35.2</v>
       </c>
       <c r="W6">
         <v>63.3</v>
@@ -2513,7 +2498,7 @@
         <v>4</v>
       </c>
       <c r="AC6">
-        <v>87.5</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="AD6" t="s">
         <v>183</v>
@@ -2567,22 +2552,22 @@
         <v>0</v>
       </c>
       <c r="AU6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AV6">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="AW6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX6">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="AY6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AZ6">
-        <v>78.09999999999999</v>
+        <v>103.1</v>
       </c>
       <c r="BA6">
         <v>5</v>
@@ -2716,7 +2701,7 @@
         <v>186</v>
       </c>
       <c r="AR7">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AS7">
         <v>0</v>
@@ -2725,19 +2710,19 @@
         <v>0</v>
       </c>
       <c r="AU7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AV7">
         <v>3.7</v>
       </c>
       <c r="AW7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX7">
         <v>1.7</v>
       </c>
       <c r="AY7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AZ7">
         <v>0</v>
@@ -2883,22 +2868,22 @@
         <v>0</v>
       </c>
       <c r="AU8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AV8">
         <v>28.3</v>
       </c>
       <c r="AW8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX8">
         <v>13</v>
       </c>
       <c r="AY8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AZ8">
-        <v>23.4</v>
+        <v>48.3</v>
       </c>
       <c r="BA8">
         <v>5</v>
@@ -2966,7 +2951,7 @@
         <v>164</v>
       </c>
       <c r="V9">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="W9">
         <v>66.3</v>
@@ -2987,7 +2972,7 @@
         <v>4.9</v>
       </c>
       <c r="AC9">
-        <v>83.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="AD9" t="s">
         <v>183</v>
@@ -3041,22 +3026,22 @@
         <v>0</v>
       </c>
       <c r="AU9" t="s">
+        <v>189</v>
+      </c>
+      <c r="AV9">
+        <v>29.5</v>
+      </c>
+      <c r="AW9" t="s">
         <v>190</v>
       </c>
-      <c r="AV9">
-        <v>29.6</v>
-      </c>
-      <c r="AW9" t="s">
-        <v>191</v>
-      </c>
       <c r="AX9">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AY9" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AZ9">
-        <v>153.9</v>
+        <v>178.8</v>
       </c>
       <c r="BA9">
         <v>5</v>
@@ -3199,22 +3184,22 @@
         <v>0</v>
       </c>
       <c r="AU10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AV10">
         <v>12.9</v>
       </c>
       <c r="AW10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX10">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="AY10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AZ10">
-        <v>128.9</v>
+        <v>153.8</v>
       </c>
       <c r="BA10">
         <v>5</v>
@@ -3282,7 +3267,7 @@
         <v>164</v>
       </c>
       <c r="V11">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="W11">
         <v>67.90000000000001</v>
@@ -3357,22 +3342,22 @@
         <v>0</v>
       </c>
       <c r="AU11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AV11">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="AW11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX11">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="AY11" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AZ11">
-        <v>103.1</v>
+        <v>128</v>
       </c>
       <c r="BA11">
         <v>5</v>
@@ -3515,22 +3500,22 @@
         <v>0</v>
       </c>
       <c r="AU12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AV12">
         <v>1.8</v>
       </c>
       <c r="AW12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX12">
         <v>8.5</v>
       </c>
       <c r="AY12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="AZ12">
-        <v>668.9</v>
+        <v>693.8</v>
       </c>
       <c r="BA12">
         <v>5</v>
@@ -3673,22 +3658,22 @@
         <v>0</v>
       </c>
       <c r="AU13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AV13">
         <v>1.3</v>
       </c>
       <c r="AW13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX13">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="AY13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AZ13">
-        <v>129</v>
+        <v>153.9</v>
       </c>
       <c r="BA13">
         <v>5</v>
@@ -3822,7 +3807,7 @@
         <v>187</v>
       </c>
       <c r="AR14">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="AS14">
         <v>0</v>
@@ -3831,22 +3816,22 @@
         <v>0</v>
       </c>
       <c r="AU14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AV14">
         <v>0</v>
       </c>
       <c r="AW14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AX14">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="AY14" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AZ14">
-        <v>534.5</v>
+        <v>559.3</v>
       </c>
       <c r="BA14">
         <v>5</v>
@@ -3977,34 +3962,34 @@
         <v>69.7</v>
       </c>
       <c r="AQ15" t="s">
+        <v>187</v>
+      </c>
+      <c r="AR15">
+        <v>7.6</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="s">
         <v>188</v>
       </c>
-      <c r="AR15">
-        <v>-3.2</v>
-      </c>
-      <c r="AS15">
-        <v>0</v>
-      </c>
-      <c r="AT15">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="s">
-        <v>189</v>
-      </c>
       <c r="AV15">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="AW15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AX15">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AY15" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AZ15">
-        <v>62.1</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="BA15">
         <v>5</v>
@@ -4093,7 +4078,7 @@
         <v>0.6</v>
       </c>
       <c r="AC16">
-        <v>87.5</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="AD16" t="s">
         <v>182</v>
@@ -4147,22 +4132,22 @@
         <v>0</v>
       </c>
       <c r="AU16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AV16">
         <v>0.2</v>
       </c>
       <c r="AW16" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AX16">
         <v>18</v>
       </c>
       <c r="AY16" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="AZ16">
-        <v>540.2</v>
+        <v>565</v>
       </c>
       <c r="BA16">
         <v>5</v>
@@ -4287,223 +4272,223 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>52</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="BW1" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="BX1" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="BY1" s="1" t="s">
-        <v>276</v>
       </c>
       <c r="BZ1" s="1" t="s">
         <v>49</v>
@@ -4512,16 +4497,16 @@
         <v>48</v>
       </c>
       <c r="CB1" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="CC1" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="CE1" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="CC1" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="CD1" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="CE1" s="1" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:83">
@@ -4538,25 +4523,25 @@
         <v>119</v>
       </c>
       <c r="E2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F2" t="s">
         <v>107</v>
       </c>
       <c r="G2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="H2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="J2">
-        <v>31.2</v>
+        <v>56.1</v>
       </c>
       <c r="K2">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
       <c r="L2">
         <v>5</v>
@@ -4583,13 +4568,13 @@
         <v>0</v>
       </c>
       <c r="T2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U2" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="V2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="W2">
         <v>0.5833</v>
@@ -4706,7 +4691,7 @@
         <v>1.1662</v>
       </c>
       <c r="BI2" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ2">
         <v>1591</v>
@@ -4754,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="BY2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ2">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="CA2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB2">
         <v>82</v>
@@ -4789,25 +4774,25 @@
         <v>119</v>
       </c>
       <c r="E3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F3" t="s">
         <v>282</v>
       </c>
-      <c r="F3" t="s">
-        <v>285</v>
-      </c>
       <c r="G3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="H3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="J3">
-        <v>31.2</v>
+        <v>56.1</v>
       </c>
       <c r="K3">
-        <v>12.7</v>
+        <v>12.3</v>
       </c>
       <c r="L3">
         <v>5</v>
@@ -4834,13 +4819,13 @@
         <v>0</v>
       </c>
       <c r="T3" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U3" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="V3" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="W3">
         <v>0.5833</v>
@@ -4849,7 +4834,7 @@
         <v>14.8</v>
       </c>
       <c r="Y3">
-        <v>91</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Z3">
         <v>60.1</v>
@@ -4957,7 +4942,7 @@
         <v>1.1636</v>
       </c>
       <c r="BI3" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ3">
         <v>1670</v>
@@ -5005,13 +4990,13 @@
         <v>0</v>
       </c>
       <c r="BY3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ3">
         <v>4.2</v>
       </c>
       <c r="CA3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB3">
         <v>83</v>
@@ -5040,25 +5025,25 @@
         <v>119</v>
       </c>
       <c r="E4" t="s">
+        <v>280</v>
+      </c>
+      <c r="F4" t="s">
         <v>283</v>
       </c>
-      <c r="F4" t="s">
-        <v>286</v>
-      </c>
       <c r="G4" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="H4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I4" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="J4">
-        <v>31.2</v>
+        <v>56.1</v>
       </c>
       <c r="K4">
-        <v>13.7</v>
+        <v>13.3</v>
       </c>
       <c r="L4">
         <v>5</v>
@@ -5085,13 +5070,13 @@
         <v>0</v>
       </c>
       <c r="T4" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U4" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="V4" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="W4">
         <v>0.5833</v>
@@ -5100,7 +5085,7 @@
         <v>13.9</v>
       </c>
       <c r="Y4">
-        <v>91.5</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="Z4">
         <v>60</v>
@@ -5208,7 +5193,7 @@
         <v>1.1617</v>
       </c>
       <c r="BI4" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ4">
         <v>1732</v>
@@ -5256,13 +5241,13 @@
         <v>0</v>
       </c>
       <c r="BY4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ4">
         <v>4</v>
       </c>
       <c r="CA4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB4">
         <v>84</v>
@@ -5291,25 +5276,25 @@
         <v>119</v>
       </c>
       <c r="E5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F5" t="s">
         <v>284</v>
       </c>
-      <c r="F5" t="s">
-        <v>287</v>
-      </c>
       <c r="G5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="H5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I5" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="J5">
-        <v>31.2</v>
+        <v>56.1</v>
       </c>
       <c r="K5">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -5336,13 +5321,13 @@
         <v>0</v>
       </c>
       <c r="T5" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U5" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="V5" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="W5">
         <v>0.5833</v>
@@ -5459,7 +5444,7 @@
         <v>1.1622</v>
       </c>
       <c r="BI5" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ5">
         <v>1715</v>
@@ -5507,13 +5492,13 @@
         <v>0</v>
       </c>
       <c r="BY5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ5">
         <v>7.1</v>
       </c>
       <c r="CA5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB5">
         <v>83</v>
@@ -5542,25 +5527,25 @@
         <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F6" t="s">
         <v>108</v>
       </c>
       <c r="G6" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I6" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="J6">
-        <v>433.7</v>
+        <v>458.6</v>
       </c>
       <c r="K6">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -5587,13 +5572,13 @@
         <v>0</v>
       </c>
       <c r="T6" t="s">
+        <v>344</v>
+      </c>
+      <c r="U6" t="s">
         <v>349</v>
       </c>
-      <c r="U6" t="s">
-        <v>354</v>
-      </c>
       <c r="V6" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="W6">
         <v>0.0833</v>
@@ -5710,7 +5695,7 @@
         <v>1.156</v>
       </c>
       <c r="BI6" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ6">
         <v>1880</v>
@@ -5758,13 +5743,13 @@
         <v>0.2</v>
       </c>
       <c r="BY6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ6">
         <v>4.2</v>
       </c>
       <c r="CA6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB6">
         <v>87</v>
@@ -5793,25 +5778,25 @@
         <v>120</v>
       </c>
       <c r="E7" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F7" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G7" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I7" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="J7">
-        <v>433.7</v>
+        <v>458.6</v>
       </c>
       <c r="K7">
-        <v>18.2</v>
+        <v>17.8</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -5838,13 +5823,13 @@
         <v>56.2</v>
       </c>
       <c r="T7" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U7" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="V7" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="W7">
         <v>0.0833</v>
@@ -5961,7 +5946,7 @@
         <v>1.1612</v>
       </c>
       <c r="BI7" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ7">
         <v>1705</v>
@@ -6009,13 +5994,13 @@
         <v>0.2</v>
       </c>
       <c r="BY7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ7">
         <v>7.6</v>
       </c>
       <c r="CA7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB7">
         <v>84</v>
@@ -6044,25 +6029,25 @@
         <v>120</v>
       </c>
       <c r="E8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F8" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="G8" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I8" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="J8">
-        <v>433.7</v>
+        <v>458.6</v>
       </c>
       <c r="K8">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
       <c r="L8">
         <v>5</v>
@@ -6089,13 +6074,13 @@
         <v>75</v>
       </c>
       <c r="T8" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U8" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="V8" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="W8">
         <v>0.0833</v>
@@ -6104,7 +6089,7 @@
         <v>15.2</v>
       </c>
       <c r="Y8">
-        <v>90.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="Z8">
         <v>49.5</v>
@@ -6212,7 +6197,7 @@
         <v>1.169</v>
       </c>
       <c r="BI8" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ8">
         <v>1415</v>
@@ -6260,13 +6245,13 @@
         <v>0.2</v>
       </c>
       <c r="BY8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ8">
         <v>4.6</v>
       </c>
       <c r="CA8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB8">
         <v>80</v>
@@ -6295,25 +6280,25 @@
         <v>120</v>
       </c>
       <c r="E9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F9" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G9" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I9" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="J9">
-        <v>433.7</v>
+        <v>458.6</v>
       </c>
       <c r="K9">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="L9">
         <v>5</v>
@@ -6340,13 +6325,13 @@
         <v>100</v>
       </c>
       <c r="T9" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U9" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="V9" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="W9">
         <v>0.0833</v>
@@ -6415,7 +6400,7 @@
         <v>9.4</v>
       </c>
       <c r="AS9" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="AT9">
         <v>150.3</v>
@@ -6463,7 +6448,7 @@
         <v>1.1726</v>
       </c>
       <c r="BI9" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ9">
         <v>1288</v>
@@ -6511,13 +6496,13 @@
         <v>0.2</v>
       </c>
       <c r="BY9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ9">
         <v>6.4</v>
       </c>
       <c r="CA9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB9">
         <v>79</v>
@@ -6546,25 +6531,25 @@
         <v>119</v>
       </c>
       <c r="E10" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F10" t="s">
         <v>109</v>
       </c>
       <c r="G10" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I10" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="J10">
-        <v>31.3</v>
+        <v>56.2</v>
       </c>
       <c r="K10">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="L10">
         <v>5</v>
@@ -6591,13 +6576,13 @@
         <v>25</v>
       </c>
       <c r="T10" t="s">
+        <v>344</v>
+      </c>
+      <c r="U10" t="s">
         <v>349</v>
       </c>
-      <c r="U10" t="s">
-        <v>354</v>
-      </c>
       <c r="V10" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="W10">
         <v>0.1667</v>
@@ -6714,7 +6699,7 @@
         <v>1.1691</v>
       </c>
       <c r="BI10" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ10">
         <v>1505</v>
@@ -6762,13 +6747,13 @@
         <v>0</v>
       </c>
       <c r="BY10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ10">
         <v>7.5</v>
       </c>
       <c r="CA10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB10">
         <v>80</v>
@@ -6797,25 +6782,25 @@
         <v>119</v>
       </c>
       <c r="E11" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G11" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I11" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="J11">
-        <v>31.3</v>
+        <v>56.2</v>
       </c>
       <c r="K11">
-        <v>18.2</v>
+        <v>17.8</v>
       </c>
       <c r="L11">
         <v>5</v>
@@ -6842,13 +6827,13 @@
         <v>81.2</v>
       </c>
       <c r="T11" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U11" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="V11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="W11">
         <v>0.1667</v>
@@ -6917,7 +6902,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="AS11" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="AT11">
         <v>316.6</v>
@@ -6965,7 +6950,7 @@
         <v>1.1773</v>
       </c>
       <c r="BI11" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ11">
         <v>1247</v>
@@ -7013,13 +6998,13 @@
         <v>0</v>
       </c>
       <c r="BY11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ11">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CA11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB11">
         <v>76</v>
@@ -7048,25 +7033,25 @@
         <v>119</v>
       </c>
       <c r="E12" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F12" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="G12" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I12" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="J12">
-        <v>31.3</v>
+        <v>56.2</v>
       </c>
       <c r="K12">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
       <c r="L12">
         <v>5</v>
@@ -7093,13 +7078,13 @@
         <v>81.2</v>
       </c>
       <c r="T12" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U12" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="V12" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="W12">
         <v>0.1667</v>
@@ -7168,7 +7153,7 @@
         <v>7.4</v>
       </c>
       <c r="AS12" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="AT12">
         <v>18.5</v>
@@ -7216,7 +7201,7 @@
         <v>1.1842</v>
       </c>
       <c r="BI12" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ12">
         <v>1021</v>
@@ -7264,13 +7249,13 @@
         <v>0.4</v>
       </c>
       <c r="BY12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ12">
         <v>4.9</v>
       </c>
       <c r="CA12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB12">
         <v>74</v>
@@ -7299,25 +7284,25 @@
         <v>119</v>
       </c>
       <c r="E13" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F13" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="G13" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I13" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="J13">
-        <v>31.3</v>
+        <v>56.2</v>
       </c>
       <c r="K13">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="L13">
         <v>5</v>
@@ -7344,13 +7329,13 @@
         <v>81.2</v>
       </c>
       <c r="T13" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U13" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="V13" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="W13">
         <v>0.1667</v>
@@ -7467,7 +7452,7 @@
         <v>1.1892</v>
       </c>
       <c r="BI13" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ13">
         <v>873</v>
@@ -7515,13 +7500,13 @@
         <v>0.9</v>
       </c>
       <c r="BY13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ13">
         <v>4.2</v>
       </c>
       <c r="CA13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB13">
         <v>72</v>
@@ -7550,25 +7535,25 @@
         <v>121</v>
       </c>
       <c r="E14" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F14" t="s">
         <v>109</v>
       </c>
       <c r="G14" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I14" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="J14">
-        <v>578.5</v>
+        <v>603.3</v>
       </c>
       <c r="K14">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="L14">
         <v>5</v>
@@ -7595,13 +7580,13 @@
         <v>56.2</v>
       </c>
       <c r="T14" t="s">
+        <v>344</v>
+      </c>
+      <c r="U14" t="s">
         <v>349</v>
       </c>
-      <c r="U14" t="s">
-        <v>354</v>
-      </c>
       <c r="V14" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="W14">
         <v>0.1667</v>
@@ -7610,7 +7595,7 @@
         <v>6.8</v>
       </c>
       <c r="Y14">
-        <v>95.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="Z14">
         <v>53.4</v>
@@ -7718,7 +7703,7 @@
         <v>1.1393</v>
       </c>
       <c r="BI14" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ14">
         <v>2273</v>
@@ -7766,13 +7751,13 @@
         <v>3.9</v>
       </c>
       <c r="BY14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ14">
         <v>2.9</v>
       </c>
       <c r="CA14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB14">
         <v>85</v>
@@ -7801,25 +7786,25 @@
         <v>121</v>
       </c>
       <c r="E15" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F15" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G15" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I15" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="J15">
-        <v>578.5</v>
+        <v>603.3</v>
       </c>
       <c r="K15">
-        <v>18.2</v>
+        <v>17.8</v>
       </c>
       <c r="L15">
         <v>5</v>
@@ -7846,13 +7831,13 @@
         <v>56.2</v>
       </c>
       <c r="T15" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U15" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="V15" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="W15">
         <v>0.1667</v>
@@ -7969,7 +7954,7 @@
         <v>1.1418</v>
       </c>
       <c r="BI15" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ15">
         <v>2187</v>
@@ -8017,13 +8002,13 @@
         <v>13.7</v>
       </c>
       <c r="BY15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ15">
         <v>5.9</v>
       </c>
       <c r="CA15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB15">
         <v>83</v>
@@ -8052,25 +8037,25 @@
         <v>121</v>
       </c>
       <c r="E16" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F16" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="G16" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H16" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I16" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="J16">
-        <v>578.5</v>
+        <v>603.3</v>
       </c>
       <c r="K16">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
       <c r="L16">
         <v>5</v>
@@ -8097,13 +8082,13 @@
         <v>56.2</v>
       </c>
       <c r="T16" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U16" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="V16" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="W16">
         <v>0.1667</v>
@@ -8172,7 +8157,7 @@
         <v>6</v>
       </c>
       <c r="AS16" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="AT16">
         <v>133.6</v>
@@ -8220,7 +8205,7 @@
         <v>1.1467</v>
       </c>
       <c r="BI16" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ16">
         <v>2033</v>
@@ -8268,13 +8253,13 @@
         <v>11.6</v>
       </c>
       <c r="BY16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ16">
         <v>7.9</v>
       </c>
       <c r="CA16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB16">
         <v>80</v>
@@ -8303,25 +8288,25 @@
         <v>121</v>
       </c>
       <c r="E17" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F17" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="G17" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H17" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I17" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="J17">
-        <v>578.5</v>
+        <v>603.3</v>
       </c>
       <c r="K17">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="L17">
         <v>5</v>
@@ -8348,13 +8333,13 @@
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U17" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="V17" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="W17">
         <v>0.1667</v>
@@ -8471,7 +8456,7 @@
         <v>1.1488</v>
       </c>
       <c r="BI17" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ17">
         <v>1977</v>
@@ -8519,13 +8504,13 @@
         <v>2.5</v>
       </c>
       <c r="BY17" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ17">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="CA17" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB17">
         <v>79</v>
@@ -8554,25 +8539,25 @@
         <v>122</v>
       </c>
       <c r="E18" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F18" t="s">
         <v>110</v>
       </c>
       <c r="G18" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I18" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="J18">
-        <v>78.09999999999999</v>
+        <v>103.1</v>
       </c>
       <c r="K18">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
       <c r="L18">
         <v>5</v>
@@ -8584,7 +8569,7 @@
         <v>0.47</v>
       </c>
       <c r="O18">
-        <v>26.64</v>
+        <v>26.13</v>
       </c>
       <c r="P18">
         <v>6.6</v>
@@ -8599,22 +8584,22 @@
         <v>0</v>
       </c>
       <c r="T18" t="s">
+        <v>344</v>
+      </c>
+      <c r="U18" t="s">
         <v>349</v>
       </c>
-      <c r="U18" t="s">
-        <v>354</v>
-      </c>
       <c r="V18" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="W18">
         <v>0.25</v>
       </c>
       <c r="X18">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="Y18">
-        <v>84.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="Z18">
         <v>65.09999999999999</v>
@@ -8656,7 +8641,7 @@
         <v>95.8</v>
       </c>
       <c r="AM18">
-        <v>34.8</v>
+        <v>35.2</v>
       </c>
       <c r="AN18">
         <v>0.02</v>
@@ -8722,7 +8707,7 @@
         <v>1.123</v>
       </c>
       <c r="BI18" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ18">
         <v>2642</v>
@@ -8767,16 +8752,16 @@
         <v>52.4</v>
       </c>
       <c r="BX18">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="BY18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BZ18">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="CA18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB18">
         <v>84</v>
@@ -8805,25 +8790,25 @@
         <v>122</v>
       </c>
       <c r="E19" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F19" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G19" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I19" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="J19">
-        <v>78.09999999999999</v>
+        <v>103.1</v>
       </c>
       <c r="K19">
-        <v>18.3</v>
+        <v>17.9</v>
       </c>
       <c r="L19">
         <v>5</v>
@@ -8835,7 +8820,7 @@
         <v>0.44</v>
       </c>
       <c r="O19">
-        <v>24.25</v>
+        <v>24.41</v>
       </c>
       <c r="P19">
         <v>6.4</v>
@@ -8850,19 +8835,19 @@
         <v>0</v>
       </c>
       <c r="T19" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U19" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="V19" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="W19">
         <v>0.25</v>
       </c>
       <c r="X19">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="Y19">
         <v>89.3</v>
@@ -8907,7 +8892,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="AM19">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="AN19">
         <v>0.002</v>
@@ -8973,7 +8958,7 @@
         <v>1.1261</v>
       </c>
       <c r="BI19" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ19">
         <v>2547</v>
@@ -9018,16 +9003,16 @@
         <v>54.2</v>
       </c>
       <c r="BX19">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="BY19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BZ19">
         <v>2.7</v>
       </c>
       <c r="CA19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB19">
         <v>82</v>
@@ -9056,25 +9041,25 @@
         <v>122</v>
       </c>
       <c r="E20" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F20" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G20" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I20" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="J20">
-        <v>78.09999999999999</v>
+        <v>103.1</v>
       </c>
       <c r="K20">
-        <v>19.3</v>
+        <v>18.9</v>
       </c>
       <c r="L20">
         <v>5</v>
@@ -9086,7 +9071,7 @@
         <v>0.73</v>
       </c>
       <c r="O20">
-        <v>20.05</v>
+        <v>19.67</v>
       </c>
       <c r="P20">
         <v>3.9</v>
@@ -9101,22 +9086,22 @@
         <v>0</v>
       </c>
       <c r="T20" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U20" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="V20" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="W20">
         <v>0.25</v>
       </c>
       <c r="X20">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="Y20">
-        <v>89.59999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="Z20">
         <v>66.5</v>
@@ -9158,7 +9143,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="AM20">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
       <c r="AN20">
         <v>0</v>
@@ -9176,7 +9161,7 @@
         <v>14.4</v>
       </c>
       <c r="AS20" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="AT20">
         <v>305.7</v>
@@ -9224,7 +9209,7 @@
         <v>1.1303</v>
       </c>
       <c r="BI20" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ20">
         <v>2417</v>
@@ -9269,16 +9254,16 @@
         <v>56.8</v>
       </c>
       <c r="BX20">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="BY20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ20">
         <v>3.5</v>
       </c>
       <c r="CA20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB20">
         <v>80</v>
@@ -9307,25 +9292,25 @@
         <v>122</v>
       </c>
       <c r="E21" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F21" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G21" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H21" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I21" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="J21">
-        <v>78.09999999999999</v>
+        <v>103.1</v>
       </c>
       <c r="K21">
-        <v>20.3</v>
+        <v>19.9</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -9337,7 +9322,7 @@
         <v>1.01</v>
       </c>
       <c r="O21">
-        <v>11.84</v>
+        <v>11.29</v>
       </c>
       <c r="P21">
         <v>2.3</v>
@@ -9352,22 +9337,22 @@
         <v>0</v>
       </c>
       <c r="T21" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U21" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="V21" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="W21">
         <v>0.25</v>
       </c>
       <c r="X21">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="Y21">
-        <v>91.7</v>
+        <v>91.8</v>
       </c>
       <c r="Z21">
         <v>66.3</v>
@@ -9409,7 +9394,7 @@
         <v>94</v>
       </c>
       <c r="AM21">
-        <v>9.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="AN21">
         <v>0</v>
@@ -9427,7 +9412,7 @@
         <v>12.1</v>
       </c>
       <c r="AS21" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="AT21">
         <v>307.5</v>
@@ -9475,7 +9460,7 @@
         <v>1.1347</v>
       </c>
       <c r="BI21" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ21">
         <v>2283</v>
@@ -9520,16 +9505,16 @@
         <v>59</v>
       </c>
       <c r="BX21">
-        <v>17.1</v>
+        <v>17.6</v>
       </c>
       <c r="BY21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ21">
         <v>2.6</v>
       </c>
       <c r="CA21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB21">
         <v>78</v>
@@ -9558,22 +9543,22 @@
         <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F22" t="s">
         <v>110</v>
       </c>
       <c r="G22" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H22" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
       <c r="L22">
         <v>4</v>
@@ -9600,13 +9585,13 @@
         <v>0</v>
       </c>
       <c r="T22" t="s">
+        <v>344</v>
+      </c>
+      <c r="U22" t="s">
         <v>349</v>
       </c>
-      <c r="U22" t="s">
-        <v>354</v>
-      </c>
       <c r="V22" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="W22">
         <v>0.25</v>
@@ -9723,7 +9708,7 @@
         <v>1.171</v>
       </c>
       <c r="BI22" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ22">
         <v>1338</v>
@@ -9771,13 +9756,13 @@
         <v>1.2</v>
       </c>
       <c r="BY22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ22">
         <v>1.4</v>
       </c>
       <c r="CA22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CC22">
         <v>74.59999999999999</v>
@@ -9803,22 +9788,22 @@
         <v>123</v>
       </c>
       <c r="E23" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F23" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G23" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H23" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23">
-        <v>18.3</v>
+        <v>17.9</v>
       </c>
       <c r="L23">
         <v>4</v>
@@ -9845,13 +9830,13 @@
         <v>56.2</v>
       </c>
       <c r="T23" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U23" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="V23" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="W23">
         <v>0.25</v>
@@ -9968,7 +9953,7 @@
         <v>1.1724</v>
       </c>
       <c r="BI23" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ23">
         <v>1295</v>
@@ -10016,13 +10001,13 @@
         <v>1.7</v>
       </c>
       <c r="BY23" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ23">
         <v>1.5</v>
       </c>
       <c r="CA23" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CC23">
         <v>73.8</v>
@@ -10048,22 +10033,22 @@
         <v>123</v>
       </c>
       <c r="E24" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F24" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G24" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H24" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>19.3</v>
+        <v>18.9</v>
       </c>
       <c r="L24">
         <v>4</v>
@@ -10090,13 +10075,13 @@
         <v>56.2</v>
       </c>
       <c r="T24" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U24" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="V24" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="W24">
         <v>0.25</v>
@@ -10213,7 +10198,7 @@
         <v>1.1749</v>
       </c>
       <c r="BI24" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ24">
         <v>1218</v>
@@ -10261,13 +10246,13 @@
         <v>2.5</v>
       </c>
       <c r="BY24" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ24">
         <v>1.6</v>
       </c>
       <c r="CA24" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CC24">
         <v>72.59999999999999</v>
@@ -10293,22 +10278,22 @@
         <v>123</v>
       </c>
       <c r="E25" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F25" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G25" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H25" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
-        <v>20.3</v>
+        <v>19.9</v>
       </c>
       <c r="L25">
         <v>4</v>
@@ -10335,13 +10320,13 @@
         <v>56.2</v>
       </c>
       <c r="T25" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U25" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="V25" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="W25">
         <v>0.25</v>
@@ -10350,7 +10335,7 @@
         <v>16.5</v>
       </c>
       <c r="Y25">
-        <v>91.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="Z25">
         <v>54.8</v>
@@ -10458,7 +10443,7 @@
         <v>1.1748</v>
       </c>
       <c r="BI25" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ25">
         <v>1226</v>
@@ -10506,13 +10491,13 @@
         <v>3.7</v>
       </c>
       <c r="BY25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ25">
         <v>1.7</v>
       </c>
       <c r="CA25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CC25">
         <v>72.59999999999999</v>
@@ -10538,25 +10523,25 @@
         <v>124</v>
       </c>
       <c r="E26" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F26" t="s">
         <v>111</v>
       </c>
       <c r="G26" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="H26" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I26" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="J26">
-        <v>23.4</v>
+        <v>48.3</v>
       </c>
       <c r="K26">
-        <v>17.7</v>
+        <v>17.3</v>
       </c>
       <c r="L26">
         <v>5</v>
@@ -10583,13 +10568,13 @@
         <v>100</v>
       </c>
       <c r="T26" t="s">
+        <v>344</v>
+      </c>
+      <c r="U26" t="s">
+        <v>353</v>
+      </c>
+      <c r="V26" t="s">
         <v>349</v>
-      </c>
-      <c r="U26" t="s">
-        <v>358</v>
-      </c>
-      <c r="V26" t="s">
-        <v>354</v>
       </c>
       <c r="W26">
         <v>0.6667</v>
@@ -10598,7 +10583,7 @@
         <v>26.1</v>
       </c>
       <c r="Y26">
-        <v>85.2</v>
+        <v>85.3</v>
       </c>
       <c r="Z26">
         <v>53.3</v>
@@ -10706,7 +10691,7 @@
         <v>1.1896</v>
       </c>
       <c r="BI26" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ26">
         <v>858</v>
@@ -10754,13 +10739,13 @@
         <v>0</v>
       </c>
       <c r="BY26" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="BZ26">
         <v>5.5</v>
       </c>
       <c r="CA26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB26">
         <v>88</v>
@@ -10789,25 +10774,25 @@
         <v>124</v>
       </c>
       <c r="E27" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F27" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G27" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="H27" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I27" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="J27">
-        <v>23.4</v>
+        <v>48.3</v>
       </c>
       <c r="K27">
-        <v>18.7</v>
+        <v>18.3</v>
       </c>
       <c r="L27">
         <v>5</v>
@@ -10819,7 +10804,7 @@
         <v>3.41</v>
       </c>
       <c r="O27">
-        <v>28.73</v>
+        <v>28.63</v>
       </c>
       <c r="P27">
         <v>2.4</v>
@@ -10834,13 +10819,13 @@
         <v>100</v>
       </c>
       <c r="T27" t="s">
+        <v>344</v>
+      </c>
+      <c r="U27" t="s">
         <v>349</v>
       </c>
-      <c r="U27" t="s">
-        <v>354</v>
-      </c>
       <c r="V27" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="W27">
         <v>0.6667</v>
@@ -10867,7 +10852,7 @@
         <v>0.5</v>
       </c>
       <c r="AE27" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="AF27">
         <v>85</v>
@@ -10891,7 +10876,7 @@
         <v>75</v>
       </c>
       <c r="AM27">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="AN27">
         <v>0.019</v>
@@ -10957,7 +10942,7 @@
         <v>1.126</v>
       </c>
       <c r="BI27" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ27">
         <v>2596</v>
@@ -11005,13 +10990,13 @@
         <v>28.3</v>
       </c>
       <c r="BY27" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BZ27">
         <v>13</v>
       </c>
       <c r="CA27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB27">
         <v>85</v>
@@ -11040,25 +11025,25 @@
         <v>124</v>
       </c>
       <c r="E28" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F28" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G28" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="H28" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I28" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="J28">
-        <v>23.4</v>
+        <v>48.3</v>
       </c>
       <c r="K28">
-        <v>19.7</v>
+        <v>19.3</v>
       </c>
       <c r="L28">
         <v>5</v>
@@ -11085,13 +11070,13 @@
         <v>0</v>
       </c>
       <c r="T28" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U28" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="V28" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="W28">
         <v>0.6667</v>
@@ -11100,7 +11085,7 @@
         <v>26.9</v>
       </c>
       <c r="Y28">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="Z28">
         <v>58.6</v>
@@ -11118,7 +11103,7 @@
         <v>0.5</v>
       </c>
       <c r="AE28" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AF28">
         <v>82.8</v>
@@ -11208,7 +11193,7 @@
         <v>1.1303</v>
       </c>
       <c r="BI28" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ28">
         <v>2455</v>
@@ -11256,13 +11241,13 @@
         <v>22.3</v>
       </c>
       <c r="BY28" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BZ28">
         <v>12.1</v>
       </c>
       <c r="CA28" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB28">
         <v>83</v>
@@ -11291,25 +11276,25 @@
         <v>124</v>
       </c>
       <c r="E29" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F29" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G29" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="H29" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I29" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="J29">
-        <v>23.4</v>
+        <v>48.3</v>
       </c>
       <c r="K29">
-        <v>20.7</v>
+        <v>20.3</v>
       </c>
       <c r="L29">
         <v>5</v>
@@ -11336,13 +11321,13 @@
         <v>0</v>
       </c>
       <c r="T29" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U29" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="V29" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="W29">
         <v>0.6667</v>
@@ -11354,7 +11339,7 @@
         <v>84.7</v>
       </c>
       <c r="Z29">
-        <v>59.6</v>
+        <v>59.7</v>
       </c>
       <c r="AA29">
         <v>0.82</v>
@@ -11459,7 +11444,7 @@
         <v>1.133</v>
       </c>
       <c r="BI29" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ29">
         <v>2371</v>
@@ -11507,13 +11492,13 @@
         <v>15</v>
       </c>
       <c r="BY29" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ29">
         <v>9.699999999999999</v>
       </c>
       <c r="CA29" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB29">
         <v>82</v>
@@ -11542,25 +11527,25 @@
         <v>125</v>
       </c>
       <c r="E30" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F30" t="s">
         <v>112</v>
       </c>
       <c r="G30" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="H30" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I30" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="J30">
-        <v>153.9</v>
+        <v>178.8</v>
       </c>
       <c r="K30">
-        <v>18.2</v>
+        <v>17.7</v>
       </c>
       <c r="L30">
         <v>5</v>
@@ -11572,7 +11557,7 @@
         <v>0.98</v>
       </c>
       <c r="O30">
-        <v>35.63</v>
+        <v>35.95</v>
       </c>
       <c r="P30">
         <v>17.5</v>
@@ -11587,19 +11572,19 @@
         <v>0</v>
       </c>
       <c r="T30" t="s">
+        <v>344</v>
+      </c>
+      <c r="U30" t="s">
         <v>349</v>
       </c>
-      <c r="U30" t="s">
-        <v>354</v>
-      </c>
       <c r="V30" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="W30">
         <v>0.0833</v>
       </c>
       <c r="X30">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Y30">
         <v>77.7</v>
@@ -11644,7 +11629,7 @@
         <v>42.5</v>
       </c>
       <c r="AM30">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="AN30">
         <v>0.007</v>
@@ -11710,7 +11695,7 @@
         <v>1.1497</v>
       </c>
       <c r="BI30" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ30">
         <v>1889</v>
@@ -11755,16 +11740,16 @@
         <v>51.6</v>
       </c>
       <c r="BX30">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="BY30" t="s">
+        <v>189</v>
+      </c>
+      <c r="BZ30">
+        <v>21.6</v>
+      </c>
+      <c r="CA30" t="s">
         <v>190</v>
-      </c>
-      <c r="BZ30">
-        <v>21.7</v>
-      </c>
-      <c r="CA30" t="s">
-        <v>191</v>
       </c>
       <c r="CB30">
         <v>86</v>
@@ -11793,25 +11778,25 @@
         <v>125</v>
       </c>
       <c r="E31" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F31" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G31" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="H31" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I31" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="J31">
-        <v>153.9</v>
+        <v>178.8</v>
       </c>
       <c r="K31">
-        <v>19.2</v>
+        <v>18.7</v>
       </c>
       <c r="L31">
         <v>5</v>
@@ -11823,7 +11808,7 @@
         <v>2.27</v>
       </c>
       <c r="O31">
-        <v>26.44</v>
+        <v>25.65</v>
       </c>
       <c r="P31">
         <v>6.9</v>
@@ -11838,22 +11823,22 @@
         <v>0</v>
       </c>
       <c r="T31" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U31" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="V31" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="W31">
         <v>0.0833</v>
       </c>
       <c r="X31">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="Y31">
-        <v>86.3</v>
+        <v>86.5</v>
       </c>
       <c r="Z31">
         <v>77.90000000000001</v>
@@ -11895,7 +11880,7 @@
         <v>46.5</v>
       </c>
       <c r="AM31">
-        <v>23.1</v>
+        <v>23.6</v>
       </c>
       <c r="AN31">
         <v>0.003</v>
@@ -11961,7 +11946,7 @@
         <v>1.1518</v>
       </c>
       <c r="BI31" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ31">
         <v>1821</v>
@@ -12006,16 +11991,16 @@
         <v>49.7</v>
       </c>
       <c r="BX31">
-        <v>25.9</v>
+        <v>26.2</v>
       </c>
       <c r="BY31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BZ31">
         <v>3.8</v>
       </c>
       <c r="CA31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB31">
         <v>84</v>
@@ -12044,25 +12029,25 @@
         <v>125</v>
       </c>
       <c r="E32" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F32" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G32" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="H32" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I32" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="J32">
-        <v>153.9</v>
+        <v>178.8</v>
       </c>
       <c r="K32">
-        <v>20.2</v>
+        <v>19.7</v>
       </c>
       <c r="L32">
         <v>5</v>
@@ -12074,7 +12059,7 @@
         <v>1.01</v>
       </c>
       <c r="O32">
-        <v>16.49</v>
+        <v>16.05</v>
       </c>
       <c r="P32">
         <v>14.5</v>
@@ -12089,25 +12074,25 @@
         <v>0</v>
       </c>
       <c r="T32" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U32" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="V32" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="W32">
         <v>0.0833</v>
       </c>
       <c r="X32">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="Y32">
-        <v>87.2</v>
+        <v>87.3</v>
       </c>
       <c r="Z32">
-        <v>75.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AA32">
         <v>1.18</v>
@@ -12146,7 +12131,7 @@
         <v>86.7</v>
       </c>
       <c r="AM32">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="AN32">
         <v>0.001</v>
@@ -12212,7 +12197,7 @@
         <v>1.1537</v>
       </c>
       <c r="BI32" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ32">
         <v>1747</v>
@@ -12257,16 +12242,16 @@
         <v>51.2</v>
       </c>
       <c r="BX32">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="BY32" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BZ32">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="CA32" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB32">
         <v>83</v>
@@ -12295,25 +12280,25 @@
         <v>125</v>
       </c>
       <c r="E33" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F33" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G33" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="H33" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I33" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="J33">
-        <v>153.9</v>
+        <v>178.8</v>
       </c>
       <c r="K33">
-        <v>21.2</v>
+        <v>20.7</v>
       </c>
       <c r="L33">
         <v>5</v>
@@ -12340,13 +12325,13 @@
         <v>0</v>
       </c>
       <c r="T33" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U33" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="V33" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="W33">
         <v>0.0833</v>
@@ -12373,7 +12358,7 @@
         <v>1.8</v>
       </c>
       <c r="AE33" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="AF33">
         <v>81.09999999999999</v>
@@ -12463,7 +12448,7 @@
         <v>1.1564</v>
       </c>
       <c r="BI33" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ33">
         <v>1654</v>
@@ -12511,13 +12496,13 @@
         <v>19.8</v>
       </c>
       <c r="BY33" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ33">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="CA33" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB33">
         <v>81</v>
@@ -12546,25 +12531,25 @@
         <v>126</v>
       </c>
       <c r="E34" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F34" t="s">
         <v>113</v>
       </c>
       <c r="G34" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="H34" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I34" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="J34">
-        <v>128.9</v>
+        <v>153.8</v>
       </c>
       <c r="K34">
-        <v>18.2</v>
+        <v>17.8</v>
       </c>
       <c r="L34">
         <v>5</v>
@@ -12591,13 +12576,13 @@
         <v>0</v>
       </c>
       <c r="T34" t="s">
+        <v>344</v>
+      </c>
+      <c r="U34" t="s">
         <v>349</v>
       </c>
-      <c r="U34" t="s">
-        <v>354</v>
-      </c>
       <c r="V34" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="W34">
         <v>0.1667</v>
@@ -12714,7 +12699,7 @@
         <v>1.1896</v>
       </c>
       <c r="BI34" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ34">
         <v>858</v>
@@ -12762,13 +12747,13 @@
         <v>0</v>
       </c>
       <c r="BY34" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="BZ34">
         <v>12.9</v>
       </c>
       <c r="CA34" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB34">
         <v>90</v>
@@ -12797,25 +12782,25 @@
         <v>126</v>
       </c>
       <c r="E35" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F35" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G35" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="H35" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I35" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="J35">
-        <v>128.9</v>
+        <v>153.8</v>
       </c>
       <c r="K35">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
       <c r="L35">
         <v>5</v>
@@ -12842,13 +12827,13 @@
         <v>0</v>
       </c>
       <c r="T35" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U35" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="V35" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="W35">
         <v>0.1667</v>
@@ -12965,7 +12950,7 @@
         <v>1.1575</v>
       </c>
       <c r="BI35" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ35">
         <v>1621</v>
@@ -13013,13 +12998,13 @@
         <v>12.9</v>
       </c>
       <c r="BY35" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ35">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="CA35" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB35">
         <v>88</v>
@@ -13048,25 +13033,25 @@
         <v>126</v>
       </c>
       <c r="E36" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F36" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="G36" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="H36" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I36" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="J36">
-        <v>128.9</v>
+        <v>153.8</v>
       </c>
       <c r="K36">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="L36">
         <v>5</v>
@@ -13093,13 +13078,13 @@
         <v>0</v>
       </c>
       <c r="T36" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U36" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="V36" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="W36">
         <v>0.1667</v>
@@ -13216,7 +13201,7 @@
         <v>1.1622</v>
       </c>
       <c r="BI36" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ36">
         <v>1467</v>
@@ -13264,13 +13249,13 @@
         <v>12.5</v>
       </c>
       <c r="BY36" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ36">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="CA36" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB36">
         <v>85</v>
@@ -13299,25 +13284,25 @@
         <v>126</v>
       </c>
       <c r="E37" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F37" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G37" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="H37" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I37" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="J37">
-        <v>128.9</v>
+        <v>153.8</v>
       </c>
       <c r="K37">
-        <v>21.2</v>
+        <v>20.8</v>
       </c>
       <c r="L37">
         <v>5</v>
@@ -13344,13 +13329,13 @@
         <v>0</v>
       </c>
       <c r="T37" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U37" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="V37" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="W37">
         <v>0.1667</v>
@@ -13467,7 +13452,7 @@
         <v>1.1646</v>
       </c>
       <c r="BI37" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ37">
         <v>1385</v>
@@ -13515,13 +13500,13 @@
         <v>12.9</v>
       </c>
       <c r="BY37" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ37">
         <v>10.7</v>
       </c>
       <c r="CA37" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB37">
         <v>84</v>
@@ -13550,25 +13535,25 @@
         <v>127</v>
       </c>
       <c r="E38" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F38" t="s">
         <v>113</v>
       </c>
       <c r="G38" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="H38" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I38" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="J38">
-        <v>103.1</v>
+        <v>128</v>
       </c>
       <c r="K38">
-        <v>18.2</v>
+        <v>17.8</v>
       </c>
       <c r="L38">
         <v>5</v>
@@ -13580,7 +13565,7 @@
         <v>1.31</v>
       </c>
       <c r="O38">
-        <v>24.62</v>
+        <v>24.85</v>
       </c>
       <c r="P38">
         <v>5.4</v>
@@ -13595,22 +13580,22 @@
         <v>0</v>
       </c>
       <c r="T38" t="s">
+        <v>344</v>
+      </c>
+      <c r="U38" t="s">
         <v>349</v>
       </c>
-      <c r="U38" t="s">
-        <v>354</v>
-      </c>
       <c r="V38" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="W38">
         <v>0.1667</v>
       </c>
       <c r="X38">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="Y38">
-        <v>86.7</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="Z38">
         <v>76.90000000000001</v>
@@ -13652,7 +13637,7 @@
         <v>45.4</v>
       </c>
       <c r="AM38">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="AN38">
         <v>0.002</v>
@@ -13718,7 +13703,7 @@
         <v>1.1173</v>
       </c>
       <c r="BI38" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ38">
         <v>2873</v>
@@ -13763,16 +13748,16 @@
         <v>47.2</v>
       </c>
       <c r="BX38">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="BY38" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BZ38">
         <v>11.8</v>
       </c>
       <c r="CA38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB38">
         <v>89</v>
@@ -13801,25 +13786,25 @@
         <v>127</v>
       </c>
       <c r="E39" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F39" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G39" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="H39" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I39" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="J39">
-        <v>103.1</v>
+        <v>128</v>
       </c>
       <c r="K39">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
       <c r="L39">
         <v>5</v>
@@ -13846,13 +13831,13 @@
         <v>0</v>
       </c>
       <c r="T39" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U39" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="V39" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="W39">
         <v>0.1667</v>
@@ -13969,7 +13954,7 @@
         <v>1.1216</v>
       </c>
       <c r="BI39" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ39">
         <v>2731</v>
@@ -14017,13 +14002,13 @@
         <v>18.5</v>
       </c>
       <c r="BY39" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ39">
         <v>12.4</v>
       </c>
       <c r="CA39" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB39">
         <v>87</v>
@@ -14052,25 +14037,25 @@
         <v>127</v>
       </c>
       <c r="E40" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F40" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="G40" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="H40" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I40" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="J40">
-        <v>103.1</v>
+        <v>128</v>
       </c>
       <c r="K40">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="L40">
         <v>5</v>
@@ -14097,13 +14082,13 @@
         <v>0</v>
       </c>
       <c r="T40" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U40" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="V40" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="W40">
         <v>0.1667</v>
@@ -14112,10 +14097,10 @@
         <v>15.1</v>
       </c>
       <c r="Y40">
-        <v>85.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Z40">
-        <v>69.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="AA40">
         <v>1.03</v>
@@ -14220,7 +14205,7 @@
         <v>1.1259</v>
       </c>
       <c r="BI40" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ40">
         <v>2592</v>
@@ -14268,13 +14253,13 @@
         <v>15</v>
       </c>
       <c r="BY40" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ40">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="CA40" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB40">
         <v>85</v>
@@ -14303,25 +14288,25 @@
         <v>127</v>
       </c>
       <c r="E41" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F41" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G41" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="H41" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I41" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="J41">
-        <v>103.1</v>
+        <v>128</v>
       </c>
       <c r="K41">
-        <v>21.2</v>
+        <v>20.8</v>
       </c>
       <c r="L41">
         <v>5</v>
@@ -14348,13 +14333,13 @@
         <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U41" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="V41" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="W41">
         <v>0.1667</v>
@@ -14471,7 +14456,7 @@
         <v>1.13</v>
       </c>
       <c r="BI41" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ41">
         <v>2461</v>
@@ -14519,13 +14504,13 @@
         <v>11.6</v>
       </c>
       <c r="BY41" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ41">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="CA41" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB41">
         <v>83</v>
@@ -14554,25 +14539,25 @@
         <v>128</v>
       </c>
       <c r="E42" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F42" t="s">
         <v>114</v>
       </c>
       <c r="G42" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="H42" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I42" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="J42">
-        <v>668.9</v>
+        <v>693.8</v>
       </c>
       <c r="K42">
-        <v>18.7</v>
+        <v>18.3</v>
       </c>
       <c r="L42">
         <v>5</v>
@@ -14599,13 +14584,13 @@
         <v>75</v>
       </c>
       <c r="T42" t="s">
+        <v>344</v>
+      </c>
+      <c r="U42" t="s">
+        <v>353</v>
+      </c>
+      <c r="V42" t="s">
         <v>349</v>
-      </c>
-      <c r="U42" t="s">
-        <v>358</v>
-      </c>
-      <c r="V42" t="s">
-        <v>354</v>
       </c>
       <c r="W42">
         <v>0.6667</v>
@@ -14614,10 +14599,10 @@
         <v>11.5</v>
       </c>
       <c r="Y42">
-        <v>92.5</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Z42">
-        <v>71.7</v>
+        <v>71.8</v>
       </c>
       <c r="AA42">
         <v>1.05</v>
@@ -14722,7 +14707,7 @@
         <v>0.9556</v>
       </c>
       <c r="BI42" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="BJ42">
         <v>8309</v>
@@ -14770,13 +14755,13 @@
         <v>1.8</v>
       </c>
       <c r="BY42" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ42">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="CA42" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB42">
         <v>92</v>
@@ -14805,25 +14790,25 @@
         <v>128</v>
       </c>
       <c r="E43" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F43" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G43" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="H43" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I43" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="J43">
-        <v>668.9</v>
+        <v>693.8</v>
       </c>
       <c r="K43">
-        <v>19.7</v>
+        <v>19.3</v>
       </c>
       <c r="L43">
         <v>5</v>
@@ -14850,13 +14835,13 @@
         <v>75</v>
       </c>
       <c r="T43" t="s">
+        <v>344</v>
+      </c>
+      <c r="U43" t="s">
         <v>349</v>
       </c>
-      <c r="U43" t="s">
-        <v>354</v>
-      </c>
       <c r="V43" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="W43">
         <v>0.6667</v>
@@ -14973,7 +14958,7 @@
         <v>0.9583</v>
       </c>
       <c r="BI43" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="BJ43">
         <v>8204</v>
@@ -15021,13 +15006,13 @@
         <v>1</v>
       </c>
       <c r="BY43" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ43">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="CA43" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB43">
         <v>91</v>
@@ -15056,25 +15041,25 @@
         <v>128</v>
       </c>
       <c r="E44" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F44" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G44" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="H44" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I44" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="J44">
-        <v>668.9</v>
+        <v>693.8</v>
       </c>
       <c r="K44">
-        <v>20.7</v>
+        <v>20.3</v>
       </c>
       <c r="L44">
         <v>5</v>
@@ -15101,13 +15086,13 @@
         <v>0</v>
       </c>
       <c r="T44" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U44" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="V44" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="W44">
         <v>0.6667</v>
@@ -15224,7 +15209,7 @@
         <v>0.9641999999999999</v>
       </c>
       <c r="BI44" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="BJ44">
         <v>7979</v>
@@ -15272,13 +15257,13 @@
         <v>1.3</v>
       </c>
       <c r="BY44" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ44">
         <v>8.5</v>
       </c>
       <c r="CA44" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB44">
         <v>87</v>
@@ -15307,25 +15292,25 @@
         <v>128</v>
       </c>
       <c r="E45" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F45" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G45" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="H45" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I45" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="J45">
-        <v>668.9</v>
+        <v>693.8</v>
       </c>
       <c r="K45">
-        <v>21.7</v>
+        <v>21.3</v>
       </c>
       <c r="L45">
         <v>5</v>
@@ -15352,13 +15337,13 @@
         <v>0</v>
       </c>
       <c r="T45" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U45" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="V45" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="W45">
         <v>0.6667</v>
@@ -15427,7 +15412,7 @@
         <v>19.4</v>
       </c>
       <c r="AS45" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="AT45">
         <v>132.2</v>
@@ -15475,7 +15460,7 @@
         <v>0.9697</v>
       </c>
       <c r="BI45" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="BJ45">
         <v>7772</v>
@@ -15523,13 +15508,13 @@
         <v>0.6</v>
       </c>
       <c r="BY45" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ45">
         <v>7.1</v>
       </c>
       <c r="CA45" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB45">
         <v>84</v>
@@ -15558,25 +15543,25 @@
         <v>129</v>
       </c>
       <c r="E46" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F46" t="s">
         <v>115</v>
       </c>
       <c r="G46" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="H46" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I46" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="J46">
-        <v>129</v>
+        <v>153.9</v>
       </c>
       <c r="K46">
-        <v>19.7</v>
+        <v>19.3</v>
       </c>
       <c r="L46">
         <v>5</v>
@@ -15603,13 +15588,13 @@
         <v>0</v>
       </c>
       <c r="T46" t="s">
+        <v>344</v>
+      </c>
+      <c r="U46" t="s">
+        <v>353</v>
+      </c>
+      <c r="V46" t="s">
         <v>349</v>
-      </c>
-      <c r="U46" t="s">
-        <v>358</v>
-      </c>
-      <c r="V46" t="s">
-        <v>354</v>
       </c>
       <c r="W46">
         <v>0.6333</v>
@@ -15726,7 +15711,7 @@
         <v>1.1717</v>
       </c>
       <c r="BI46" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ46">
         <v>1281</v>
@@ -15774,13 +15759,13 @@
         <v>1.3</v>
       </c>
       <c r="BY46" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ46">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="CA46" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB46">
         <v>79</v>
@@ -15809,25 +15794,25 @@
         <v>129</v>
       </c>
       <c r="E47" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F47" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G47" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="H47" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I47" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="J47">
-        <v>129</v>
+        <v>153.9</v>
       </c>
       <c r="K47">
-        <v>20.7</v>
+        <v>20.3</v>
       </c>
       <c r="L47">
         <v>5</v>
@@ -15854,13 +15839,13 @@
         <v>0</v>
       </c>
       <c r="T47" t="s">
+        <v>344</v>
+      </c>
+      <c r="U47" t="s">
         <v>349</v>
       </c>
-      <c r="U47" t="s">
-        <v>354</v>
-      </c>
       <c r="V47" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="W47">
         <v>0.6333</v>
@@ -15977,7 +15962,7 @@
         <v>1.1783</v>
       </c>
       <c r="BI47" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ47">
         <v>1087</v>
@@ -16025,13 +16010,13 @@
         <v>1.3</v>
       </c>
       <c r="BY47" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ47">
         <v>13.2</v>
       </c>
       <c r="CA47" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB47">
         <v>76</v>
@@ -16060,25 +16045,25 @@
         <v>129</v>
       </c>
       <c r="E48" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F48" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G48" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="H48" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I48" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="J48">
-        <v>129</v>
+        <v>153.9</v>
       </c>
       <c r="K48">
-        <v>21.7</v>
+        <v>21.3</v>
       </c>
       <c r="L48">
         <v>5</v>
@@ -16105,13 +16090,13 @@
         <v>0</v>
       </c>
       <c r="T48" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U48" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="V48" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="W48">
         <v>0.6333</v>
@@ -16228,7 +16213,7 @@
         <v>1.1839</v>
       </c>
       <c r="BI48" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ48">
         <v>917</v>
@@ -16276,13 +16261,13 @@
         <v>1.3</v>
       </c>
       <c r="BY48" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ48">
         <v>8.4</v>
       </c>
       <c r="CA48" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB48">
         <v>73</v>
@@ -16311,25 +16296,25 @@
         <v>129</v>
       </c>
       <c r="E49" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F49" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G49" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="H49" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I49" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="J49">
-        <v>129</v>
+        <v>153.9</v>
       </c>
       <c r="K49">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="L49">
         <v>5</v>
@@ -16356,13 +16341,13 @@
         <v>0</v>
       </c>
       <c r="T49" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U49" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="V49" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="W49">
         <v>0.6333</v>
@@ -16479,7 +16464,7 @@
         <v>1.1875</v>
       </c>
       <c r="BI49" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ49">
         <v>808</v>
@@ -16527,13 +16512,13 @@
         <v>1.3</v>
       </c>
       <c r="BY49" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ49">
         <v>4.5</v>
       </c>
       <c r="CA49" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB49">
         <v>71</v>
@@ -16562,25 +16547,25 @@
         <v>130</v>
       </c>
       <c r="E50" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F50" t="s">
         <v>116</v>
       </c>
       <c r="G50" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="H50" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I50" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="J50">
-        <v>534.5</v>
+        <v>559.3</v>
       </c>
       <c r="K50">
-        <v>19.7</v>
+        <v>19.3</v>
       </c>
       <c r="L50">
         <v>5</v>
@@ -16607,13 +16592,13 @@
         <v>0</v>
       </c>
       <c r="T50" t="s">
+        <v>344</v>
+      </c>
+      <c r="U50" t="s">
+        <v>353</v>
+      </c>
+      <c r="V50" t="s">
         <v>349</v>
-      </c>
-      <c r="U50" t="s">
-        <v>358</v>
-      </c>
-      <c r="V50" t="s">
-        <v>354</v>
       </c>
       <c r="W50">
         <v>0.6667</v>
@@ -16730,7 +16715,7 @@
         <v>1.157</v>
       </c>
       <c r="BI50" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ50">
         <v>1846</v>
@@ -16778,13 +16763,13 @@
         <v>0</v>
       </c>
       <c r="BY50" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ50">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="CA50" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB50">
         <v>84</v>
@@ -16813,25 +16798,25 @@
         <v>130</v>
       </c>
       <c r="E51" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F51" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G51" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="H51" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I51" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="J51">
-        <v>534.5</v>
+        <v>559.3</v>
       </c>
       <c r="K51">
-        <v>20.7</v>
+        <v>20.3</v>
       </c>
       <c r="L51">
         <v>5</v>
@@ -16858,13 +16843,13 @@
         <v>0</v>
       </c>
       <c r="T51" t="s">
+        <v>344</v>
+      </c>
+      <c r="U51" t="s">
         <v>349</v>
       </c>
-      <c r="U51" t="s">
-        <v>354</v>
-      </c>
       <c r="V51" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="W51">
         <v>0.6667</v>
@@ -16981,7 +16966,7 @@
         <v>1.1689</v>
       </c>
       <c r="BI51" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ51">
         <v>1474</v>
@@ -17029,13 +17014,13 @@
         <v>0</v>
       </c>
       <c r="BY51" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ51">
         <v>4.7</v>
       </c>
       <c r="CA51" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB51">
         <v>78</v>
@@ -17064,25 +17049,25 @@
         <v>130</v>
       </c>
       <c r="E52" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F52" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G52" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="H52" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I52" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="J52">
-        <v>534.5</v>
+        <v>559.3</v>
       </c>
       <c r="K52">
-        <v>21.7</v>
+        <v>21.3</v>
       </c>
       <c r="L52">
         <v>5</v>
@@ -17109,13 +17094,13 @@
         <v>0</v>
       </c>
       <c r="T52" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U52" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="V52" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="W52">
         <v>0.6667</v>
@@ -17232,7 +17217,7 @@
         <v>1.1815</v>
       </c>
       <c r="BI52" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ52">
         <v>1092</v>
@@ -17280,13 +17265,13 @@
         <v>0</v>
       </c>
       <c r="BY52" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ52">
         <v>5.4</v>
       </c>
       <c r="CA52" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB52">
         <v>72</v>
@@ -17315,25 +17300,25 @@
         <v>130</v>
       </c>
       <c r="E53" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F53" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G53" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="H53" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I53" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="J53">
-        <v>534.5</v>
+        <v>559.3</v>
       </c>
       <c r="K53">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="L53">
         <v>5</v>
@@ -17360,13 +17345,13 @@
         <v>0</v>
       </c>
       <c r="T53" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U53" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="V53" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="W53">
         <v>0.6667</v>
@@ -17483,7 +17468,7 @@
         <v>1.1915</v>
       </c>
       <c r="BI53" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ53">
         <v>794</v>
@@ -17531,13 +17516,13 @@
         <v>0</v>
       </c>
       <c r="BY53" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ53">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="CA53" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB53">
         <v>68</v>
@@ -17566,25 +17551,25 @@
         <v>131</v>
       </c>
       <c r="E54" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F54" t="s">
         <v>117</v>
       </c>
       <c r="G54" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="H54" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I54" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="J54">
-        <v>62.1</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K54">
-        <v>19.7</v>
+        <v>19.3</v>
       </c>
       <c r="L54">
         <v>5</v>
@@ -17611,13 +17596,13 @@
         <v>81.2</v>
       </c>
       <c r="T54" t="s">
+        <v>344</v>
+      </c>
+      <c r="U54" t="s">
+        <v>353</v>
+      </c>
+      <c r="V54" t="s">
         <v>349</v>
-      </c>
-      <c r="U54" t="s">
-        <v>358</v>
-      </c>
-      <c r="V54" t="s">
-        <v>354</v>
       </c>
       <c r="W54">
         <v>0.6667</v>
@@ -17734,7 +17719,7 @@
         <v>1.1896</v>
       </c>
       <c r="BI54" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ54">
         <v>858</v>
@@ -17782,13 +17767,13 @@
         <v>0</v>
       </c>
       <c r="BY54" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="BZ54">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="CA54" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="CB54">
         <v>91</v>
@@ -17817,25 +17802,25 @@
         <v>131</v>
       </c>
       <c r="E55" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F55" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G55" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="H55" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I55" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="J55">
-        <v>62.1</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K55">
-        <v>20.7</v>
+        <v>20.3</v>
       </c>
       <c r="L55">
         <v>5</v>
@@ -17847,7 +17832,7 @@
         <v>0.72</v>
       </c>
       <c r="O55">
-        <v>5.97</v>
+        <v>6.12</v>
       </c>
       <c r="P55">
         <v>43.6</v>
@@ -17862,19 +17847,19 @@
         <v>25</v>
       </c>
       <c r="T55" t="s">
+        <v>344</v>
+      </c>
+      <c r="U55" t="s">
         <v>349</v>
       </c>
-      <c r="U55" t="s">
-        <v>354</v>
-      </c>
       <c r="V55" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="W55">
         <v>0.6667</v>
       </c>
       <c r="X55">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="Y55">
         <v>84.8</v>
@@ -17919,7 +17904,7 @@
         <v>99.8</v>
       </c>
       <c r="AM55">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AN55">
         <v>0</v>
@@ -17985,7 +17970,7 @@
         <v>1.1079</v>
       </c>
       <c r="BI55" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ55">
         <v>3086</v>
@@ -18030,16 +18015,16 @@
         <v>49.9</v>
       </c>
       <c r="BX55">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="BY55" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ55">
         <v>18.3</v>
       </c>
       <c r="CA55" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="CB55">
         <v>90</v>
@@ -18068,25 +18053,25 @@
         <v>131</v>
       </c>
       <c r="E56" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F56" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G56" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="H56" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I56" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="J56">
-        <v>62.1</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K56">
-        <v>21.7</v>
+        <v>21.3</v>
       </c>
       <c r="L56">
         <v>5</v>
@@ -18098,7 +18083,7 @@
         <v>0.61</v>
       </c>
       <c r="O56">
-        <v>4.09</v>
+        <v>4.26</v>
       </c>
       <c r="P56">
         <v>55.8</v>
@@ -18113,13 +18098,13 @@
         <v>25</v>
       </c>
       <c r="T56" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U56" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="V56" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="W56">
         <v>0.6667</v>
@@ -18170,7 +18155,7 @@
         <v>99.8</v>
       </c>
       <c r="AM56">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="AN56">
         <v>0</v>
@@ -18188,7 +18173,7 @@
         <v>4.5</v>
       </c>
       <c r="AS56" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="AT56">
         <v>126.4</v>
@@ -18236,7 +18221,7 @@
         <v>1.1101</v>
       </c>
       <c r="BI56" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ56">
         <v>3020</v>
@@ -18281,16 +18266,16 @@
         <v>51</v>
       </c>
       <c r="BX56">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="BY56" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ56">
         <v>17.6</v>
       </c>
       <c r="CA56" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB56">
         <v>89</v>
@@ -18319,25 +18304,25 @@
         <v>131</v>
       </c>
       <c r="E57" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F57" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G57" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="H57" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I57" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="J57">
-        <v>62.1</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K57">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="L57">
         <v>5</v>
@@ -18349,7 +18334,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="O57">
-        <v>4.06</v>
+        <v>4.09</v>
       </c>
       <c r="P57">
         <v>90.09999999999999</v>
@@ -18364,13 +18349,13 @@
         <v>25</v>
       </c>
       <c r="T57" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U57" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="V57" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="W57">
         <v>0.6667</v>
@@ -18379,7 +18364,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Y57">
-        <v>87.09999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="Z57">
         <v>60.4</v>
@@ -18421,7 +18406,7 @@
         <v>99.8</v>
       </c>
       <c r="AM57">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="AN57">
         <v>0</v>
@@ -18439,7 +18424,7 @@
         <v>3</v>
       </c>
       <c r="AS57" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="AT57">
         <v>250.8</v>
@@ -18487,7 +18472,7 @@
         <v>1.1121</v>
       </c>
       <c r="BI57" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="BJ57">
         <v>2956</v>
@@ -18532,16 +18517,16 @@
         <v>51.6</v>
       </c>
       <c r="BX57">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="BY57" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ57">
         <v>16.7</v>
       </c>
       <c r="CA57" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB57">
         <v>88</v>
@@ -18570,25 +18555,25 @@
         <v>132</v>
       </c>
       <c r="E58" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F58" t="s">
         <v>118</v>
       </c>
       <c r="G58" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="H58" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I58" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="J58">
-        <v>540.2</v>
+        <v>565</v>
       </c>
       <c r="K58">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="L58">
         <v>5</v>
@@ -18615,13 +18600,13 @@
         <v>56.2</v>
       </c>
       <c r="T58" t="s">
+        <v>344</v>
+      </c>
+      <c r="U58" t="s">
         <v>349</v>
       </c>
-      <c r="U58" t="s">
-        <v>354</v>
-      </c>
       <c r="V58" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="W58">
         <v>0.1667</v>
@@ -18630,7 +18615,7 @@
         <v>4.9</v>
       </c>
       <c r="Y58">
-        <v>88.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Z58">
         <v>54.8</v>
@@ -18738,7 +18723,7 @@
         <v>1.1875</v>
       </c>
       <c r="BI58" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ58">
         <v>885</v>
@@ -18786,13 +18771,13 @@
         <v>0.2</v>
       </c>
       <c r="BY58" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ58">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="CA58" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB58">
         <v>75</v>
@@ -18821,25 +18806,25 @@
         <v>132</v>
       </c>
       <c r="E59" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F59" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G59" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="H59" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I59" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="J59">
-        <v>540.2</v>
+        <v>565</v>
       </c>
       <c r="K59">
-        <v>21.2</v>
+        <v>20.8</v>
       </c>
       <c r="L59">
         <v>5</v>
@@ -18866,13 +18851,13 @@
         <v>56.2</v>
       </c>
       <c r="T59" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U59" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="V59" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="W59">
         <v>0.1667</v>
@@ -18881,7 +18866,7 @@
         <v>9.5</v>
       </c>
       <c r="Y59">
-        <v>85.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Z59">
         <v>50.5</v>
@@ -18941,7 +18926,7 @@
         <v>9.4</v>
       </c>
       <c r="AS59" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="AT59">
         <v>325.1</v>
@@ -18989,7 +18974,7 @@
         <v>1.1931</v>
       </c>
       <c r="BI59" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ59">
         <v>720</v>
@@ -19037,13 +19022,13 @@
         <v>0.2</v>
       </c>
       <c r="BY59" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ59">
         <v>18</v>
       </c>
       <c r="CA59" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="CB59">
         <v>73</v>
@@ -19072,25 +19057,25 @@
         <v>132</v>
       </c>
       <c r="E60" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F60" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G60" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="H60" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I60" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="J60">
-        <v>540.2</v>
+        <v>565</v>
       </c>
       <c r="K60">
-        <v>22.2</v>
+        <v>21.8</v>
       </c>
       <c r="L60">
         <v>5</v>
@@ -19117,13 +19102,13 @@
         <v>56.2</v>
       </c>
       <c r="T60" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U60" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="V60" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="W60">
         <v>0.1667</v>
@@ -19132,7 +19117,7 @@
         <v>12.4</v>
       </c>
       <c r="Y60">
-        <v>87.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="Z60">
         <v>49.2</v>
@@ -19192,7 +19177,7 @@
         <v>8.6</v>
       </c>
       <c r="AS60" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="AT60">
         <v>332.6</v>
@@ -19240,7 +19225,7 @@
         <v>1.2008</v>
       </c>
       <c r="BI60" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ60">
         <v>497</v>
@@ -19288,13 +19273,13 @@
         <v>0.2</v>
       </c>
       <c r="BY60" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ60">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="CA60" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB60">
         <v>69</v>
@@ -19323,25 +19308,25 @@
         <v>132</v>
       </c>
       <c r="E61" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F61" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G61" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="H61" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I61" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="J61">
-        <v>540.2</v>
+        <v>565</v>
       </c>
       <c r="K61">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="L61">
         <v>5</v>
@@ -19368,13 +19353,13 @@
         <v>56.2</v>
       </c>
       <c r="T61" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="U61" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="V61" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="W61">
         <v>0.1667</v>
@@ -19383,7 +19368,7 @@
         <v>11.6</v>
       </c>
       <c r="Y61">
-        <v>87.7</v>
+        <v>87.8</v>
       </c>
       <c r="Z61">
         <v>48.3</v>
@@ -19443,7 +19428,7 @@
         <v>6.8</v>
       </c>
       <c r="AS61" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="AT61">
         <v>341.2</v>
@@ -19491,7 +19476,7 @@
         <v>1.2065</v>
       </c>
       <c r="BI61" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="BJ61">
         <v>335</v>
@@ -19539,13 +19524,13 @@
         <v>0.2</v>
       </c>
       <c r="BY61" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BZ61">
         <v>12.8</v>
       </c>
       <c r="CA61" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CB61">
         <v>66</v>
@@ -19691,7 +19676,7 @@
         <v>133</v>
       </c>
       <c r="P2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q2">
         <v>5</v>
@@ -19744,7 +19729,7 @@
         <v>133</v>
       </c>
       <c r="P3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -19797,7 +19782,7 @@
         <v>133</v>
       </c>
       <c r="P4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q4">
         <v>5</v>
@@ -19823,7 +19808,7 @@
         <v>166</v>
       </c>
       <c r="G5">
-        <v>83.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="H5">
         <v>10</v>
@@ -19850,7 +19835,7 @@
         <v>133</v>
       </c>
       <c r="P5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q5">
         <v>5</v>
@@ -19876,7 +19861,7 @@
         <v>166</v>
       </c>
       <c r="G6">
-        <v>87.5</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="H6">
         <v>8</v>
@@ -19903,7 +19888,7 @@
         <v>133</v>
       </c>
       <c r="P6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q6">
         <v>5</v>
@@ -19956,7 +19941,7 @@
         <v>133</v>
       </c>
       <c r="P7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -19982,7 +19967,7 @@
         <v>165</v>
       </c>
       <c r="G8">
-        <v>93.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="H8">
         <v>5</v>
@@ -20009,7 +19994,7 @@
         <v>133</v>
       </c>
       <c r="P8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q8">
         <v>5</v>
@@ -20035,7 +20020,7 @@
         <v>165</v>
       </c>
       <c r="G9">
-        <v>91.2</v>
+        <v>91.3</v>
       </c>
       <c r="H9">
         <v>4</v>
@@ -20062,7 +20047,7 @@
         <v>133</v>
       </c>
       <c r="P9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q9">
         <v>5</v>
@@ -20115,7 +20100,7 @@
         <v>133</v>
       </c>
       <c r="P10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -20168,7 +20153,7 @@
         <v>133</v>
       </c>
       <c r="P11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q11">
         <v>4</v>
@@ -20221,7 +20206,7 @@
         <v>133</v>
       </c>
       <c r="P12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q12">
         <v>5</v>
@@ -20247,7 +20232,7 @@
         <v>165</v>
       </c>
       <c r="G13">
-        <v>87.5</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -20274,7 +20259,7 @@
         <v>133</v>
       </c>
       <c r="P13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q13">
         <v>5</v>
@@ -20327,7 +20312,7 @@
         <v>134</v>
       </c>
       <c r="P14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q14">
         <v>5</v>
@@ -20380,7 +20365,7 @@
         <v>134</v>
       </c>
       <c r="P15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -20433,7 +20418,7 @@
         <v>134</v>
       </c>
       <c r="P16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q16">
         <v>5</v>

--- a/mlb_weather_professional_v4_1_2026_07_17.xlsx
+++ b/mlb_weather_professional_v4_1_2026_07_17.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1862" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1862" uniqueCount="374">
   <si>
     <t>Date</t>
   </si>
@@ -443,13 +443,13 @@
     <t>Mostly clear</t>
   </si>
   <si>
+    <t>Clear</t>
+  </si>
+  <si>
     <t>Partly cloudy</t>
   </si>
   <si>
-    <t>Clear</t>
-  </si>
-  <si>
-    <t>Code 29</t>
+    <t>Code 28</t>
   </si>
   <si>
     <t>Code 15</t>
@@ -464,12 +464,15 @@
     <t>Overcast</t>
   </si>
   <si>
-    <t>🟡 8.1 mph Cross (LF → RF)</t>
+    <t>🟡 8.0 mph Cross (LF → RF)</t>
   </si>
   <si>
     <t>⚪ Light Variable</t>
   </si>
   <si>
+    <t>🟢 4.6 mph Out to LF</t>
+  </si>
+  <si>
     <t>⚪ Calm</t>
   </si>
   <si>
@@ -500,18 +503,18 @@
     <t>ESE</t>
   </si>
   <si>
+    <t>SSW</t>
+  </si>
+  <si>
+    <t>SW</t>
+  </si>
+  <si>
     <t>S</t>
   </si>
   <si>
-    <t>SW</t>
-  </si>
-  <si>
     <t>E</t>
   </si>
   <si>
-    <t>SSW</t>
-  </si>
-  <si>
     <t>ENE</t>
   </si>
   <si>
@@ -524,19 +527,19 @@
     <t>B+</t>
   </si>
   <si>
-    <t>Density 68 | Wind 54 | Temp 62 | Altitude 61 | Confidence 91%</t>
+    <t>Density 68 | Wind 54 | Temp 62 | Altitude 61 | Confidence 92%</t>
   </si>
   <si>
     <t>Density 69 | Wind 50 | Temp 63 | Altitude 62 | Confidence 91%</t>
   </si>
   <si>
-    <t>Density 65 | Wind 51 | Temp 56 | Altitude 59 | Confidence 93%</t>
+    <t>Density 65 | Wind 52 | Temp 56 | Altitude 59 | Confidence 92%</t>
   </si>
   <si>
     <t>Density 75 | Wind 49 | Temp 62 | Altitude 66 | Confidence 94%</t>
   </si>
   <si>
-    <t>Density 80 | Wind 58 | Temp 61 | Altitude 69 | Confidence 88%</t>
+    <t>Density 80 | Wind 59 | Temp 61 | Altitude 69 | Confidence 85%</t>
   </si>
   <si>
     <t>Density 66 | Wind 53 | Temp 52 | Altitude 59 | Confidence 93%</t>
@@ -596,43 +599,49 @@
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>2026-07-16 11:19:57 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 11:19:58 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 11:19:59 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 11:20:00 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 11:20:04 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 11:20:09 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 11:20:10 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 11:20:11 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 11:20:12 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 11:20:13 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 11:20:14 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 11:20:15 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-16 11:20:16 PM PDT</t>
+    <t>2026-07-16 11:49:52 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:49:53 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:49:54 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:49:55 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:49:56 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:50:03 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:50:04 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:50:05 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:50:06 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:50:07 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:50:08 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:50:09 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:50:10 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:50:11 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:50:12 PM PDT</t>
   </si>
   <si>
     <t>Period</t>
@@ -977,43 +986,49 @@
     <t>10:10 PM PDT</t>
   </si>
   <si>
-    <t>2026-07-17 06:19:57 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 06:19:58 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 06:19:59 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 06:20:00 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 06:20:04 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 06:20:09 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 06:20:10 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 06:20:11 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 06:20:12 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 06:20:13 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 06:20:14 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 06:20:15 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-17 06:20:16 UTC</t>
+    <t>2026-07-17 06:49:52 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:49:53 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:49:54 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:49:55 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:49:56 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:50:03 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:50:04 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:50:05 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:50:06 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:50:07 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:50:08 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:50:09 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:50:10 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:50:11 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:50:12 UTC</t>
   </si>
   <si>
     <t>2026-07-17T05:23:49+00:00</t>
@@ -1815,7 +1830,7 @@
         <v>139</v>
       </c>
       <c r="K2">
-        <v>83.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="L2">
         <v>26.6</v>
@@ -1824,10 +1839,10 @@
         <v>147</v>
       </c>
       <c r="N2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="O2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P2">
         <v>-2.1</v>
@@ -1839,10 +1854,10 @@
         <v>5.1</v>
       </c>
       <c r="S2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="U2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V2">
         <v>0</v>
@@ -1851,10 +1866,10 @@
         <v>57.2</v>
       </c>
       <c r="X2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Z2">
         <v>4</v>
@@ -1866,10 +1881,10 @@
         <v>2.2</v>
       </c>
       <c r="AC2">
-        <v>91.3</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="AD2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AE2">
         <v>1.7</v>
@@ -1887,16 +1902,16 @@
         <v>7</v>
       </c>
       <c r="AJ2">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK2">
         <v>1.1641</v>
       </c>
       <c r="AL2">
-        <v>1655</v>
+        <v>1658</v>
       </c>
       <c r="AM2">
-        <v>1012.9</v>
+        <v>1012.8</v>
       </c>
       <c r="AN2">
         <v>44.5</v>
@@ -1905,10 +1920,10 @@
         <v>83.90000000000001</v>
       </c>
       <c r="AP2">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="AQ2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1920,22 +1935,22 @@
         <v>0</v>
       </c>
       <c r="AU2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AV2">
         <v>0</v>
       </c>
       <c r="AW2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AX2">
-        <v>7.1</v>
+        <v>5.9</v>
       </c>
       <c r="AY2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AZ2">
-        <v>56.1</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="BA2">
         <v>5</v>
@@ -1970,13 +1985,13 @@
         <v>135</v>
       </c>
       <c r="J3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K3">
         <v>87.3</v>
       </c>
       <c r="L3">
-        <v>29.6</v>
+        <v>29.9</v>
       </c>
       <c r="M3" t="s">
         <v>148</v>
@@ -1985,22 +2000,22 @@
         <v>5</v>
       </c>
       <c r="O3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P3">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="Q3">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R3">
         <v>4.4</v>
       </c>
       <c r="S3">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="U3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V3">
         <v>0.3</v>
@@ -2009,10 +2024,10 @@
         <v>56.3</v>
       </c>
       <c r="X3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Z3">
         <v>4</v>
@@ -2027,7 +2042,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="AD3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AE3">
         <v>0.1</v>
@@ -2042,34 +2057,34 @@
         <v>41.9</v>
       </c>
       <c r="AI3">
-        <v>31.9</v>
+        <v>30.6</v>
       </c>
       <c r="AJ3">
         <v>0.7</v>
       </c>
       <c r="AK3">
-        <v>1.1618</v>
+        <v>1.1619</v>
       </c>
       <c r="AL3">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="AM3">
-        <v>1013</v>
+        <v>1013.2</v>
       </c>
       <c r="AN3">
-        <v>53.1</v>
+        <v>53.3</v>
       </c>
       <c r="AO3">
         <v>84.3</v>
       </c>
       <c r="AP3">
-        <v>37.4</v>
+        <v>37.6</v>
       </c>
       <c r="AQ3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AR3">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="AS3">
         <v>0</v>
@@ -2078,22 +2093,22 @@
         <v>0</v>
       </c>
       <c r="AU3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AV3">
         <v>0.2</v>
       </c>
       <c r="AW3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AX3">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="AY3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AZ3">
-        <v>458.6</v>
+        <v>488.5</v>
       </c>
       <c r="BA3">
         <v>5</v>
@@ -2128,13 +2143,13 @@
         <v>135</v>
       </c>
       <c r="J4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K4">
-        <v>81.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="L4">
-        <v>28.8</v>
+        <v>29.3</v>
       </c>
       <c r="M4" t="s">
         <v>148</v>
@@ -2143,34 +2158,34 @@
         <v>5.1</v>
       </c>
       <c r="O4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P4">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="Q4">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="R4">
+        <v>3.8</v>
+      </c>
+      <c r="S4">
         <v>3.7</v>
       </c>
-      <c r="S4">
-        <v>4</v>
-      </c>
       <c r="U4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V4">
         <v>0</v>
       </c>
       <c r="W4">
-        <v>54.8</v>
+        <v>54.9</v>
       </c>
       <c r="X4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Z4">
         <v>3</v>
@@ -2179,34 +2194,34 @@
         <v>2</v>
       </c>
       <c r="AB4">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC4">
-        <v>92.59999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="AD4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AE4">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AF4">
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>18.8</v>
+        <v>41.3</v>
       </c>
       <c r="AH4">
         <v>58.7</v>
       </c>
       <c r="AI4">
-        <v>44.4</v>
+        <v>45.1</v>
       </c>
       <c r="AJ4">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK4">
-        <v>1.1766</v>
+        <v>1.1765</v>
       </c>
       <c r="AL4">
         <v>1268</v>
@@ -2215,19 +2230,19 @@
         <v>1012.9</v>
       </c>
       <c r="AN4">
-        <v>46.1</v>
+        <v>46.5</v>
       </c>
       <c r="AO4">
-        <v>78</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AP4">
-        <v>35</v>
+        <v>35.2</v>
       </c>
       <c r="AQ4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AR4">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="AS4">
         <v>0</v>
@@ -2236,22 +2251,22 @@
         <v>0</v>
       </c>
       <c r="AU4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AV4">
         <v>0.9</v>
       </c>
       <c r="AW4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AX4">
         <v>8.199999999999999</v>
       </c>
       <c r="AY4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AZ4">
-        <v>56.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="BA4">
         <v>5</v>
@@ -2286,28 +2301,28 @@
         <v>135</v>
       </c>
       <c r="J5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K5">
-        <v>85.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="L5">
-        <v>47.3</v>
+        <v>46.3</v>
       </c>
       <c r="M5" t="s">
         <v>148</v>
       </c>
       <c r="N5">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P5">
         <v>-0.3</v>
       </c>
       <c r="Q5">
-        <v>-1.8</v>
+        <v>-1.9</v>
       </c>
       <c r="R5">
         <v>-2.6</v>
@@ -2316,19 +2331,19 @@
         <v>-2.3</v>
       </c>
       <c r="U5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V5">
         <v>1.7</v>
       </c>
       <c r="W5">
-        <v>58</v>
+        <v>57.8</v>
       </c>
       <c r="X5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Z5">
         <v>5</v>
@@ -2337,16 +2352,16 @@
         <v>4</v>
       </c>
       <c r="AB5">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC5">
-        <v>93.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AD5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AE5">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AF5">
         <v>0</v>
@@ -2358,31 +2373,31 @@
         <v>50.6</v>
       </c>
       <c r="AI5">
-        <v>55.9</v>
+        <v>56.2</v>
       </c>
       <c r="AJ5">
         <v>1.9</v>
       </c>
       <c r="AK5">
-        <v>1.1425</v>
+        <v>1.1426</v>
       </c>
       <c r="AL5">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="AM5">
-        <v>997.1</v>
+        <v>997.3</v>
       </c>
       <c r="AN5">
-        <v>62.8</v>
+        <v>62.5</v>
       </c>
       <c r="AO5">
         <v>83.59999999999999</v>
       </c>
       <c r="AP5">
-        <v>50.8</v>
+        <v>50.4</v>
       </c>
       <c r="AQ5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AR5">
         <v>-1.4</v>
@@ -2394,22 +2409,22 @@
         <v>0</v>
       </c>
       <c r="AU5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AV5">
         <v>13.7</v>
       </c>
       <c r="AW5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AX5">
         <v>11.7</v>
       </c>
       <c r="AY5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AZ5">
-        <v>603.3</v>
+        <v>633.3</v>
       </c>
       <c r="BA5">
         <v>5</v>
@@ -2447,46 +2462,46 @@
         <v>142</v>
       </c>
       <c r="K6">
-        <v>83.90000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="L6">
-        <v>72.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="M6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N6">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="O6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P6">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="Q6">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="R6">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S6">
-        <v>-2.7</v>
+        <v>-3.1</v>
       </c>
       <c r="U6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V6">
         <v>35.2</v>
       </c>
       <c r="W6">
-        <v>63.3</v>
+        <v>63.5</v>
       </c>
       <c r="X6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Y6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Z6">
         <v>8</v>
@@ -2498,13 +2513,13 @@
         <v>4</v>
       </c>
       <c r="AC6">
-        <v>87.59999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="AD6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AE6">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AF6">
         <v>2</v>
@@ -2516,34 +2531,34 @@
         <v>0</v>
       </c>
       <c r="AI6">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="AJ6">
         <v>0.5</v>
       </c>
       <c r="AK6">
-        <v>1.1266</v>
+        <v>1.1255</v>
       </c>
       <c r="AL6">
-        <v>2533</v>
+        <v>2570</v>
       </c>
       <c r="AM6">
         <v>983.9</v>
       </c>
       <c r="AN6">
-        <v>72.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="AO6">
-        <v>82.2</v>
+        <v>82.8</v>
       </c>
       <c r="AP6">
-        <v>75.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AQ6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AR6">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AS6">
         <v>0</v>
@@ -2552,22 +2567,22 @@
         <v>0</v>
       </c>
       <c r="AU6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AV6">
         <v>39.2</v>
       </c>
       <c r="AW6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AX6">
-        <v>11.7</v>
+        <v>14.5</v>
       </c>
       <c r="AY6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AZ6">
-        <v>103.1</v>
+        <v>132.9</v>
       </c>
       <c r="BA6">
         <v>5</v>
@@ -2602,49 +2617,49 @@
         <v>136</v>
       </c>
       <c r="J7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K7">
-        <v>74.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="L7">
-        <v>57.9</v>
+        <v>54.9</v>
       </c>
       <c r="M7" t="s">
         <v>148</v>
       </c>
       <c r="N7">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="O7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P7">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q7">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="R7">
-        <v>0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="S7">
-        <v>-2.7</v>
+        <v>-3.5</v>
       </c>
       <c r="U7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V7">
         <v>1.8</v>
       </c>
       <c r="W7">
-        <v>55.3</v>
+        <v>55.1</v>
       </c>
       <c r="X7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Z7">
         <v>3</v>
@@ -2653,55 +2668,55 @@
         <v>2</v>
       </c>
       <c r="AB7">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AC7">
         <v>93.2</v>
       </c>
       <c r="AD7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AE7">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AF7">
         <v>1</v>
       </c>
       <c r="AG7">
-        <v>64.40000000000001</v>
+        <v>41.9</v>
       </c>
       <c r="AH7">
         <v>33.7</v>
       </c>
       <c r="AI7">
-        <v>37.5</v>
+        <v>41.1</v>
       </c>
       <c r="AJ7">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AK7">
-        <v>1.1726</v>
+        <v>1.1731</v>
       </c>
       <c r="AL7">
-        <v>1290</v>
+        <v>1281</v>
       </c>
       <c r="AM7">
-        <v>1004</v>
+        <v>1004.1</v>
       </c>
       <c r="AN7">
-        <v>59</v>
+        <v>58.2</v>
       </c>
       <c r="AO7">
-        <v>73.8</v>
+        <v>73.7</v>
       </c>
       <c r="AP7">
-        <v>59.9</v>
+        <v>58.7</v>
       </c>
       <c r="AQ7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AR7">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AS7">
         <v>0</v>
@@ -2710,19 +2725,19 @@
         <v>0</v>
       </c>
       <c r="AU7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AV7">
         <v>3.7</v>
       </c>
       <c r="AW7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AX7">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AY7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AZ7">
         <v>0</v>
@@ -2763,19 +2778,19 @@
         <v>143</v>
       </c>
       <c r="K8">
-        <v>87.40000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="L8">
-        <v>58.5</v>
+        <v>55</v>
       </c>
       <c r="M8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N8">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -2790,7 +2805,7 @@
         <v>-0</v>
       </c>
       <c r="U8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V8">
         <v>19.9</v>
@@ -2799,10 +2814,10 @@
         <v>50</v>
       </c>
       <c r="X8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2814,10 +2829,10 @@
         <v>0</v>
       </c>
       <c r="AC8">
-        <v>82.3</v>
+        <v>81.7</v>
       </c>
       <c r="AD8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AE8">
         <v>0.1</v>
@@ -2832,10 +2847,10 @@
         <v>70</v>
       </c>
       <c r="AI8">
-        <v>15.2</v>
+        <v>6.6</v>
       </c>
       <c r="AJ8">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="AK8">
         <v>1.153</v>
@@ -2844,19 +2859,19 @@
         <v>1850</v>
       </c>
       <c r="AM8">
-        <v>987.5</v>
+        <v>987.6</v>
       </c>
       <c r="AN8">
-        <v>70.5</v>
+        <v>69.8</v>
       </c>
       <c r="AO8">
-        <v>85.2</v>
+        <v>85.5</v>
       </c>
       <c r="AP8">
-        <v>62</v>
+        <v>60.6</v>
       </c>
       <c r="AQ8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AR8">
         <v>6.1</v>
@@ -2868,22 +2883,22 @@
         <v>0</v>
       </c>
       <c r="AU8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AV8">
         <v>28.3</v>
       </c>
       <c r="AW8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AX8">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="AY8" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AZ8">
-        <v>48.3</v>
+        <v>78.2</v>
       </c>
       <c r="BA8">
         <v>5</v>
@@ -2927,13 +2942,13 @@
         <v>63.1</v>
       </c>
       <c r="M9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N9">
         <v>9.5</v>
       </c>
       <c r="O9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P9">
         <v>6.3</v>
@@ -2948,7 +2963,7 @@
         <v>-0.6</v>
       </c>
       <c r="U9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V9">
         <v>26.5</v>
@@ -2957,10 +2972,10 @@
         <v>66.3</v>
       </c>
       <c r="X9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Y9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Z9">
         <v>10</v>
@@ -2975,7 +2990,7 @@
         <v>83.40000000000001</v>
       </c>
       <c r="AD9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AE9">
         <v>8.199999999999999</v>
@@ -3014,10 +3029,10 @@
         <v>66.59999999999999</v>
       </c>
       <c r="AQ9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AR9">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AS9">
         <v>0</v>
@@ -3026,22 +3041,22 @@
         <v>0</v>
       </c>
       <c r="AU9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AV9">
         <v>29.5</v>
       </c>
       <c r="AW9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AX9">
         <v>21.6</v>
       </c>
       <c r="AY9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AZ9">
-        <v>178.8</v>
+        <v>208.7</v>
       </c>
       <c r="BA9">
         <v>5</v>
@@ -3076,7 +3091,7 @@
         <v>137</v>
       </c>
       <c r="J10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K10">
         <v>87.5</v>
@@ -3085,13 +3100,13 @@
         <v>63.3</v>
       </c>
       <c r="M10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N10">
         <v>7</v>
       </c>
       <c r="O10" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -3106,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V10">
         <v>17.6</v>
@@ -3115,10 +3130,10 @@
         <v>50</v>
       </c>
       <c r="X10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -3133,7 +3148,7 @@
         <v>87.3</v>
       </c>
       <c r="AD10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AE10">
         <v>2.8</v>
@@ -3172,10 +3187,10 @@
         <v>68.8</v>
       </c>
       <c r="AQ10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AR10">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="AS10">
         <v>0</v>
@@ -3184,22 +3199,22 @@
         <v>0</v>
       </c>
       <c r="AU10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AV10">
         <v>12.9</v>
       </c>
       <c r="AW10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AX10">
         <v>15.6</v>
       </c>
       <c r="AY10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AZ10">
-        <v>153.8</v>
+        <v>183.7</v>
       </c>
       <c r="BA10">
         <v>5</v>
@@ -3243,13 +3258,13 @@
         <v>56.7</v>
       </c>
       <c r="M11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N11">
         <v>8.9</v>
       </c>
       <c r="O11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P11">
         <v>7.6</v>
@@ -3264,7 +3279,7 @@
         <v>-1.5</v>
       </c>
       <c r="U11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V11">
         <v>19.2</v>
@@ -3273,10 +3288,10 @@
         <v>67.90000000000001</v>
       </c>
       <c r="X11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Y11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Z11">
         <v>11</v>
@@ -3291,7 +3306,7 @@
         <v>86.3</v>
       </c>
       <c r="AD11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AE11">
         <v>6.6</v>
@@ -3330,7 +3345,7 @@
         <v>61.1</v>
       </c>
       <c r="AQ11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AR11">
         <v>5.6</v>
@@ -3342,22 +3357,22 @@
         <v>0</v>
       </c>
       <c r="AU11" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AV11">
         <v>22.6</v>
       </c>
       <c r="AW11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AX11">
         <v>13.3</v>
       </c>
       <c r="AY11" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AZ11">
-        <v>128</v>
+        <v>157.9</v>
       </c>
       <c r="BA11">
         <v>5</v>
@@ -3392,7 +3407,7 @@
         <v>135</v>
       </c>
       <c r="J12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K12">
         <v>92</v>
@@ -3401,13 +3416,13 @@
         <v>18.6</v>
       </c>
       <c r="M12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N12">
         <v>8.699999999999999</v>
       </c>
       <c r="O12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="P12">
         <v>4</v>
@@ -3422,7 +3437,7 @@
         <v>-8.4</v>
       </c>
       <c r="U12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V12">
         <v>3.2</v>
@@ -3431,10 +3446,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="X12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Y12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Z12">
         <v>12</v>
@@ -3449,7 +3464,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="AD12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AE12">
         <v>1.5</v>
@@ -3488,10 +3503,10 @@
         <v>20.5</v>
       </c>
       <c r="AQ12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AR12">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="AS12">
         <v>0</v>
@@ -3500,22 +3515,22 @@
         <v>0</v>
       </c>
       <c r="AU12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AV12">
         <v>1.8</v>
       </c>
       <c r="AW12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AX12">
         <v>8.5</v>
       </c>
       <c r="AY12" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AZ12">
-        <v>693.8</v>
+        <v>723.7</v>
       </c>
       <c r="BA12">
         <v>5</v>
@@ -3550,7 +3565,7 @@
         <v>135</v>
       </c>
       <c r="J13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K13">
         <v>76.90000000000001</v>
@@ -3559,13 +3574,13 @@
         <v>66.5</v>
       </c>
       <c r="M13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N13">
         <v>8</v>
       </c>
       <c r="O13" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="P13">
         <v>6.8</v>
@@ -3580,7 +3595,7 @@
         <v>-4.3</v>
       </c>
       <c r="U13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V13">
         <v>2.4</v>
@@ -3589,10 +3604,10 @@
         <v>59.1</v>
       </c>
       <c r="X13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Z13">
         <v>6</v>
@@ -3607,7 +3622,7 @@
         <v>90.2</v>
       </c>
       <c r="AD13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AE13">
         <v>4.2</v>
@@ -3646,7 +3661,7 @@
         <v>72.09999999999999</v>
       </c>
       <c r="AQ13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AR13">
         <v>4.2</v>
@@ -3658,22 +3673,22 @@
         <v>0</v>
       </c>
       <c r="AU13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AV13">
         <v>1.3</v>
       </c>
       <c r="AW13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AX13">
         <v>14.4</v>
       </c>
       <c r="AY13" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AZ13">
-        <v>153.9</v>
+        <v>183.8</v>
       </c>
       <c r="BA13">
         <v>5</v>
@@ -3708,7 +3723,7 @@
         <v>135</v>
       </c>
       <c r="J14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K14">
         <v>85.5</v>
@@ -3717,13 +3732,13 @@
         <v>31.2</v>
       </c>
       <c r="M14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N14">
         <v>10.8</v>
       </c>
       <c r="O14" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="P14">
         <v>10.2</v>
@@ -3738,7 +3753,7 @@
         <v>-4.3</v>
       </c>
       <c r="U14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -3747,10 +3762,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="X14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Y14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Z14">
         <v>10</v>
@@ -3765,7 +3780,7 @@
         <v>93.2</v>
       </c>
       <c r="AD14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AE14">
         <v>8.800000000000001</v>
@@ -3804,7 +3819,7 @@
         <v>39.2</v>
       </c>
       <c r="AQ14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AR14">
         <v>11.2</v>
@@ -3816,22 +3831,22 @@
         <v>0</v>
       </c>
       <c r="AU14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AV14">
         <v>0</v>
       </c>
       <c r="AW14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AX14">
         <v>6.9</v>
       </c>
       <c r="AY14" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AZ14">
-        <v>559.3</v>
+        <v>589.3</v>
       </c>
       <c r="BA14">
         <v>5</v>
@@ -3875,13 +3890,13 @@
         <v>67.2</v>
       </c>
       <c r="M15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N15">
         <v>2.5</v>
       </c>
       <c r="O15" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -3896,7 +3911,7 @@
         <v>-0</v>
       </c>
       <c r="U15" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V15">
         <v>9.6</v>
@@ -3905,10 +3920,10 @@
         <v>50</v>
       </c>
       <c r="X15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -3923,7 +3938,7 @@
         <v>84.7</v>
       </c>
       <c r="AD15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AE15">
         <v>0.3</v>
@@ -3962,7 +3977,7 @@
         <v>69.7</v>
       </c>
       <c r="AQ15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AR15">
         <v>7.6</v>
@@ -3974,22 +3989,22 @@
         <v>0</v>
       </c>
       <c r="AU15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AV15">
         <v>16.4</v>
       </c>
       <c r="AW15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AX15">
         <v>18.8</v>
       </c>
       <c r="AY15" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AZ15">
-        <v>86.90000000000001</v>
+        <v>116.9</v>
       </c>
       <c r="BA15">
         <v>5</v>
@@ -4024,7 +4039,7 @@
         <v>138</v>
       </c>
       <c r="J16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K16">
         <v>70.7</v>
@@ -4039,7 +4054,7 @@
         <v>4.4</v>
       </c>
       <c r="O16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P16">
         <v>-0.4</v>
@@ -4054,7 +4069,7 @@
         <v>3.7</v>
       </c>
       <c r="U16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V16">
         <v>0.3</v>
@@ -4063,10 +4078,10 @@
         <v>51.9</v>
       </c>
       <c r="X16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y16" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Z16">
         <v>1</v>
@@ -4081,7 +4096,7 @@
         <v>87.59999999999999</v>
       </c>
       <c r="AD16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AE16">
         <v>0.3</v>
@@ -4120,7 +4135,7 @@
         <v>61.8</v>
       </c>
       <c r="AQ16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AR16">
         <v>-0.2</v>
@@ -4132,22 +4147,22 @@
         <v>0</v>
       </c>
       <c r="AU16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AV16">
         <v>0.2</v>
       </c>
       <c r="AW16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AX16">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="AY16" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AZ16">
-        <v>565</v>
+        <v>595</v>
       </c>
       <c r="BA16">
         <v>5</v>
@@ -4272,223 +4287,223 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>52</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="BZ1" s="1" t="s">
         <v>49</v>
@@ -4497,16 +4512,16 @@
         <v>48</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:83">
@@ -4523,43 +4538,43 @@
         <v>119</v>
       </c>
       <c r="E2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F2" t="s">
         <v>107</v>
       </c>
       <c r="G2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="H2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I2" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="J2">
-        <v>56.1</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K2">
-        <v>11.3</v>
+        <v>10.8</v>
       </c>
       <c r="L2">
         <v>5</v>
       </c>
       <c r="M2">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="N2">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="Q2">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="R2">
         <v>100</v>
@@ -4568,22 +4583,22 @@
         <v>0</v>
       </c>
       <c r="T2" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U2" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="V2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="W2">
         <v>0.5833</v>
       </c>
       <c r="X2">
-        <v>15</v>
+        <v>14.3</v>
       </c>
       <c r="Y2">
-        <v>91.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="Z2">
         <v>59.8</v>
@@ -4604,25 +4619,25 @@
         <v>139</v>
       </c>
       <c r="AF2">
-        <v>83.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="AG2">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="AH2">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="AI2">
         <v>26.6</v>
       </c>
       <c r="AJ2">
-        <v>1013.2</v>
+        <v>1013</v>
       </c>
       <c r="AK2">
-        <v>1015.4</v>
+        <v>1015.2</v>
       </c>
       <c r="AL2">
-        <v>46.7</v>
+        <v>47.3</v>
       </c>
       <c r="AM2">
         <v>0</v>
@@ -4631,22 +4646,22 @@
         <v>0</v>
       </c>
       <c r="AO2">
-        <v>152.2</v>
+        <v>150.9</v>
       </c>
       <c r="AP2">
         <v>2</v>
       </c>
       <c r="AQ2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR2">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="AS2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AT2">
-        <v>298.7</v>
+        <v>298.9</v>
       </c>
       <c r="AU2">
         <v>2.3</v>
@@ -4655,7 +4670,7 @@
         <v>-2.9</v>
       </c>
       <c r="AW2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="AX2">
         <v>1.9</v>
@@ -4667,7 +4682,7 @@
         <v>5.1</v>
       </c>
       <c r="BA2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="BB2">
         <v>1.7</v>
@@ -4688,13 +4703,13 @@
         <v>0.14</v>
       </c>
       <c r="BH2">
-        <v>1.1662</v>
+        <v>1.1661</v>
       </c>
       <c r="BI2" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ2">
-        <v>1591</v>
+        <v>1595</v>
       </c>
       <c r="BK2" t="s">
         <v>133</v>
@@ -4709,7 +4724,7 @@
         <v>5.6</v>
       </c>
       <c r="BO2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP2">
         <v>0.3</v>
@@ -4721,43 +4736,43 @@
         <v>1.026</v>
       </c>
       <c r="BS2">
-        <v>63.8</v>
+        <v>63.7</v>
       </c>
       <c r="BT2">
-        <v>57.3</v>
+        <v>57.2</v>
       </c>
       <c r="BU2">
-        <v>58.4</v>
+        <v>58.3</v>
       </c>
       <c r="BV2">
         <v>51.9</v>
       </c>
       <c r="BW2">
-        <v>60</v>
+        <v>60.1</v>
       </c>
       <c r="BX2">
         <v>0</v>
       </c>
       <c r="BY2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ2">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="CA2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB2">
         <v>82</v>
       </c>
       <c r="CC2">
-        <v>83</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="CD2">
         <v>10</v>
       </c>
       <c r="CE2">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="3" spans="1:83">
@@ -4774,40 +4789,40 @@
         <v>119</v>
       </c>
       <c r="E3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="G3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="H3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I3" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="J3">
-        <v>56.1</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K3">
-        <v>12.3</v>
+        <v>11.8</v>
       </c>
       <c r="L3">
         <v>5</v>
       </c>
       <c r="M3">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="N3">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Q3">
         <v>1.3</v>
@@ -4819,25 +4834,25 @@
         <v>0</v>
       </c>
       <c r="T3" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U3" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="V3" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="W3">
         <v>0.5833</v>
       </c>
       <c r="X3">
-        <v>14.8</v>
+        <v>14.3</v>
       </c>
       <c r="Y3">
-        <v>91.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="Z3">
-        <v>60.1</v>
+        <v>60.2</v>
       </c>
       <c r="AA3">
         <v>0.88</v>
@@ -4852,13 +4867,13 @@
         <v>0.6</v>
       </c>
       <c r="AE3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AF3">
         <v>84.09999999999999</v>
       </c>
       <c r="AG3">
-        <v>82</v>
+        <v>81.8</v>
       </c>
       <c r="AH3">
         <v>44.5</v>
@@ -4867,13 +4882,13 @@
         <v>25.3</v>
       </c>
       <c r="AJ3">
-        <v>1012.9</v>
+        <v>1012.7</v>
       </c>
       <c r="AK3">
-        <v>1015.2</v>
+        <v>1015</v>
       </c>
       <c r="AL3">
-        <v>18.6</v>
+        <v>19.5</v>
       </c>
       <c r="AM3">
         <v>0</v>
@@ -4882,7 +4897,7 @@
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>152.3</v>
+        <v>151.7</v>
       </c>
       <c r="AP3">
         <v>3</v>
@@ -4891,10 +4906,10 @@
         <v>8.6</v>
       </c>
       <c r="AR3">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="AS3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AT3">
         <v>297.6</v>
@@ -4912,7 +4927,7 @@
         <v>2</v>
       </c>
       <c r="AY3">
-        <v>-2</v>
+        <v>-1.9</v>
       </c>
       <c r="AZ3">
         <v>5.1</v>
@@ -4942,10 +4957,10 @@
         <v>1.1636</v>
       </c>
       <c r="BI3" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ3">
-        <v>1670</v>
+        <v>1673</v>
       </c>
       <c r="BK3" t="s">
         <v>133</v>
@@ -4984,25 +4999,25 @@
         <v>52.2</v>
       </c>
       <c r="BW3">
-        <v>59.2</v>
+        <v>59.3</v>
       </c>
       <c r="BX3">
         <v>0</v>
       </c>
       <c r="BY3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ3">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="CA3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB3">
         <v>83</v>
       </c>
       <c r="CC3">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="CD3">
         <v>10</v>
@@ -5025,43 +5040,43 @@
         <v>119</v>
       </c>
       <c r="E4" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F4" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="G4" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="H4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I4" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="J4">
-        <v>56.1</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K4">
-        <v>13.3</v>
+        <v>12.8</v>
       </c>
       <c r="L4">
         <v>5</v>
       </c>
       <c r="M4">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="N4">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="Q4">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -5070,25 +5085,25 @@
         <v>0</v>
       </c>
       <c r="T4" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U4" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="V4" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="W4">
         <v>0.5833</v>
       </c>
       <c r="X4">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="Y4">
-        <v>91.59999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="Z4">
-        <v>60</v>
+        <v>60.2</v>
       </c>
       <c r="AA4">
         <v>0.88</v>
@@ -5103,28 +5118,28 @@
         <v>0.6</v>
       </c>
       <c r="AE4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AF4">
-        <v>85</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="AG4">
-        <v>81.8</v>
+        <v>81.5</v>
       </c>
       <c r="AH4">
-        <v>44.4</v>
+        <v>44.6</v>
       </c>
       <c r="AI4">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="AJ4">
-        <v>1012.7</v>
+        <v>1012.5</v>
       </c>
       <c r="AK4">
-        <v>1014.9</v>
+        <v>1014.7</v>
       </c>
       <c r="AL4">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AM4">
         <v>0</v>
@@ -5133,7 +5148,7 @@
         <v>0</v>
       </c>
       <c r="AO4">
-        <v>154.6</v>
+        <v>153.4</v>
       </c>
       <c r="AP4">
         <v>4</v>
@@ -5142,37 +5157,37 @@
         <v>8.5</v>
       </c>
       <c r="AR4">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="AS4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AT4">
-        <v>298.8</v>
+        <v>298.3</v>
       </c>
       <c r="AU4">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AV4">
-        <v>-2.9</v>
+        <v>-2.8</v>
       </c>
       <c r="AW4">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="AX4">
         <v>1.9</v>
       </c>
       <c r="AY4">
-        <v>-2.1</v>
+        <v>-2</v>
       </c>
       <c r="AZ4">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BA4">
         <v>7.9</v>
       </c>
       <c r="BB4">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="BC4">
         <v>1.2</v>
@@ -5190,13 +5205,13 @@
         <v>0.14</v>
       </c>
       <c r="BH4">
-        <v>1.1617</v>
+        <v>1.1616</v>
       </c>
       <c r="BI4" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ4">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="BK4" t="s">
         <v>133</v>
@@ -5205,61 +5220,61 @@
         <v>135</v>
       </c>
       <c r="BM4">
-        <v>60.9</v>
+        <v>61.1</v>
       </c>
       <c r="BN4">
         <v>6</v>
       </c>
       <c r="BO4">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BP4">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="BQ4">
         <v>0</v>
       </c>
       <c r="BR4">
-        <v>1.026</v>
+        <v>1.027</v>
       </c>
       <c r="BS4">
-        <v>63.9</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="BT4">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
       <c r="BU4">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
       <c r="BV4">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
       <c r="BW4">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
       <c r="BX4">
         <v>0</v>
       </c>
       <c r="BY4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ4">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="CA4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB4">
         <v>84</v>
       </c>
       <c r="CC4">
-        <v>84.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="CD4">
         <v>10</v>
       </c>
       <c r="CE4">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="5" spans="1:83">
@@ -5276,40 +5291,40 @@
         <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F5" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="H5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I5" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="J5">
-        <v>56.1</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K5">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="L5">
         <v>5</v>
       </c>
       <c r="M5">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="N5">
-        <v>1.88</v>
+        <v>2.22</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="Q5">
         <v>1.2</v>
@@ -5321,22 +5336,22 @@
         <v>0</v>
       </c>
       <c r="T5" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U5" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="V5" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="W5">
         <v>0.5833</v>
       </c>
       <c r="X5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y5">
-        <v>90.7</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Z5">
         <v>59.4</v>
@@ -5354,28 +5369,28 @@
         <v>0.6</v>
       </c>
       <c r="AE5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AF5">
-        <v>84.59999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="AG5">
-        <v>80.59999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AH5">
-        <v>44.2</v>
+        <v>44.6</v>
       </c>
       <c r="AI5">
-        <v>24.9</v>
+        <v>25.3</v>
       </c>
       <c r="AJ5">
         <v>1012.4</v>
       </c>
       <c r="AK5">
-        <v>1014.7</v>
+        <v>1014.6</v>
       </c>
       <c r="AL5">
-        <v>35</v>
+        <v>13.5</v>
       </c>
       <c r="AM5">
         <v>0</v>
@@ -5384,46 +5399,46 @@
         <v>0</v>
       </c>
       <c r="AO5">
-        <v>157.9</v>
+        <v>155.8</v>
       </c>
       <c r="AP5">
         <v>4</v>
       </c>
       <c r="AQ5">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AR5">
-        <v>14.1</v>
+        <v>14.5</v>
       </c>
       <c r="AS5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AT5">
-        <v>299.7</v>
+        <v>300.4</v>
       </c>
       <c r="AU5">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AV5">
-        <v>-2.9</v>
+        <v>-3.1</v>
       </c>
       <c r="AW5">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="AX5">
         <v>1.7</v>
       </c>
       <c r="AY5">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AZ5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA5">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="BB5">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="BC5">
         <v>1.2</v>
@@ -5441,13 +5456,13 @@
         <v>0.14</v>
       </c>
       <c r="BH5">
-        <v>1.1622</v>
+        <v>1.1623</v>
       </c>
       <c r="BI5" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ5">
-        <v>1715</v>
+        <v>1710</v>
       </c>
       <c r="BK5" t="s">
         <v>133</v>
@@ -5462,10 +5477,10 @@
         <v>6</v>
       </c>
       <c r="BO5">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BP5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="BQ5">
         <v>0</v>
@@ -5474,43 +5489,43 @@
         <v>1.025</v>
       </c>
       <c r="BS5">
-        <v>63.3</v>
+        <v>63.4</v>
       </c>
       <c r="BT5">
-        <v>57.1</v>
+        <v>57</v>
       </c>
       <c r="BU5">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
       <c r="BV5">
         <v>52.1</v>
       </c>
       <c r="BW5">
-        <v>59</v>
+        <v>59.1</v>
       </c>
       <c r="BX5">
         <v>0</v>
       </c>
       <c r="BY5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ5">
-        <v>7.1</v>
+        <v>5.9</v>
       </c>
       <c r="CA5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB5">
         <v>83</v>
       </c>
       <c r="CC5">
-        <v>84.90000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="CD5">
         <v>10</v>
       </c>
       <c r="CE5">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:83">
@@ -5527,31 +5542,31 @@
         <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F6" t="s">
         <v>108</v>
       </c>
       <c r="G6" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="H6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I6" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="J6">
-        <v>458.6</v>
+        <v>488.5</v>
       </c>
       <c r="K6">
-        <v>16.8</v>
+        <v>16.3</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="N6">
         <v>1.29</v>
@@ -5560,10 +5575,10 @@
         <v>0.5</v>
       </c>
       <c r="P6">
-        <v>8.5</v>
+        <v>5.1</v>
       </c>
       <c r="Q6">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -5572,25 +5587,25 @@
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U6" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="V6" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="W6">
         <v>0.0833</v>
       </c>
       <c r="X6">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="Y6">
         <v>90.3</v>
       </c>
       <c r="Z6">
-        <v>64.40000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="AA6">
         <v>0.92</v>
@@ -5605,28 +5620,28 @@
         <v>0.9</v>
       </c>
       <c r="AE6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AF6">
         <v>87.3</v>
       </c>
       <c r="AG6">
-        <v>84.8</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="AH6">
-        <v>49.6</v>
+        <v>50.1</v>
       </c>
       <c r="AI6">
-        <v>29.6</v>
+        <v>29.9</v>
       </c>
       <c r="AJ6">
-        <v>1012.8</v>
+        <v>1013.2</v>
       </c>
       <c r="AK6">
-        <v>1015.4</v>
+        <v>1015.7</v>
       </c>
       <c r="AL6">
-        <v>93.7</v>
+        <v>44.7</v>
       </c>
       <c r="AM6">
         <v>0.3</v>
@@ -5635,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AO6">
-        <v>156.8</v>
+        <v>153.7</v>
       </c>
       <c r="AP6">
         <v>0</v>
@@ -5644,37 +5659,37 @@
         <v>5</v>
       </c>
       <c r="AR6">
-        <v>10.6</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AT6">
-        <v>287.8</v>
+        <v>283.6</v>
       </c>
       <c r="AU6">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV6">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AW6">
         <v>5</v>
       </c>
       <c r="AX6">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AY6">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AZ6">
         <v>4.4</v>
       </c>
       <c r="BA6">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="BB6">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BC6">
         <v>0.6</v>
@@ -5692,13 +5707,13 @@
         <v>0.12</v>
       </c>
       <c r="BH6">
-        <v>1.156</v>
+        <v>1.1562</v>
       </c>
       <c r="BI6" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ6">
-        <v>1880</v>
+        <v>1871</v>
       </c>
       <c r="BK6" t="s">
         <v>133</v>
@@ -5707,13 +5722,13 @@
         <v>135</v>
       </c>
       <c r="BM6">
-        <v>66</v>
+        <v>66.3</v>
       </c>
       <c r="BN6">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="BO6">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="BP6">
         <v>0</v>
@@ -5722,19 +5737,19 @@
         <v>0</v>
       </c>
       <c r="BR6">
-        <v>1.038</v>
+        <v>1.039</v>
       </c>
       <c r="BS6">
-        <v>66.8</v>
+        <v>67</v>
       </c>
       <c r="BT6">
-        <v>64.3</v>
+        <v>64.7</v>
       </c>
       <c r="BU6">
-        <v>57.9</v>
+        <v>57.8</v>
       </c>
       <c r="BV6">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="BW6">
         <v>56</v>
@@ -5743,19 +5758,19 @@
         <v>0.2</v>
       </c>
       <c r="BY6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ6">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="CA6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB6">
         <v>87</v>
       </c>
       <c r="CC6">
-        <v>86.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="CD6">
         <v>6</v>
@@ -5778,25 +5793,25 @@
         <v>120</v>
       </c>
       <c r="E7" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F7" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="G7" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="H7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I7" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="J7">
-        <v>458.6</v>
+        <v>488.5</v>
       </c>
       <c r="K7">
-        <v>17.8</v>
+        <v>17.3</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -5823,13 +5838,13 @@
         <v>56.2</v>
       </c>
       <c r="T7" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U7" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="V7" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W7">
         <v>0.0833</v>
@@ -5898,7 +5913,7 @@
         <v>7</v>
       </c>
       <c r="AS7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AT7">
         <v>75.59999999999999</v>
@@ -5946,7 +5961,7 @@
         <v>1.1612</v>
       </c>
       <c r="BI7" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ7">
         <v>1705</v>
@@ -5994,13 +6009,13 @@
         <v>0.2</v>
       </c>
       <c r="BY7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ7">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="CA7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB7">
         <v>84</v>
@@ -6029,25 +6044,25 @@
         <v>120</v>
       </c>
       <c r="E8" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F8" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G8" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="H8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I8" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="J8">
-        <v>458.6</v>
+        <v>488.5</v>
       </c>
       <c r="K8">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="L8">
         <v>5</v>
@@ -6074,13 +6089,13 @@
         <v>75</v>
       </c>
       <c r="T8" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U8" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="V8" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="W8">
         <v>0.0833</v>
@@ -6107,7 +6122,7 @@
         <v>0.9</v>
       </c>
       <c r="AE8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AF8">
         <v>80.40000000000001</v>
@@ -6149,7 +6164,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="AS8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AT8">
         <v>112.3</v>
@@ -6197,7 +6212,7 @@
         <v>1.169</v>
       </c>
       <c r="BI8" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ8">
         <v>1415</v>
@@ -6245,13 +6260,13 @@
         <v>0.2</v>
       </c>
       <c r="BY8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="CA8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB8">
         <v>80</v>
@@ -6280,25 +6295,25 @@
         <v>120</v>
       </c>
       <c r="E9" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F9" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G9" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="H9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I9" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="J9">
-        <v>458.6</v>
+        <v>488.5</v>
       </c>
       <c r="K9">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="L9">
         <v>5</v>
@@ -6325,13 +6340,13 @@
         <v>100</v>
       </c>
       <c r="T9" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U9" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="V9" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="W9">
         <v>0.0833</v>
@@ -6358,7 +6373,7 @@
         <v>0.9</v>
       </c>
       <c r="AE9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AF9">
         <v>78.7</v>
@@ -6400,7 +6415,7 @@
         <v>9.4</v>
       </c>
       <c r="AS9" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="AT9">
         <v>150.3</v>
@@ -6448,7 +6463,7 @@
         <v>1.1726</v>
       </c>
       <c r="BI9" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ9">
         <v>1288</v>
@@ -6496,13 +6511,13 @@
         <v>0.2</v>
       </c>
       <c r="BY9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ9">
         <v>6.4</v>
       </c>
       <c r="CA9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB9">
         <v>79</v>
@@ -6531,70 +6546,70 @@
         <v>119</v>
       </c>
       <c r="E10" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F10" t="s">
         <v>109</v>
       </c>
       <c r="G10" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="H10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I10" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="J10">
-        <v>56.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K10">
-        <v>16.8</v>
+        <v>16.3</v>
       </c>
       <c r="L10">
         <v>5</v>
       </c>
       <c r="M10">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="N10">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>20.1</v>
+        <v>21.8</v>
       </c>
       <c r="Q10">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="R10">
-        <v>18.8</v>
+        <v>75</v>
       </c>
       <c r="S10">
         <v>25</v>
       </c>
       <c r="T10" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U10" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="V10" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="W10">
         <v>0.1667</v>
       </c>
       <c r="X10">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y10">
-        <v>91.7</v>
+        <v>91.3</v>
       </c>
       <c r="Z10">
-        <v>60.4</v>
+        <v>61.2</v>
       </c>
       <c r="AA10">
         <v>0.88</v>
@@ -6609,28 +6624,28 @@
         <v>0.6</v>
       </c>
       <c r="AE10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AF10">
-        <v>81.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="AG10">
-        <v>77.2</v>
+        <v>77.8</v>
       </c>
       <c r="AH10">
-        <v>43.9</v>
+        <v>44.8</v>
       </c>
       <c r="AI10">
-        <v>28.8</v>
+        <v>29.3</v>
       </c>
       <c r="AJ10">
-        <v>1012.5</v>
+        <v>1012.6</v>
       </c>
       <c r="AK10">
-        <v>1014.7</v>
+        <v>1014.8</v>
       </c>
       <c r="AL10">
-        <v>11.3</v>
+        <v>24.9</v>
       </c>
       <c r="AM10">
         <v>0</v>
@@ -6639,7 +6654,7 @@
         <v>0</v>
       </c>
       <c r="AO10">
-        <v>159.1</v>
+        <v>151.9</v>
       </c>
       <c r="AP10">
         <v>0</v>
@@ -6648,37 +6663,37 @@
         <v>5.1</v>
       </c>
       <c r="AR10">
-        <v>11.2</v>
+        <v>11.6</v>
       </c>
       <c r="AS10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AT10">
-        <v>278</v>
+        <v>271.6</v>
       </c>
       <c r="AU10">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AV10">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="AW10">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX10">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="AY10">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="AZ10">
+        <v>3.8</v>
+      </c>
+      <c r="BA10">
         <v>3.7</v>
       </c>
-      <c r="BA10">
-        <v>4</v>
-      </c>
       <c r="BB10">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="BC10">
         <v>0.7</v>
@@ -6696,13 +6711,13 @@
         <v>0.14</v>
       </c>
       <c r="BH10">
-        <v>1.1691</v>
+        <v>1.1689</v>
       </c>
       <c r="BI10" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ10">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="BK10" t="s">
         <v>133</v>
@@ -6711,13 +6726,13 @@
         <v>135</v>
       </c>
       <c r="BM10">
-        <v>61.4</v>
+        <v>62.2</v>
       </c>
       <c r="BN10">
         <v>5.3</v>
       </c>
       <c r="BO10">
-        <v>5.4</v>
+        <v>6.3</v>
       </c>
       <c r="BP10">
         <v>0</v>
@@ -6726,19 +6741,19 @@
         <v>0</v>
       </c>
       <c r="BR10">
-        <v>1.027</v>
+        <v>1.029</v>
       </c>
       <c r="BS10">
-        <v>62.7</v>
+        <v>63.4</v>
       </c>
       <c r="BT10">
-        <v>59.4</v>
+        <v>60.3</v>
       </c>
       <c r="BU10">
-        <v>56.6</v>
+        <v>56.7</v>
       </c>
       <c r="BV10">
-        <v>51.8</v>
+        <v>52</v>
       </c>
       <c r="BW10">
         <v>62.4</v>
@@ -6747,25 +6762,25 @@
         <v>0</v>
       </c>
       <c r="BY10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ10">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="CA10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB10">
         <v>80</v>
       </c>
       <c r="CC10">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="CD10">
         <v>5</v>
       </c>
       <c r="CE10">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="11" spans="1:83">
@@ -6782,25 +6797,25 @@
         <v>119</v>
       </c>
       <c r="E11" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G11" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="H11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I11" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="J11">
-        <v>56.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K11">
-        <v>17.8</v>
+        <v>17.3</v>
       </c>
       <c r="L11">
         <v>5</v>
@@ -6827,13 +6842,13 @@
         <v>81.2</v>
       </c>
       <c r="T11" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U11" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="V11" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W11">
         <v>0.1667</v>
@@ -6860,7 +6875,7 @@
         <v>0.6</v>
       </c>
       <c r="AE11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AF11">
         <v>77.7</v>
@@ -6902,7 +6917,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="AS11" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="AT11">
         <v>316.6</v>
@@ -6950,7 +6965,7 @@
         <v>1.1773</v>
       </c>
       <c r="BI11" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ11">
         <v>1247</v>
@@ -6998,13 +7013,13 @@
         <v>0</v>
       </c>
       <c r="BY11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ11">
         <v>8.199999999999999</v>
       </c>
       <c r="CA11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB11">
         <v>76</v>
@@ -7033,25 +7048,25 @@
         <v>119</v>
       </c>
       <c r="E12" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F12" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="G12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="H12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I12" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="J12">
-        <v>56.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K12">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="L12">
         <v>5</v>
@@ -7078,13 +7093,13 @@
         <v>81.2</v>
       </c>
       <c r="T12" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U12" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="V12" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="W12">
         <v>0.1667</v>
@@ -7093,7 +7108,7 @@
         <v>6.4</v>
       </c>
       <c r="Y12">
-        <v>94.40000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="Z12">
         <v>49.5</v>
@@ -7153,7 +7168,7 @@
         <v>7.4</v>
       </c>
       <c r="AS12" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AT12">
         <v>18.5</v>
@@ -7201,7 +7216,7 @@
         <v>1.1842</v>
       </c>
       <c r="BI12" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ12">
         <v>1021</v>
@@ -7249,13 +7264,13 @@
         <v>0.4</v>
       </c>
       <c r="BY12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ12">
         <v>4.9</v>
       </c>
       <c r="CA12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB12">
         <v>74</v>
@@ -7284,25 +7299,25 @@
         <v>119</v>
       </c>
       <c r="E13" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F13" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="G13" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="H13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I13" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="J13">
-        <v>56.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K13">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="L13">
         <v>5</v>
@@ -7329,13 +7344,13 @@
         <v>81.2</v>
       </c>
       <c r="T13" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U13" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="V13" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="W13">
         <v>0.1667</v>
@@ -7344,7 +7359,7 @@
         <v>6.8</v>
       </c>
       <c r="Y13">
-        <v>94.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="Z13">
         <v>52.6</v>
@@ -7362,7 +7377,7 @@
         <v>0.6</v>
       </c>
       <c r="AE13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AF13">
         <v>72.40000000000001</v>
@@ -7404,7 +7419,7 @@
         <v>7.2</v>
       </c>
       <c r="AS13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AT13">
         <v>120.4</v>
@@ -7452,7 +7467,7 @@
         <v>1.1892</v>
       </c>
       <c r="BI13" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ13">
         <v>873</v>
@@ -7500,13 +7515,13 @@
         <v>0.9</v>
       </c>
       <c r="BY13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ13">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="CA13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB13">
         <v>72</v>
@@ -7535,43 +7550,43 @@
         <v>121</v>
       </c>
       <c r="E14" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F14" t="s">
         <v>109</v>
       </c>
       <c r="G14" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="H14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I14" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="J14">
-        <v>603.3</v>
+        <v>633.3</v>
       </c>
       <c r="K14">
-        <v>16.8</v>
+        <v>16.3</v>
       </c>
       <c r="L14">
         <v>5</v>
       </c>
       <c r="M14">
-        <v>0.7</v>
+        <v>0.53</v>
       </c>
       <c r="N14">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="O14">
         <v>0.63</v>
       </c>
       <c r="P14">
-        <v>45.9</v>
+        <v>46.7</v>
       </c>
       <c r="Q14">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R14">
         <v>18.8</v>
@@ -7580,25 +7595,25 @@
         <v>56.2</v>
       </c>
       <c r="T14" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U14" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="V14" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="W14">
         <v>0.1667</v>
       </c>
       <c r="X14">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="Y14">
-        <v>95.40000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="Z14">
-        <v>53.4</v>
+        <v>53.2</v>
       </c>
       <c r="AA14">
         <v>0.92</v>
@@ -7613,25 +7628,25 @@
         <v>0.3</v>
       </c>
       <c r="AE14" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AF14">
-        <v>85.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="AG14">
-        <v>85.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="AH14">
-        <v>62.6</v>
+        <v>61.8</v>
       </c>
       <c r="AI14">
-        <v>47.3</v>
+        <v>46.3</v>
       </c>
       <c r="AJ14">
-        <v>997.4</v>
+        <v>997.7</v>
       </c>
       <c r="AK14">
-        <v>1014.5</v>
+        <v>1014.9</v>
       </c>
       <c r="AL14">
         <v>91.40000000000001</v>
@@ -7643,34 +7658,34 @@
         <v>0</v>
       </c>
       <c r="AO14">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="AP14">
         <v>298</v>
       </c>
       <c r="AQ14">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AR14">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="AS14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AT14">
-        <v>48.7</v>
+        <v>48</v>
       </c>
       <c r="AU14">
-        <v>-2</v>
+        <v>-2.1</v>
       </c>
       <c r="AV14">
         <v>-0.3</v>
       </c>
       <c r="AW14">
-        <v>-3</v>
+        <v>-3.1</v>
       </c>
       <c r="AX14">
-        <v>-1.8</v>
+        <v>-1.9</v>
       </c>
       <c r="AY14">
         <v>-0.3</v>
@@ -7682,7 +7697,7 @@
         <v>-2.3</v>
       </c>
       <c r="BB14">
-        <v>-1.6</v>
+        <v>-1.7</v>
       </c>
       <c r="BC14">
         <v>0.4</v>
@@ -7700,13 +7715,13 @@
         <v>0.12</v>
       </c>
       <c r="BH14">
-        <v>1.1393</v>
+        <v>1.1397</v>
       </c>
       <c r="BI14" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ14">
-        <v>2273</v>
+        <v>2268</v>
       </c>
       <c r="BK14" t="s">
         <v>133</v>
@@ -7715,13 +7730,13 @@
         <v>135</v>
       </c>
       <c r="BM14">
-        <v>53.6</v>
+        <v>53.3</v>
       </c>
       <c r="BN14">
         <v>8.1</v>
       </c>
       <c r="BO14">
-        <v>-4.9</v>
+        <v>-5.1</v>
       </c>
       <c r="BP14">
         <v>-0</v>
@@ -7730,46 +7745,46 @@
         <v>0</v>
       </c>
       <c r="BR14">
-        <v>1.009</v>
+        <v>1.008</v>
       </c>
       <c r="BS14">
-        <v>52.7</v>
+        <v>52.5</v>
       </c>
       <c r="BT14">
-        <v>54.8</v>
+        <v>54.6</v>
       </c>
       <c r="BU14">
-        <v>54.5</v>
+        <v>54.4</v>
       </c>
       <c r="BV14">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="BW14">
-        <v>58.2</v>
+        <v>58.1</v>
       </c>
       <c r="BX14">
         <v>3.9</v>
       </c>
       <c r="BY14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ14">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="CA14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB14">
         <v>85</v>
       </c>
       <c r="CC14">
-        <v>85.09999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="CD14">
         <v>3</v>
       </c>
       <c r="CE14">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="15" spans="1:83">
@@ -7786,25 +7801,25 @@
         <v>121</v>
       </c>
       <c r="E15" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F15" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G15" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="H15" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I15" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="J15">
-        <v>603.3</v>
+        <v>633.3</v>
       </c>
       <c r="K15">
-        <v>17.8</v>
+        <v>17.3</v>
       </c>
       <c r="L15">
         <v>5</v>
@@ -7831,13 +7846,13 @@
         <v>56.2</v>
       </c>
       <c r="T15" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U15" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="V15" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W15">
         <v>0.1667</v>
@@ -7846,7 +7861,7 @@
         <v>6.5</v>
       </c>
       <c r="Y15">
-        <v>93.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="Z15">
         <v>56.6</v>
@@ -7906,7 +7921,7 @@
         <v>5.8</v>
       </c>
       <c r="AS15" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AT15">
         <v>78.2</v>
@@ -7954,7 +7969,7 @@
         <v>1.1418</v>
       </c>
       <c r="BI15" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ15">
         <v>2187</v>
@@ -8002,13 +8017,13 @@
         <v>13.7</v>
       </c>
       <c r="BY15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ15">
         <v>5.9</v>
       </c>
       <c r="CA15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB15">
         <v>83</v>
@@ -8037,25 +8052,25 @@
         <v>121</v>
       </c>
       <c r="E16" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F16" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="G16" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="H16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I16" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="J16">
-        <v>603.3</v>
+        <v>633.3</v>
       </c>
       <c r="K16">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="L16">
         <v>5</v>
@@ -8082,13 +8097,13 @@
         <v>56.2</v>
       </c>
       <c r="T16" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U16" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="V16" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="W16">
         <v>0.1667</v>
@@ -8157,7 +8172,7 @@
         <v>6</v>
       </c>
       <c r="AS16" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AT16">
         <v>133.6</v>
@@ -8205,7 +8220,7 @@
         <v>1.1467</v>
       </c>
       <c r="BI16" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ16">
         <v>2033</v>
@@ -8253,13 +8268,13 @@
         <v>11.6</v>
       </c>
       <c r="BY16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ16">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="CA16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB16">
         <v>80</v>
@@ -8288,25 +8303,25 @@
         <v>121</v>
       </c>
       <c r="E17" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F17" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="G17" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="H17" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I17" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="J17">
-        <v>603.3</v>
+        <v>633.3</v>
       </c>
       <c r="K17">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="L17">
         <v>5</v>
@@ -8333,13 +8348,13 @@
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U17" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="V17" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="W17">
         <v>0.1667</v>
@@ -8348,7 +8363,7 @@
         <v>8.5</v>
       </c>
       <c r="Y17">
-        <v>89.7</v>
+        <v>89.8</v>
       </c>
       <c r="Z17">
         <v>62.6</v>
@@ -8408,7 +8423,7 @@
         <v>7.6</v>
       </c>
       <c r="AS17" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AT17">
         <v>169.9</v>
@@ -8456,7 +8471,7 @@
         <v>1.1488</v>
       </c>
       <c r="BI17" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ17">
         <v>1977</v>
@@ -8504,13 +8519,13 @@
         <v>2.5</v>
       </c>
       <c r="BY17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ17">
         <v>11.7</v>
       </c>
       <c r="CA17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB17">
         <v>79</v>
@@ -8539,43 +8554,43 @@
         <v>122</v>
       </c>
       <c r="E18" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F18" t="s">
         <v>110</v>
       </c>
       <c r="G18" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I18" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="J18">
-        <v>103.1</v>
+        <v>132.9</v>
       </c>
       <c r="K18">
-        <v>16.9</v>
+        <v>16.4</v>
       </c>
       <c r="L18">
         <v>5</v>
       </c>
       <c r="M18">
-        <v>2.54</v>
+        <v>4.76</v>
       </c>
       <c r="N18">
-        <v>0.47</v>
+        <v>1.45</v>
       </c>
       <c r="O18">
         <v>26.13</v>
       </c>
       <c r="P18">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q18">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -8584,25 +8599,25 @@
         <v>0</v>
       </c>
       <c r="T18" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U18" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="V18" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="W18">
         <v>0.25</v>
       </c>
       <c r="X18">
-        <v>20.7</v>
+        <v>32.5</v>
       </c>
       <c r="Y18">
-        <v>84.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="Z18">
-        <v>65.09999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="AA18">
         <v>0.9399999999999999</v>
@@ -8620,25 +8635,25 @@
         <v>142</v>
       </c>
       <c r="AF18">
-        <v>83.90000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="AG18">
-        <v>91.59999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AH18">
-        <v>73.2</v>
+        <v>72.2</v>
       </c>
       <c r="AI18">
-        <v>72.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AJ18">
-        <v>983.9</v>
+        <v>984</v>
       </c>
       <c r="AK18">
-        <v>1016.9</v>
+        <v>1016.7</v>
       </c>
       <c r="AL18">
-        <v>95.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AM18">
         <v>35.2</v>
@@ -8647,46 +8662,46 @@
         <v>0.02</v>
       </c>
       <c r="AO18">
-        <v>55</v>
+        <v>74.5</v>
       </c>
       <c r="AP18">
-        <v>2229</v>
+        <v>1879</v>
       </c>
       <c r="AQ18">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AR18">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="AS18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AT18">
-        <v>301.5</v>
+        <v>300.5</v>
       </c>
       <c r="AU18">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AV18">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AW18">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AX18">
+        <v>3.9</v>
+      </c>
+      <c r="AY18">
+        <v>4.6</v>
+      </c>
+      <c r="AZ18">
+        <v>1.4</v>
+      </c>
+      <c r="BA18">
+        <v>-3.1</v>
+      </c>
+      <c r="BB18">
         <v>3.5</v>
-      </c>
-      <c r="AY18">
-        <v>4.1</v>
-      </c>
-      <c r="AZ18">
-        <v>1.3</v>
-      </c>
-      <c r="BA18">
-        <v>-2.7</v>
-      </c>
-      <c r="BB18">
-        <v>3.1</v>
       </c>
       <c r="BC18">
         <v>0.5</v>
@@ -8704,13 +8719,13 @@
         <v>0.1</v>
       </c>
       <c r="BH18">
-        <v>1.123</v>
+        <v>1.1204</v>
       </c>
       <c r="BI18" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ18">
-        <v>2642</v>
+        <v>2735</v>
       </c>
       <c r="BK18" t="s">
         <v>133</v>
@@ -8719,13 +8734,13 @@
         <v>135</v>
       </c>
       <c r="BM18">
-        <v>68</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="BN18">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="BO18">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
       <c r="BP18">
         <v>0</v>
@@ -8734,46 +8749,46 @@
         <v>0</v>
       </c>
       <c r="BR18">
-        <v>1.043</v>
+        <v>1.046</v>
       </c>
       <c r="BS18">
-        <v>66.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="BT18">
-        <v>68.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="BU18">
-        <v>59.3</v>
+        <v>59.9</v>
       </c>
       <c r="BV18">
-        <v>55</v>
+        <v>55.4</v>
       </c>
       <c r="BW18">
-        <v>52.4</v>
+        <v>51.6</v>
       </c>
       <c r="BX18">
         <v>39.2</v>
       </c>
       <c r="BY18" t="s">
+        <v>190</v>
+      </c>
+      <c r="BZ18">
+        <v>14.5</v>
+      </c>
+      <c r="CA18" t="s">
         <v>189</v>
-      </c>
-      <c r="BZ18">
-        <v>11.7</v>
-      </c>
-      <c r="CA18" t="s">
-        <v>188</v>
       </c>
       <c r="CB18">
         <v>84</v>
       </c>
       <c r="CC18">
-        <v>82.90000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="CD18">
         <v>5</v>
       </c>
       <c r="CE18">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="19" spans="1:83">
@@ -8790,25 +8805,25 @@
         <v>122</v>
       </c>
       <c r="E19" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F19" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="G19" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H19" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I19" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="J19">
-        <v>103.1</v>
+        <v>132.9</v>
       </c>
       <c r="K19">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="L19">
         <v>5</v>
@@ -8835,13 +8850,13 @@
         <v>0</v>
       </c>
       <c r="T19" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U19" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="V19" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W19">
         <v>0.25</v>
@@ -8850,7 +8865,7 @@
         <v>20.4</v>
       </c>
       <c r="Y19">
-        <v>89.3</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="Z19">
         <v>66.3</v>
@@ -8910,7 +8925,7 @@
         <v>14.5</v>
       </c>
       <c r="AS19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AT19">
         <v>302.4</v>
@@ -8958,7 +8973,7 @@
         <v>1.1261</v>
       </c>
       <c r="BI19" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ19">
         <v>2547</v>
@@ -9006,13 +9021,13 @@
         <v>24.1</v>
       </c>
       <c r="BY19" t="s">
+        <v>190</v>
+      </c>
+      <c r="BZ19">
+        <v>2.6</v>
+      </c>
+      <c r="CA19" t="s">
         <v>189</v>
-      </c>
-      <c r="BZ19">
-        <v>2.7</v>
-      </c>
-      <c r="CA19" t="s">
-        <v>188</v>
       </c>
       <c r="CB19">
         <v>82</v>
@@ -9041,25 +9056,25 @@
         <v>122</v>
       </c>
       <c r="E20" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F20" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G20" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H20" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I20" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="J20">
-        <v>103.1</v>
+        <v>132.9</v>
       </c>
       <c r="K20">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="L20">
         <v>5</v>
@@ -9086,13 +9101,13 @@
         <v>0</v>
       </c>
       <c r="T20" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U20" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="V20" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="W20">
         <v>0.25</v>
@@ -9119,7 +9134,7 @@
         <v>0.6</v>
       </c>
       <c r="AE20" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AF20">
         <v>80.40000000000001</v>
@@ -9161,7 +9176,7 @@
         <v>14.4</v>
       </c>
       <c r="AS20" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="AT20">
         <v>305.7</v>
@@ -9209,7 +9224,7 @@
         <v>1.1303</v>
       </c>
       <c r="BI20" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ20">
         <v>2417</v>
@@ -9257,13 +9272,13 @@
         <v>19.9</v>
       </c>
       <c r="BY20" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ20">
         <v>3.5</v>
       </c>
       <c r="CA20" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB20">
         <v>80</v>
@@ -9292,25 +9307,25 @@
         <v>122</v>
       </c>
       <c r="E21" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F21" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G21" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I21" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="J21">
-        <v>103.1</v>
+        <v>132.9</v>
       </c>
       <c r="K21">
-        <v>19.9</v>
+        <v>19.4</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -9337,13 +9352,13 @@
         <v>0</v>
       </c>
       <c r="T21" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U21" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="V21" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="W21">
         <v>0.25</v>
@@ -9355,7 +9370,7 @@
         <v>91.8</v>
       </c>
       <c r="Z21">
-        <v>66.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AA21">
         <v>0.9399999999999999</v>
@@ -9370,7 +9385,7 @@
         <v>0.6</v>
       </c>
       <c r="AE21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AF21">
         <v>78.5</v>
@@ -9412,7 +9427,7 @@
         <v>12.1</v>
       </c>
       <c r="AS21" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="AT21">
         <v>307.5</v>
@@ -9460,7 +9475,7 @@
         <v>1.1347</v>
       </c>
       <c r="BI21" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ21">
         <v>2283</v>
@@ -9508,13 +9523,13 @@
         <v>17.6</v>
       </c>
       <c r="BY21" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ21">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="CA21" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB21">
         <v>78</v>
@@ -9543,67 +9558,67 @@
         <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F22" t="s">
         <v>110</v>
       </c>
       <c r="G22" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="H22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>16.9</v>
+        <v>16.4</v>
       </c>
       <c r="L22">
         <v>4</v>
       </c>
       <c r="M22">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="N22">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="O22">
         <v>0.32</v>
       </c>
       <c r="P22">
-        <v>23.9</v>
+        <v>32.8</v>
       </c>
       <c r="Q22">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="R22">
-        <v>100</v>
+        <v>43.8</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
       <c r="T22" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U22" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="V22" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="W22">
         <v>0.25</v>
       </c>
       <c r="X22">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="Y22">
         <v>94.3</v>
       </c>
       <c r="Z22">
-        <v>59</v>
+        <v>58.3</v>
       </c>
       <c r="AA22">
         <v>0.7</v>
@@ -9618,25 +9633,25 @@
         <v>0.2</v>
       </c>
       <c r="AE22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AF22">
-        <v>74.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AG22">
-        <v>74</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AH22">
-        <v>58.9</v>
+        <v>57.1</v>
       </c>
       <c r="AI22">
-        <v>57.9</v>
+        <v>54.9</v>
       </c>
       <c r="AJ22">
-        <v>1004.2</v>
+        <v>1004.5</v>
       </c>
       <c r="AK22">
-        <v>1014.7</v>
+        <v>1014.9</v>
       </c>
       <c r="AL22">
         <v>75.2</v>
@@ -9648,46 +9663,46 @@
         <v>0</v>
       </c>
       <c r="AO22">
-        <v>62.4</v>
+        <v>71.8</v>
       </c>
       <c r="AP22">
         <v>28</v>
       </c>
       <c r="AQ22">
+        <v>4</v>
+      </c>
+      <c r="AR22">
+        <v>7.3</v>
+      </c>
+      <c r="AS22" t="s">
+        <v>159</v>
+      </c>
+      <c r="AT22">
+        <v>102.8</v>
+      </c>
+      <c r="AU22">
+        <v>1.9</v>
+      </c>
+      <c r="AV22">
         <v>3.6</v>
       </c>
-      <c r="AR22">
-        <v>7</v>
-      </c>
-      <c r="AS22" t="s">
-        <v>158</v>
-      </c>
-      <c r="AT22">
-        <v>113.4</v>
-      </c>
-      <c r="AU22">
-        <v>2.3</v>
-      </c>
-      <c r="AV22">
-        <v>3.5</v>
-      </c>
       <c r="AW22">
-        <v>0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="AX22">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AY22">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AZ22">
-        <v>0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="BA22">
-        <v>-2.7</v>
+        <v>-3.5</v>
       </c>
       <c r="BB22">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="BC22">
         <v>0.3</v>
@@ -9705,13 +9720,13 @@
         <v>0.08</v>
       </c>
       <c r="BH22">
-        <v>1.171</v>
+        <v>1.1722</v>
       </c>
       <c r="BI22" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ22">
-        <v>1338</v>
+        <v>1316</v>
       </c>
       <c r="BK22" t="s">
         <v>133</v>
@@ -9720,13 +9735,13 @@
         <v>136</v>
       </c>
       <c r="BM22">
-        <v>59.5</v>
+        <v>58.8</v>
       </c>
       <c r="BN22">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO22">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="BP22">
         <v>0</v>
@@ -9735,43 +9750,43 @@
         <v>0</v>
       </c>
       <c r="BR22">
-        <v>1.023</v>
+        <v>1.021</v>
       </c>
       <c r="BS22">
-        <v>58.2</v>
+        <v>57.2</v>
       </c>
       <c r="BT22">
-        <v>60.4</v>
+        <v>60</v>
       </c>
       <c r="BU22">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="BV22">
-        <v>51.6</v>
+        <v>51.3</v>
       </c>
       <c r="BW22">
-        <v>69.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="BX22">
         <v>1.2</v>
       </c>
       <c r="BY22" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ22">
         <v>1.4</v>
       </c>
       <c r="CA22" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CC22">
-        <v>74.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="CD22">
         <v>0</v>
       </c>
       <c r="CE22">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="23" spans="1:83">
@@ -9788,22 +9803,22 @@
         <v>123</v>
       </c>
       <c r="E23" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F23" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="G23" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="H23" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="L23">
         <v>4</v>
@@ -9830,13 +9845,13 @@
         <v>56.2</v>
       </c>
       <c r="T23" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U23" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="V23" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W23">
         <v>0.25</v>
@@ -9905,7 +9920,7 @@
         <v>7.1</v>
       </c>
       <c r="AS23" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AT23">
         <v>94.90000000000001</v>
@@ -9953,7 +9968,7 @@
         <v>1.1724</v>
       </c>
       <c r="BI23" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ23">
         <v>1295</v>
@@ -10001,13 +10016,13 @@
         <v>1.7</v>
       </c>
       <c r="BY23" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ23">
         <v>1.5</v>
       </c>
       <c r="CA23" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CC23">
         <v>73.8</v>
@@ -10033,22 +10048,22 @@
         <v>123</v>
       </c>
       <c r="E24" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F24" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G24" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="H24" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="L24">
         <v>4</v>
@@ -10075,13 +10090,13 @@
         <v>56.2</v>
       </c>
       <c r="T24" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U24" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="V24" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="W24">
         <v>0.25</v>
@@ -10108,7 +10123,7 @@
         <v>0.2</v>
       </c>
       <c r="AE24" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AF24">
         <v>72.59999999999999</v>
@@ -10150,7 +10165,7 @@
         <v>6.4</v>
       </c>
       <c r="AS24" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AT24">
         <v>86.59999999999999</v>
@@ -10198,7 +10213,7 @@
         <v>1.1749</v>
       </c>
       <c r="BI24" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ24">
         <v>1218</v>
@@ -10246,13 +10261,13 @@
         <v>2.5</v>
       </c>
       <c r="BY24" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ24">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="CA24" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CC24">
         <v>72.59999999999999</v>
@@ -10278,22 +10293,22 @@
         <v>123</v>
       </c>
       <c r="E25" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F25" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G25" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="H25" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
-        <v>19.9</v>
+        <v>19.4</v>
       </c>
       <c r="L25">
         <v>4</v>
@@ -10320,13 +10335,13 @@
         <v>56.2</v>
       </c>
       <c r="T25" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U25" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="V25" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="W25">
         <v>0.25</v>
@@ -10353,7 +10368,7 @@
         <v>0.2</v>
       </c>
       <c r="AE25" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AF25">
         <v>72.59999999999999</v>
@@ -10395,7 +10410,7 @@
         <v>5.7</v>
       </c>
       <c r="AS25" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AT25">
         <v>76.8</v>
@@ -10443,7 +10458,7 @@
         <v>1.1748</v>
       </c>
       <c r="BI25" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ25">
         <v>1226</v>
@@ -10491,13 +10506,13 @@
         <v>3.7</v>
       </c>
       <c r="BY25" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ25">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="CA25" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CC25">
         <v>72.59999999999999</v>
@@ -10523,43 +10538,43 @@
         <v>124</v>
       </c>
       <c r="E26" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F26" t="s">
         <v>111</v>
       </c>
       <c r="G26" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="H26" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I26" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="J26">
-        <v>48.3</v>
+        <v>78.2</v>
       </c>
       <c r="K26">
-        <v>17.3</v>
+        <v>16.8</v>
       </c>
       <c r="L26">
         <v>5</v>
       </c>
       <c r="M26">
-        <v>3.04</v>
+        <v>4.23</v>
       </c>
       <c r="N26">
-        <v>0.72</v>
+        <v>0.4</v>
       </c>
       <c r="O26">
         <v>33.59</v>
       </c>
       <c r="P26">
-        <v>34.3</v>
+        <v>12.9</v>
       </c>
       <c r="Q26">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -10568,25 +10583,25 @@
         <v>100</v>
       </c>
       <c r="T26" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U26" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="V26" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="W26">
         <v>0.6667</v>
       </c>
       <c r="X26">
-        <v>26.1</v>
+        <v>29.9</v>
       </c>
       <c r="Y26">
-        <v>85.3</v>
+        <v>83.7</v>
       </c>
       <c r="Z26">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
       <c r="AA26">
         <v>0.82</v>
@@ -10604,25 +10619,25 @@
         <v>143</v>
       </c>
       <c r="AF26">
-        <v>87.40000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="AG26">
-        <v>96.40000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="AH26">
-        <v>71.2</v>
+        <v>69.5</v>
       </c>
       <c r="AI26">
-        <v>58.5</v>
+        <v>55</v>
       </c>
       <c r="AJ26">
-        <v>987.7</v>
+        <v>987.9</v>
       </c>
       <c r="AK26">
-        <v>1011.5</v>
+        <v>1011.7</v>
       </c>
       <c r="AL26">
-        <v>60.3</v>
+        <v>60.9</v>
       </c>
       <c r="AM26">
         <v>19.9</v>
@@ -10631,22 +10646,22 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="AO26">
-        <v>64.7</v>
+        <v>86</v>
       </c>
       <c r="AP26">
-        <v>1910</v>
+        <v>1402</v>
       </c>
       <c r="AQ26">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AR26">
-        <v>11.5</v>
+        <v>12.2</v>
       </c>
       <c r="AS26" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AT26">
-        <v>190.9</v>
+        <v>205.8</v>
       </c>
       <c r="AU26">
         <v>-0</v>
@@ -10691,7 +10706,7 @@
         <v>1.1896</v>
       </c>
       <c r="BI26" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ26">
         <v>858</v>
@@ -10739,25 +10754,25 @@
         <v>0</v>
       </c>
       <c r="BY26" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="BZ26">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="CA26" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB26">
         <v>88</v>
       </c>
       <c r="CC26">
-        <v>87</v>
+        <v>88.3</v>
       </c>
       <c r="CD26">
         <v>5</v>
       </c>
       <c r="CE26">
-        <v>6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="27" spans="1:83">
@@ -10774,25 +10789,25 @@
         <v>124</v>
       </c>
       <c r="E27" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F27" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G27" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="H27" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I27" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="J27">
-        <v>48.3</v>
+        <v>78.2</v>
       </c>
       <c r="K27">
-        <v>18.3</v>
+        <v>17.8</v>
       </c>
       <c r="L27">
         <v>5</v>
@@ -10819,13 +10834,13 @@
         <v>100</v>
       </c>
       <c r="T27" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U27" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="V27" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="W27">
         <v>0.6667</v>
@@ -10852,7 +10867,7 @@
         <v>0.5</v>
       </c>
       <c r="AE27" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AF27">
         <v>85</v>
@@ -10894,7 +10909,7 @@
         <v>16.1</v>
       </c>
       <c r="AS27" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AT27">
         <v>215.5</v>
@@ -10942,7 +10957,7 @@
         <v>1.126</v>
       </c>
       <c r="BI27" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ27">
         <v>2596</v>
@@ -10990,13 +11005,13 @@
         <v>28.3</v>
       </c>
       <c r="BY27" t="s">
+        <v>190</v>
+      </c>
+      <c r="BZ27">
+        <v>12.9</v>
+      </c>
+      <c r="CA27" t="s">
         <v>189</v>
-      </c>
-      <c r="BZ27">
-        <v>13</v>
-      </c>
-      <c r="CA27" t="s">
-        <v>188</v>
       </c>
       <c r="CB27">
         <v>85</v>
@@ -11025,25 +11040,25 @@
         <v>124</v>
       </c>
       <c r="E28" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F28" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G28" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="H28" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I28" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="J28">
-        <v>48.3</v>
+        <v>78.2</v>
       </c>
       <c r="K28">
-        <v>19.3</v>
+        <v>18.8</v>
       </c>
       <c r="L28">
         <v>5</v>
@@ -11070,13 +11085,13 @@
         <v>0</v>
       </c>
       <c r="T28" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U28" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="V28" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W28">
         <v>0.6667</v>
@@ -11103,7 +11118,7 @@
         <v>0.5</v>
       </c>
       <c r="AE28" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AF28">
         <v>82.8</v>
@@ -11145,7 +11160,7 @@
         <v>15.2</v>
       </c>
       <c r="AS28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AT28">
         <v>224.1</v>
@@ -11193,7 +11208,7 @@
         <v>1.1303</v>
       </c>
       <c r="BI28" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ28">
         <v>2455</v>
@@ -11241,13 +11256,13 @@
         <v>22.3</v>
       </c>
       <c r="BY28" t="s">
+        <v>190</v>
+      </c>
+      <c r="BZ28">
+        <v>12</v>
+      </c>
+      <c r="CA28" t="s">
         <v>189</v>
-      </c>
-      <c r="BZ28">
-        <v>12.1</v>
-      </c>
-      <c r="CA28" t="s">
-        <v>188</v>
       </c>
       <c r="CB28">
         <v>83</v>
@@ -11276,25 +11291,25 @@
         <v>124</v>
       </c>
       <c r="E29" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F29" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G29" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="H29" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I29" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="J29">
-        <v>48.3</v>
+        <v>78.2</v>
       </c>
       <c r="K29">
-        <v>20.3</v>
+        <v>19.8</v>
       </c>
       <c r="L29">
         <v>5</v>
@@ -11321,13 +11336,13 @@
         <v>0</v>
       </c>
       <c r="T29" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U29" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="V29" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="W29">
         <v>0.6667</v>
@@ -11336,7 +11351,7 @@
         <v>22</v>
       </c>
       <c r="Y29">
-        <v>84.7</v>
+        <v>84.8</v>
       </c>
       <c r="Z29">
         <v>59.7</v>
@@ -11354,7 +11369,7 @@
         <v>0.5</v>
       </c>
       <c r="AE29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AF29">
         <v>81.5</v>
@@ -11396,7 +11411,7 @@
         <v>14.2</v>
       </c>
       <c r="AS29" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AT29">
         <v>230.9</v>
@@ -11444,7 +11459,7 @@
         <v>1.133</v>
       </c>
       <c r="BI29" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ29">
         <v>2371</v>
@@ -11492,13 +11507,13 @@
         <v>15</v>
       </c>
       <c r="BY29" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ29">
         <v>9.699999999999999</v>
       </c>
       <c r="CA29" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB29">
         <v>82</v>
@@ -11527,25 +11542,25 @@
         <v>125</v>
       </c>
       <c r="E30" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F30" t="s">
         <v>112</v>
       </c>
       <c r="G30" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H30" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I30" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="J30">
-        <v>178.8</v>
+        <v>208.7</v>
       </c>
       <c r="K30">
-        <v>17.7</v>
+        <v>17.2</v>
       </c>
       <c r="L30">
         <v>5</v>
@@ -11572,13 +11587,13 @@
         <v>0</v>
       </c>
       <c r="T30" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U30" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="V30" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="W30">
         <v>0.0833</v>
@@ -11647,7 +11662,7 @@
         <v>18.6</v>
       </c>
       <c r="AS30" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AT30">
         <v>213.9</v>
@@ -11695,7 +11710,7 @@
         <v>1.1497</v>
       </c>
       <c r="BI30" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ30">
         <v>1889</v>
@@ -11743,13 +11758,13 @@
         <v>29.5</v>
       </c>
       <c r="BY30" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="BZ30">
         <v>21.6</v>
       </c>
       <c r="CA30" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="CB30">
         <v>86</v>
@@ -11778,25 +11793,25 @@
         <v>125</v>
       </c>
       <c r="E31" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F31" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G31" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H31" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I31" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="J31">
-        <v>178.8</v>
+        <v>208.7</v>
       </c>
       <c r="K31">
-        <v>18.7</v>
+        <v>18.2</v>
       </c>
       <c r="L31">
         <v>5</v>
@@ -11823,13 +11838,13 @@
         <v>0</v>
       </c>
       <c r="T31" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U31" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="V31" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W31">
         <v>0.0833</v>
@@ -11898,7 +11913,7 @@
         <v>22.2</v>
       </c>
       <c r="AS31" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AT31">
         <v>235.6</v>
@@ -11946,7 +11961,7 @@
         <v>1.1518</v>
       </c>
       <c r="BI31" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ31">
         <v>1821</v>
@@ -11994,13 +12009,13 @@
         <v>26.2</v>
       </c>
       <c r="BY31" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="BZ31">
         <v>3.8</v>
       </c>
       <c r="CA31" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB31">
         <v>84</v>
@@ -12029,25 +12044,25 @@
         <v>125</v>
       </c>
       <c r="E32" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F32" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="G32" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H32" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I32" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="J32">
-        <v>178.8</v>
+        <v>208.7</v>
       </c>
       <c r="K32">
-        <v>19.7</v>
+        <v>19.2</v>
       </c>
       <c r="L32">
         <v>5</v>
@@ -12074,13 +12089,13 @@
         <v>0</v>
       </c>
       <c r="T32" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U32" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="V32" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="W32">
         <v>0.0833</v>
@@ -12149,7 +12164,7 @@
         <v>20.5</v>
       </c>
       <c r="AS32" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AT32">
         <v>234.5</v>
@@ -12197,7 +12212,7 @@
         <v>1.1537</v>
       </c>
       <c r="BI32" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ32">
         <v>1747</v>
@@ -12245,13 +12260,13 @@
         <v>23.1</v>
       </c>
       <c r="BY32" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="BZ32">
         <v>7.9</v>
       </c>
       <c r="CA32" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB32">
         <v>83</v>
@@ -12280,25 +12295,25 @@
         <v>125</v>
       </c>
       <c r="E33" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F33" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="G33" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H33" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I33" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="J33">
-        <v>178.8</v>
+        <v>208.7</v>
       </c>
       <c r="K33">
-        <v>20.7</v>
+        <v>20.2</v>
       </c>
       <c r="L33">
         <v>5</v>
@@ -12325,13 +12340,13 @@
         <v>0</v>
       </c>
       <c r="T33" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U33" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="V33" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="W33">
         <v>0.0833</v>
@@ -12343,7 +12358,7 @@
         <v>89.2</v>
       </c>
       <c r="Z33">
-        <v>75.09999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="AA33">
         <v>1.18</v>
@@ -12358,7 +12373,7 @@
         <v>1.8</v>
       </c>
       <c r="AE33" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="AF33">
         <v>81.09999999999999</v>
@@ -12400,7 +12415,7 @@
         <v>16.7</v>
       </c>
       <c r="AS33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AT33">
         <v>228.2</v>
@@ -12448,7 +12463,7 @@
         <v>1.1564</v>
       </c>
       <c r="BI33" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ33">
         <v>1654</v>
@@ -12496,13 +12511,13 @@
         <v>19.8</v>
       </c>
       <c r="BY33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ33">
         <v>7.6</v>
       </c>
       <c r="CA33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB33">
         <v>81</v>
@@ -12531,25 +12546,25 @@
         <v>126</v>
       </c>
       <c r="E34" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F34" t="s">
         <v>113</v>
       </c>
       <c r="G34" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="H34" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I34" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="J34">
-        <v>153.8</v>
+        <v>183.7</v>
       </c>
       <c r="K34">
-        <v>17.8</v>
+        <v>17.3</v>
       </c>
       <c r="L34">
         <v>5</v>
@@ -12576,13 +12591,13 @@
         <v>0</v>
       </c>
       <c r="T34" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U34" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="V34" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="W34">
         <v>0.1667</v>
@@ -12609,7 +12624,7 @@
         <v>0.3</v>
       </c>
       <c r="AE34" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AF34">
         <v>87.5</v>
@@ -12651,7 +12666,7 @@
         <v>12.2</v>
       </c>
       <c r="AS34" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AT34">
         <v>170.5</v>
@@ -12699,7 +12714,7 @@
         <v>1.1896</v>
       </c>
       <c r="BI34" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ34">
         <v>858</v>
@@ -12747,13 +12762,13 @@
         <v>0</v>
       </c>
       <c r="BY34" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="BZ34">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="CA34" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB34">
         <v>90</v>
@@ -12782,25 +12797,25 @@
         <v>126</v>
       </c>
       <c r="E35" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F35" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G35" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="H35" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I35" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="J35">
-        <v>153.8</v>
+        <v>183.7</v>
       </c>
       <c r="K35">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="L35">
         <v>5</v>
@@ -12827,13 +12842,13 @@
         <v>0</v>
       </c>
       <c r="T35" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U35" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="V35" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W35">
         <v>0.1667</v>
@@ -12842,7 +12857,7 @@
         <v>12.1</v>
       </c>
       <c r="Y35">
-        <v>85.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="Z35">
         <v>66.3</v>
@@ -12860,7 +12875,7 @@
         <v>0.3</v>
       </c>
       <c r="AE35" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AF35">
         <v>85.40000000000001</v>
@@ -12902,7 +12917,7 @@
         <v>11.4</v>
       </c>
       <c r="AS35" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AT35">
         <v>171.9</v>
@@ -12950,7 +12965,7 @@
         <v>1.1575</v>
       </c>
       <c r="BI35" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ35">
         <v>1621</v>
@@ -12998,13 +13013,13 @@
         <v>12.9</v>
       </c>
       <c r="BY35" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ35">
         <v>15.6</v>
       </c>
       <c r="CA35" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB35">
         <v>88</v>
@@ -13033,25 +13048,25 @@
         <v>126</v>
       </c>
       <c r="E36" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F36" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G36" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="H36" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I36" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="J36">
-        <v>153.8</v>
+        <v>183.7</v>
       </c>
       <c r="K36">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="L36">
         <v>5</v>
@@ -13078,13 +13093,13 @@
         <v>0</v>
       </c>
       <c r="T36" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U36" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="V36" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="W36">
         <v>0.1667</v>
@@ -13096,7 +13111,7 @@
         <v>88.09999999999999</v>
       </c>
       <c r="Z36">
-        <v>65.90000000000001</v>
+        <v>66</v>
       </c>
       <c r="AA36">
         <v>0.76</v>
@@ -13111,7 +13126,7 @@
         <v>0.3</v>
       </c>
       <c r="AE36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AF36">
         <v>83.3</v>
@@ -13153,7 +13168,7 @@
         <v>11.1</v>
       </c>
       <c r="AS36" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AT36">
         <v>169.9</v>
@@ -13201,7 +13216,7 @@
         <v>1.1622</v>
       </c>
       <c r="BI36" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ36">
         <v>1467</v>
@@ -13249,13 +13264,13 @@
         <v>12.5</v>
       </c>
       <c r="BY36" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ36">
         <v>13.6</v>
       </c>
       <c r="CA36" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB36">
         <v>85</v>
@@ -13284,25 +13299,25 @@
         <v>126</v>
       </c>
       <c r="E37" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F37" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G37" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="H37" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I37" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="J37">
-        <v>153.8</v>
+        <v>183.7</v>
       </c>
       <c r="K37">
-        <v>20.8</v>
+        <v>20.3</v>
       </c>
       <c r="L37">
         <v>5</v>
@@ -13329,13 +13344,13 @@
         <v>0</v>
       </c>
       <c r="T37" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U37" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="V37" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="W37">
         <v>0.1667</v>
@@ -13344,7 +13359,7 @@
         <v>8.4</v>
       </c>
       <c r="Y37">
-        <v>90.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="Z37">
         <v>62.8</v>
@@ -13362,7 +13377,7 @@
         <v>0.3</v>
       </c>
       <c r="AE37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AF37">
         <v>82.3</v>
@@ -13404,7 +13419,7 @@
         <v>10.9</v>
       </c>
       <c r="AS37" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AT37">
         <v>175.5</v>
@@ -13452,7 +13467,7 @@
         <v>1.1646</v>
       </c>
       <c r="BI37" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ37">
         <v>1385</v>
@@ -13500,13 +13515,13 @@
         <v>12.9</v>
       </c>
       <c r="BY37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ37">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="CA37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB37">
         <v>84</v>
@@ -13535,25 +13550,25 @@
         <v>127</v>
       </c>
       <c r="E38" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F38" t="s">
         <v>113</v>
       </c>
       <c r="G38" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="H38" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I38" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="J38">
-        <v>128</v>
+        <v>157.9</v>
       </c>
       <c r="K38">
-        <v>17.8</v>
+        <v>17.3</v>
       </c>
       <c r="L38">
         <v>5</v>
@@ -13580,13 +13595,13 @@
         <v>0</v>
       </c>
       <c r="T38" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U38" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="V38" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="W38">
         <v>0.1667</v>
@@ -13595,7 +13610,7 @@
         <v>15.3</v>
       </c>
       <c r="Y38">
-        <v>86.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="Z38">
         <v>76.90000000000001</v>
@@ -13655,7 +13670,7 @@
         <v>21.2</v>
       </c>
       <c r="AS38" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AT38">
         <v>217</v>
@@ -13703,7 +13718,7 @@
         <v>1.1173</v>
       </c>
       <c r="BI38" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ38">
         <v>2873</v>
@@ -13751,13 +13766,13 @@
         <v>22.6</v>
       </c>
       <c r="BY38" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="BZ38">
         <v>11.8</v>
       </c>
       <c r="CA38" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB38">
         <v>89</v>
@@ -13786,25 +13801,25 @@
         <v>127</v>
       </c>
       <c r="E39" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F39" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G39" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="H39" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I39" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="J39">
-        <v>128</v>
+        <v>157.9</v>
       </c>
       <c r="K39">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="L39">
         <v>5</v>
@@ -13831,13 +13846,13 @@
         <v>0</v>
       </c>
       <c r="T39" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U39" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="V39" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W39">
         <v>0.1667</v>
@@ -13864,7 +13879,7 @@
         <v>0.4</v>
       </c>
       <c r="AE39" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AF39">
         <v>85</v>
@@ -13906,7 +13921,7 @@
         <v>20.3</v>
       </c>
       <c r="AS39" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AT39">
         <v>203.6</v>
@@ -13954,7 +13969,7 @@
         <v>1.1216</v>
       </c>
       <c r="BI39" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ39">
         <v>2731</v>
@@ -14002,13 +14017,13 @@
         <v>18.5</v>
       </c>
       <c r="BY39" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ39">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="CA39" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB39">
         <v>87</v>
@@ -14037,25 +14052,25 @@
         <v>127</v>
       </c>
       <c r="E40" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F40" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G40" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="H40" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I40" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="J40">
-        <v>128</v>
+        <v>157.9</v>
       </c>
       <c r="K40">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="L40">
         <v>5</v>
@@ -14082,13 +14097,13 @@
         <v>0</v>
       </c>
       <c r="T40" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U40" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="V40" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="W40">
         <v>0.1667</v>
@@ -14115,7 +14130,7 @@
         <v>0.4</v>
       </c>
       <c r="AE40" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AF40">
         <v>82.90000000000001</v>
@@ -14157,7 +14172,7 @@
         <v>14.5</v>
       </c>
       <c r="AS40" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AT40">
         <v>199.1</v>
@@ -14205,7 +14220,7 @@
         <v>1.1259</v>
       </c>
       <c r="BI40" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ40">
         <v>2592</v>
@@ -14253,13 +14268,13 @@
         <v>15</v>
       </c>
       <c r="BY40" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ40">
         <v>13.3</v>
       </c>
       <c r="CA40" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB40">
         <v>85</v>
@@ -14288,25 +14303,25 @@
         <v>127</v>
       </c>
       <c r="E41" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F41" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G41" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="H41" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I41" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="J41">
-        <v>128</v>
+        <v>157.9</v>
       </c>
       <c r="K41">
-        <v>20.8</v>
+        <v>20.3</v>
       </c>
       <c r="L41">
         <v>5</v>
@@ -14333,13 +14348,13 @@
         <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U41" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="V41" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="W41">
         <v>0.1667</v>
@@ -14348,10 +14363,10 @@
         <v>10.3</v>
       </c>
       <c r="Y41">
-        <v>88.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="Z41">
-        <v>70.2</v>
+        <v>70.3</v>
       </c>
       <c r="AA41">
         <v>1.03</v>
@@ -14366,7 +14381,7 @@
         <v>0.4</v>
       </c>
       <c r="AE41" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AF41">
         <v>81.09999999999999</v>
@@ -14408,7 +14423,7 @@
         <v>13.8</v>
       </c>
       <c r="AS41" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AT41">
         <v>202.4</v>
@@ -14456,7 +14471,7 @@
         <v>1.13</v>
       </c>
       <c r="BI41" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ41">
         <v>2461</v>
@@ -14504,13 +14519,13 @@
         <v>11.6</v>
       </c>
       <c r="BY41" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ41">
         <v>11.7</v>
       </c>
       <c r="CA41" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB41">
         <v>83</v>
@@ -14539,25 +14554,25 @@
         <v>128</v>
       </c>
       <c r="E42" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F42" t="s">
         <v>114</v>
       </c>
       <c r="G42" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="H42" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I42" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="J42">
-        <v>693.8</v>
+        <v>723.7</v>
       </c>
       <c r="K42">
-        <v>18.3</v>
+        <v>17.8</v>
       </c>
       <c r="L42">
         <v>5</v>
@@ -14584,13 +14599,13 @@
         <v>75</v>
       </c>
       <c r="T42" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U42" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="V42" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="W42">
         <v>0.6667</v>
@@ -14617,7 +14632,7 @@
         <v>4</v>
       </c>
       <c r="AE42" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AF42">
         <v>92</v>
@@ -14659,7 +14674,7 @@
         <v>17.1</v>
       </c>
       <c r="AS42" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AT42">
         <v>88.8</v>
@@ -14707,7 +14722,7 @@
         <v>0.9556</v>
       </c>
       <c r="BI42" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="BJ42">
         <v>8309</v>
@@ -14755,13 +14770,13 @@
         <v>1.8</v>
       </c>
       <c r="BY42" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ42">
         <v>4.1</v>
       </c>
       <c r="CA42" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB42">
         <v>92</v>
@@ -14790,25 +14805,25 @@
         <v>128</v>
       </c>
       <c r="E43" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F43" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G43" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="H43" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I43" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="J43">
-        <v>693.8</v>
+        <v>723.7</v>
       </c>
       <c r="K43">
-        <v>19.3</v>
+        <v>18.8</v>
       </c>
       <c r="L43">
         <v>5</v>
@@ -14835,13 +14850,13 @@
         <v>75</v>
       </c>
       <c r="T43" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U43" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="V43" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="W43">
         <v>0.6667</v>
@@ -14868,7 +14883,7 @@
         <v>4</v>
       </c>
       <c r="AE43" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AF43">
         <v>90.3</v>
@@ -14910,7 +14925,7 @@
         <v>17</v>
       </c>
       <c r="AS43" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AT43">
         <v>114.8</v>
@@ -14958,7 +14973,7 @@
         <v>0.9583</v>
       </c>
       <c r="BI43" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="BJ43">
         <v>8204</v>
@@ -15006,13 +15021,13 @@
         <v>1</v>
       </c>
       <c r="BY43" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ43">
         <v>6.7</v>
       </c>
       <c r="CA43" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB43">
         <v>91</v>
@@ -15041,25 +15056,25 @@
         <v>128</v>
       </c>
       <c r="E44" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F44" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G44" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="H44" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I44" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="J44">
-        <v>693.8</v>
+        <v>723.7</v>
       </c>
       <c r="K44">
-        <v>20.3</v>
+        <v>19.8</v>
       </c>
       <c r="L44">
         <v>5</v>
@@ -15086,13 +15101,13 @@
         <v>0</v>
       </c>
       <c r="T44" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U44" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="V44" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W44">
         <v>0.6667</v>
@@ -15104,7 +15119,7 @@
         <v>88.3</v>
       </c>
       <c r="Z44">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="AA44">
         <v>1.05</v>
@@ -15119,7 +15134,7 @@
         <v>4</v>
       </c>
       <c r="AE44" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AF44">
         <v>87</v>
@@ -15161,7 +15176,7 @@
         <v>17.5</v>
       </c>
       <c r="AS44" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AT44">
         <v>120.9</v>
@@ -15209,7 +15224,7 @@
         <v>0.9641999999999999</v>
       </c>
       <c r="BI44" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="BJ44">
         <v>7979</v>
@@ -15257,13 +15272,13 @@
         <v>1.3</v>
       </c>
       <c r="BY44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ44">
         <v>8.5</v>
       </c>
       <c r="CA44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB44">
         <v>87</v>
@@ -15292,25 +15307,25 @@
         <v>128</v>
       </c>
       <c r="E45" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F45" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G45" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="H45" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I45" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="J45">
-        <v>693.8</v>
+        <v>723.7</v>
       </c>
       <c r="K45">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="L45">
         <v>5</v>
@@ -15337,13 +15352,13 @@
         <v>0</v>
       </c>
       <c r="T45" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U45" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="V45" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="W45">
         <v>0.6667</v>
@@ -15412,7 +15427,7 @@
         <v>19.4</v>
       </c>
       <c r="AS45" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AT45">
         <v>132.2</v>
@@ -15460,7 +15475,7 @@
         <v>0.9697</v>
       </c>
       <c r="BI45" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="BJ45">
         <v>7772</v>
@@ -15508,13 +15523,13 @@
         <v>0.6</v>
       </c>
       <c r="BY45" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ45">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="CA45" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB45">
         <v>84</v>
@@ -15543,25 +15558,25 @@
         <v>129</v>
       </c>
       <c r="E46" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F46" t="s">
         <v>115</v>
       </c>
       <c r="G46" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="H46" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I46" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="J46">
-        <v>153.9</v>
+        <v>183.8</v>
       </c>
       <c r="K46">
-        <v>19.3</v>
+        <v>18.8</v>
       </c>
       <c r="L46">
         <v>5</v>
@@ -15588,13 +15603,13 @@
         <v>0</v>
       </c>
       <c r="T46" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U46" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="V46" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="W46">
         <v>0.6333</v>
@@ -15603,7 +15618,7 @@
         <v>7.4</v>
       </c>
       <c r="Y46">
-        <v>88.7</v>
+        <v>88.8</v>
       </c>
       <c r="Z46">
         <v>66.3</v>
@@ -15621,7 +15636,7 @@
         <v>0</v>
       </c>
       <c r="AE46" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AF46">
         <v>76.90000000000001</v>
@@ -15663,7 +15678,7 @@
         <v>13.4</v>
       </c>
       <c r="AS46" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AT46">
         <v>190.8</v>
@@ -15711,7 +15726,7 @@
         <v>1.1717</v>
       </c>
       <c r="BI46" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ46">
         <v>1281</v>
@@ -15759,13 +15774,13 @@
         <v>1.3</v>
       </c>
       <c r="BY46" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ46">
         <v>14.4</v>
       </c>
       <c r="CA46" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB46">
         <v>79</v>
@@ -15794,25 +15809,25 @@
         <v>129</v>
       </c>
       <c r="E47" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F47" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G47" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="H47" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I47" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="J47">
-        <v>153.9</v>
+        <v>183.8</v>
       </c>
       <c r="K47">
-        <v>20.3</v>
+        <v>19.8</v>
       </c>
       <c r="L47">
         <v>5</v>
@@ -15839,13 +15854,13 @@
         <v>0</v>
       </c>
       <c r="T47" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U47" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="V47" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="W47">
         <v>0.6333</v>
@@ -15854,7 +15869,7 @@
         <v>6.5</v>
       </c>
       <c r="Y47">
-        <v>89.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="Z47">
         <v>62</v>
@@ -15872,7 +15887,7 @@
         <v>0</v>
       </c>
       <c r="AE47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AF47">
         <v>74.3</v>
@@ -15914,7 +15929,7 @@
         <v>12.8</v>
       </c>
       <c r="AS47" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AT47">
         <v>189.3</v>
@@ -15962,7 +15977,7 @@
         <v>1.1783</v>
       </c>
       <c r="BI47" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ47">
         <v>1087</v>
@@ -16010,13 +16025,13 @@
         <v>1.3</v>
       </c>
       <c r="BY47" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ47">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="CA47" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB47">
         <v>76</v>
@@ -16045,25 +16060,25 @@
         <v>129</v>
       </c>
       <c r="E48" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F48" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G48" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="H48" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I48" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="J48">
-        <v>153.9</v>
+        <v>183.8</v>
       </c>
       <c r="K48">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="L48">
         <v>5</v>
@@ -16090,13 +16105,13 @@
         <v>0</v>
       </c>
       <c r="T48" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U48" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="V48" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W48">
         <v>0.6333</v>
@@ -16165,7 +16180,7 @@
         <v>11.7</v>
       </c>
       <c r="AS48" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AT48">
         <v>188.5</v>
@@ -16213,7 +16228,7 @@
         <v>1.1839</v>
       </c>
       <c r="BI48" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ48">
         <v>917</v>
@@ -16261,13 +16276,13 @@
         <v>1.3</v>
       </c>
       <c r="BY48" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ48">
         <v>8.4</v>
       </c>
       <c r="CA48" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB48">
         <v>73</v>
@@ -16296,25 +16311,25 @@
         <v>129</v>
       </c>
       <c r="E49" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F49" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G49" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="H49" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I49" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="J49">
-        <v>153.9</v>
+        <v>183.8</v>
       </c>
       <c r="K49">
-        <v>22.3</v>
+        <v>21.8</v>
       </c>
       <c r="L49">
         <v>5</v>
@@ -16341,13 +16356,13 @@
         <v>0</v>
       </c>
       <c r="T49" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U49" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="V49" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="W49">
         <v>0.6333</v>
@@ -16374,7 +16389,7 @@
         <v>0</v>
       </c>
       <c r="AE49" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AF49">
         <v>70.8</v>
@@ -16416,7 +16431,7 @@
         <v>10.7</v>
       </c>
       <c r="AS49" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AT49">
         <v>186.4</v>
@@ -16464,7 +16479,7 @@
         <v>1.1875</v>
       </c>
       <c r="BI49" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ49">
         <v>808</v>
@@ -16512,13 +16527,13 @@
         <v>1.3</v>
       </c>
       <c r="BY49" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ49">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="CA49" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB49">
         <v>71</v>
@@ -16547,25 +16562,25 @@
         <v>130</v>
       </c>
       <c r="E50" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F50" t="s">
         <v>116</v>
       </c>
       <c r="G50" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H50" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I50" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="J50">
-        <v>559.3</v>
+        <v>589.3</v>
       </c>
       <c r="K50">
-        <v>19.3</v>
+        <v>18.8</v>
       </c>
       <c r="L50">
         <v>5</v>
@@ -16592,13 +16607,13 @@
         <v>0</v>
       </c>
       <c r="T50" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U50" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="V50" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="W50">
         <v>0.6667</v>
@@ -16607,7 +16622,7 @@
         <v>9</v>
       </c>
       <c r="Y50">
-        <v>92.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="Z50">
         <v>79.09999999999999</v>
@@ -16625,7 +16640,7 @@
         <v>1.5</v>
       </c>
       <c r="AE50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AF50">
         <v>85.5</v>
@@ -16667,7 +16682,7 @@
         <v>21.3</v>
       </c>
       <c r="AS50" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AT50">
         <v>210.6</v>
@@ -16715,7 +16730,7 @@
         <v>1.157</v>
       </c>
       <c r="BI50" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ50">
         <v>1846</v>
@@ -16763,13 +16778,13 @@
         <v>0</v>
       </c>
       <c r="BY50" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ50">
         <v>6.9</v>
       </c>
       <c r="CA50" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB50">
         <v>84</v>
@@ -16798,25 +16813,25 @@
         <v>130</v>
       </c>
       <c r="E51" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F51" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="G51" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H51" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I51" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="J51">
-        <v>559.3</v>
+        <v>589.3</v>
       </c>
       <c r="K51">
-        <v>20.3</v>
+        <v>19.8</v>
       </c>
       <c r="L51">
         <v>5</v>
@@ -16843,13 +16858,13 @@
         <v>0</v>
       </c>
       <c r="T51" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U51" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="V51" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="W51">
         <v>0.6667</v>
@@ -16858,7 +16873,7 @@
         <v>8.4</v>
       </c>
       <c r="Y51">
-        <v>93.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="Z51">
         <v>78</v>
@@ -16876,7 +16891,7 @@
         <v>1.5</v>
       </c>
       <c r="AE51" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AF51">
         <v>80.09999999999999</v>
@@ -16918,7 +16933,7 @@
         <v>22.5</v>
       </c>
       <c r="AS51" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AT51">
         <v>209.2</v>
@@ -16966,7 +16981,7 @@
         <v>1.1689</v>
       </c>
       <c r="BI51" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ51">
         <v>1474</v>
@@ -17014,13 +17029,13 @@
         <v>0</v>
       </c>
       <c r="BY51" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ51">
         <v>4.7</v>
       </c>
       <c r="CA51" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB51">
         <v>78</v>
@@ -17049,25 +17064,25 @@
         <v>130</v>
       </c>
       <c r="E52" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F52" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="G52" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H52" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I52" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="J52">
-        <v>559.3</v>
+        <v>589.3</v>
       </c>
       <c r="K52">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="L52">
         <v>5</v>
@@ -17094,13 +17109,13 @@
         <v>0</v>
       </c>
       <c r="T52" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U52" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="V52" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W52">
         <v>0.6667</v>
@@ -17127,7 +17142,7 @@
         <v>1.5</v>
       </c>
       <c r="AE52" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AF52">
         <v>74.59999999999999</v>
@@ -17169,7 +17184,7 @@
         <v>23.5</v>
       </c>
       <c r="AS52" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AT52">
         <v>206.4</v>
@@ -17217,7 +17232,7 @@
         <v>1.1815</v>
       </c>
       <c r="BI52" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ52">
         <v>1092</v>
@@ -17265,13 +17280,13 @@
         <v>0</v>
       </c>
       <c r="BY52" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ52">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="CA52" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB52">
         <v>72</v>
@@ -17300,25 +17315,25 @@
         <v>130</v>
       </c>
       <c r="E53" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F53" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="G53" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H53" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I53" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="J53">
-        <v>559.3</v>
+        <v>589.3</v>
       </c>
       <c r="K53">
-        <v>22.3</v>
+        <v>21.8</v>
       </c>
       <c r="L53">
         <v>5</v>
@@ -17345,13 +17360,13 @@
         <v>0</v>
       </c>
       <c r="T53" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U53" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="V53" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="W53">
         <v>0.6667</v>
@@ -17360,7 +17375,7 @@
         <v>6.5</v>
       </c>
       <c r="Y53">
-        <v>95.2</v>
+        <v>95.3</v>
       </c>
       <c r="Z53">
         <v>74.2</v>
@@ -17378,7 +17393,7 @@
         <v>1.5</v>
       </c>
       <c r="AE53" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AF53">
         <v>70.40000000000001</v>
@@ -17420,7 +17435,7 @@
         <v>23.6</v>
       </c>
       <c r="AS53" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AT53">
         <v>204.5</v>
@@ -17468,7 +17483,7 @@
         <v>1.1915</v>
       </c>
       <c r="BI53" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ53">
         <v>794</v>
@@ -17516,13 +17531,13 @@
         <v>0</v>
       </c>
       <c r="BY53" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ53">
         <v>3.3</v>
       </c>
       <c r="CA53" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB53">
         <v>68</v>
@@ -17551,25 +17566,25 @@
         <v>131</v>
       </c>
       <c r="E54" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F54" t="s">
         <v>117</v>
       </c>
       <c r="G54" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="H54" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I54" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="J54">
-        <v>86.90000000000001</v>
+        <v>116.9</v>
       </c>
       <c r="K54">
-        <v>19.3</v>
+        <v>18.8</v>
       </c>
       <c r="L54">
         <v>5</v>
@@ -17596,13 +17611,13 @@
         <v>81.2</v>
       </c>
       <c r="T54" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U54" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="V54" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="W54">
         <v>0.6667</v>
@@ -17611,7 +17626,7 @@
         <v>14</v>
       </c>
       <c r="Y54">
-        <v>83.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="Z54">
         <v>53.1</v>
@@ -17671,7 +17686,7 @@
         <v>6.5</v>
       </c>
       <c r="AS54" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AT54">
         <v>58.8</v>
@@ -17719,7 +17734,7 @@
         <v>1.1896</v>
       </c>
       <c r="BI54" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ54">
         <v>858</v>
@@ -17767,13 +17782,13 @@
         <v>0</v>
       </c>
       <c r="BY54" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="BZ54">
         <v>18.8</v>
       </c>
       <c r="CA54" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="CB54">
         <v>91</v>
@@ -17802,25 +17817,25 @@
         <v>131</v>
       </c>
       <c r="E55" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F55" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G55" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="H55" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I55" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="J55">
-        <v>86.90000000000001</v>
+        <v>116.9</v>
       </c>
       <c r="K55">
-        <v>20.3</v>
+        <v>19.8</v>
       </c>
       <c r="L55">
         <v>5</v>
@@ -17847,13 +17862,13 @@
         <v>25</v>
       </c>
       <c r="T55" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U55" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="V55" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="W55">
         <v>0.6667</v>
@@ -17922,7 +17937,7 @@
         <v>5.5</v>
       </c>
       <c r="AS55" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AT55">
         <v>102.7</v>
@@ -17970,7 +17985,7 @@
         <v>1.1079</v>
       </c>
       <c r="BI55" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ55">
         <v>3086</v>
@@ -18018,13 +18033,13 @@
         <v>16.4</v>
       </c>
       <c r="BY55" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ55">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="CA55" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="CB55">
         <v>90</v>
@@ -18053,25 +18068,25 @@
         <v>131</v>
       </c>
       <c r="E56" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F56" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G56" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="H56" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I56" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="J56">
-        <v>86.90000000000001</v>
+        <v>116.9</v>
       </c>
       <c r="K56">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="L56">
         <v>5</v>
@@ -18098,13 +18113,13 @@
         <v>25</v>
       </c>
       <c r="T56" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U56" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="V56" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W56">
         <v>0.6667</v>
@@ -18173,7 +18188,7 @@
         <v>4.5</v>
       </c>
       <c r="AS56" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AT56">
         <v>126.4</v>
@@ -18221,7 +18236,7 @@
         <v>1.1101</v>
       </c>
       <c r="BI56" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ56">
         <v>3020</v>
@@ -18269,13 +18284,13 @@
         <v>15.8</v>
       </c>
       <c r="BY56" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ56">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="CA56" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB56">
         <v>89</v>
@@ -18304,25 +18319,25 @@
         <v>131</v>
       </c>
       <c r="E57" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F57" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G57" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="H57" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I57" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="J57">
-        <v>86.90000000000001</v>
+        <v>116.9</v>
       </c>
       <c r="K57">
-        <v>22.3</v>
+        <v>21.8</v>
       </c>
       <c r="L57">
         <v>5</v>
@@ -18349,13 +18364,13 @@
         <v>25</v>
       </c>
       <c r="T57" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U57" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="V57" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="W57">
         <v>0.6667</v>
@@ -18424,7 +18439,7 @@
         <v>3</v>
       </c>
       <c r="AS57" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AT57">
         <v>250.8</v>
@@ -18472,7 +18487,7 @@
         <v>1.1121</v>
       </c>
       <c r="BI57" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="BJ57">
         <v>2956</v>
@@ -18520,13 +18535,13 @@
         <v>15.8</v>
       </c>
       <c r="BY57" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ57">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="CA57" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB57">
         <v>88</v>
@@ -18555,25 +18570,25 @@
         <v>132</v>
       </c>
       <c r="E58" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F58" t="s">
         <v>118</v>
       </c>
       <c r="G58" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="H58" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="I58" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="J58">
-        <v>565</v>
+        <v>595</v>
       </c>
       <c r="K58">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="L58">
         <v>5</v>
@@ -18600,13 +18615,13 @@
         <v>56.2</v>
       </c>
       <c r="T58" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U58" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="V58" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="W58">
         <v>0.1667</v>
@@ -18633,7 +18648,7 @@
         <v>-1.6</v>
       </c>
       <c r="AE58" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AF58">
         <v>70.7</v>
@@ -18675,7 +18690,7 @@
         <v>8.6</v>
       </c>
       <c r="AS58" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AT58">
         <v>291.4</v>
@@ -18723,7 +18738,7 @@
         <v>1.1875</v>
       </c>
       <c r="BI58" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ58">
         <v>885</v>
@@ -18771,13 +18786,13 @@
         <v>0.2</v>
       </c>
       <c r="BY58" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ58">
         <v>16.7</v>
       </c>
       <c r="CA58" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB58">
         <v>75</v>
@@ -18806,25 +18821,25 @@
         <v>132</v>
       </c>
       <c r="E59" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F59" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G59" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="H59" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="I59" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="J59">
-        <v>565</v>
+        <v>595</v>
       </c>
       <c r="K59">
-        <v>20.8</v>
+        <v>20.3</v>
       </c>
       <c r="L59">
         <v>5</v>
@@ -18851,13 +18866,13 @@
         <v>56.2</v>
       </c>
       <c r="T59" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U59" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="V59" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W59">
         <v>0.1667</v>
@@ -18884,7 +18899,7 @@
         <v>-1.6</v>
       </c>
       <c r="AE59" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AF59">
         <v>68.40000000000001</v>
@@ -18926,7 +18941,7 @@
         <v>9.4</v>
       </c>
       <c r="AS59" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="AT59">
         <v>325.1</v>
@@ -18974,7 +18989,7 @@
         <v>1.1931</v>
       </c>
       <c r="BI59" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ59">
         <v>720</v>
@@ -19022,13 +19037,13 @@
         <v>0.2</v>
       </c>
       <c r="BY59" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ59">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="CA59" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB59">
         <v>73</v>
@@ -19057,25 +19072,25 @@
         <v>132</v>
       </c>
       <c r="E60" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F60" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G60" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="H60" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="I60" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="J60">
-        <v>565</v>
+        <v>595</v>
       </c>
       <c r="K60">
-        <v>21.8</v>
+        <v>21.3</v>
       </c>
       <c r="L60">
         <v>5</v>
@@ -19102,13 +19117,13 @@
         <v>56.2</v>
       </c>
       <c r="T60" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U60" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="V60" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="W60">
         <v>0.1667</v>
@@ -19135,7 +19150,7 @@
         <v>-1.6</v>
       </c>
       <c r="AE60" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AF60">
         <v>65.3</v>
@@ -19177,7 +19192,7 @@
         <v>8.6</v>
       </c>
       <c r="AS60" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AT60">
         <v>332.6</v>
@@ -19225,7 +19240,7 @@
         <v>1.2008</v>
       </c>
       <c r="BI60" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ60">
         <v>497</v>
@@ -19273,13 +19288,13 @@
         <v>0.2</v>
       </c>
       <c r="BY60" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ60">
         <v>11.9</v>
       </c>
       <c r="CA60" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB60">
         <v>69</v>
@@ -19308,25 +19323,25 @@
         <v>132</v>
       </c>
       <c r="E61" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F61" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G61" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="H61" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="I61" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="J61">
-        <v>565</v>
+        <v>595</v>
       </c>
       <c r="K61">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
       <c r="L61">
         <v>5</v>
@@ -19353,13 +19368,13 @@
         <v>56.2</v>
       </c>
       <c r="T61" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="U61" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="V61" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="W61">
         <v>0.1667</v>
@@ -19386,7 +19401,7 @@
         <v>-1.6</v>
       </c>
       <c r="AE61" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AF61">
         <v>63</v>
@@ -19428,7 +19443,7 @@
         <v>6.8</v>
       </c>
       <c r="AS61" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AT61">
         <v>341.2</v>
@@ -19476,7 +19491,7 @@
         <v>1.2065</v>
       </c>
       <c r="BI61" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BJ61">
         <v>335</v>
@@ -19524,13 +19539,13 @@
         <v>0.2</v>
       </c>
       <c r="BY61" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BZ61">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="CA61" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="CB61">
         <v>66</v>
@@ -19646,7 +19661,7 @@
         <v>69.09999999999999</v>
       </c>
       <c r="F2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G2">
         <v>90.59999999999999</v>
@@ -19664,7 +19679,7 @@
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M2">
         <v>89.7</v>
@@ -19676,7 +19691,7 @@
         <v>133</v>
       </c>
       <c r="P2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q2">
         <v>5</v>
@@ -19699,7 +19714,7 @@
         <v>67.90000000000001</v>
       </c>
       <c r="F3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G3">
         <v>86.3</v>
@@ -19717,7 +19732,7 @@
         <v>5</v>
       </c>
       <c r="L3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M3">
         <v>85.09999999999999</v>
@@ -19729,7 +19744,7 @@
         <v>133</v>
       </c>
       <c r="P3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -19752,7 +19767,7 @@
         <v>66.40000000000001</v>
       </c>
       <c r="F4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G4">
         <v>93.2</v>
@@ -19770,7 +19785,7 @@
         <v>7</v>
       </c>
       <c r="L4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M4">
         <v>80.2</v>
@@ -19782,7 +19797,7 @@
         <v>133</v>
       </c>
       <c r="P4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q4">
         <v>5</v>
@@ -19805,7 +19820,7 @@
         <v>66.3</v>
       </c>
       <c r="F5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G5">
         <v>83.40000000000001</v>
@@ -19823,7 +19838,7 @@
         <v>6</v>
       </c>
       <c r="L5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M5">
         <v>83.40000000000001</v>
@@ -19835,7 +19850,7 @@
         <v>133</v>
       </c>
       <c r="P5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q5">
         <v>5</v>
@@ -19855,13 +19870,13 @@
         <v>122</v>
       </c>
       <c r="E6">
-        <v>63.3</v>
+        <v>63.5</v>
       </c>
       <c r="F6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G6">
-        <v>87.59999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H6">
         <v>8</v>
@@ -19876,19 +19891,19 @@
         <v>2</v>
       </c>
       <c r="L6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M6">
-        <v>82.2</v>
+        <v>82.8</v>
       </c>
       <c r="N6">
-        <v>2533</v>
+        <v>2570</v>
       </c>
       <c r="O6" t="s">
         <v>133</v>
       </c>
       <c r="P6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q6">
         <v>5</v>
@@ -19911,7 +19926,7 @@
         <v>59.1</v>
       </c>
       <c r="F7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G7">
         <v>90.2</v>
@@ -19929,7 +19944,7 @@
         <v>3</v>
       </c>
       <c r="L7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M7">
         <v>74.59999999999999</v>
@@ -19941,7 +19956,7 @@
         <v>133</v>
       </c>
       <c r="P7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -19961,13 +19976,13 @@
         <v>121</v>
       </c>
       <c r="E8">
-        <v>58</v>
+        <v>57.8</v>
       </c>
       <c r="F8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G8">
-        <v>93.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H8">
         <v>5</v>
@@ -19976,25 +19991,25 @@
         <v>4</v>
       </c>
       <c r="J8">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M8">
         <v>83.59999999999999</v>
       </c>
       <c r="N8">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="O8" t="s">
         <v>133</v>
       </c>
       <c r="P8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q8">
         <v>5</v>
@@ -20017,10 +20032,10 @@
         <v>57.2</v>
       </c>
       <c r="F9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G9">
-        <v>91.3</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="H9">
         <v>4</v>
@@ -20035,19 +20050,19 @@
         <v>1</v>
       </c>
       <c r="L9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M9">
         <v>83.90000000000001</v>
       </c>
       <c r="N9">
-        <v>1655</v>
+        <v>1658</v>
       </c>
       <c r="O9" t="s">
         <v>133</v>
       </c>
       <c r="P9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q9">
         <v>5</v>
@@ -20070,7 +20085,7 @@
         <v>56.3</v>
       </c>
       <c r="F10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G10">
         <v>90.59999999999999</v>
@@ -20088,19 +20103,19 @@
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M10">
         <v>84.3</v>
       </c>
       <c r="N10">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="O10" t="s">
         <v>133</v>
       </c>
       <c r="P10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -20120,10 +20135,10 @@
         <v>123</v>
       </c>
       <c r="E11">
-        <v>55.3</v>
+        <v>55.1</v>
       </c>
       <c r="F11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G11">
         <v>93.2</v>
@@ -20135,25 +20150,25 @@
         <v>2</v>
       </c>
       <c r="J11">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="K11">
         <v>1</v>
       </c>
       <c r="L11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M11">
-        <v>73.8</v>
+        <v>73.7</v>
       </c>
       <c r="N11">
-        <v>1290</v>
+        <v>1281</v>
       </c>
       <c r="O11" t="s">
         <v>133</v>
       </c>
       <c r="P11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q11">
         <v>4</v>
@@ -20173,13 +20188,13 @@
         <v>119</v>
       </c>
       <c r="E12">
-        <v>54.8</v>
+        <v>54.9</v>
       </c>
       <c r="F12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G12">
-        <v>92.59999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="H12">
         <v>3</v>
@@ -20188,16 +20203,16 @@
         <v>2</v>
       </c>
       <c r="J12">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M12">
-        <v>78</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="N12">
         <v>1268</v>
@@ -20206,7 +20221,7 @@
         <v>133</v>
       </c>
       <c r="P12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q12">
         <v>5</v>
@@ -20229,7 +20244,7 @@
         <v>51.9</v>
       </c>
       <c r="F13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G13">
         <v>87.59999999999999</v>
@@ -20247,7 +20262,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M13">
         <v>68.2</v>
@@ -20259,7 +20274,7 @@
         <v>133</v>
       </c>
       <c r="P13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q13">
         <v>5</v>
@@ -20282,10 +20297,10 @@
         <v>50</v>
       </c>
       <c r="F14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G14">
-        <v>82.3</v>
+        <v>81.7</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -20300,10 +20315,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M14">
-        <v>85.2</v>
+        <v>85.5</v>
       </c>
       <c r="N14">
         <v>1850</v>
@@ -20312,7 +20327,7 @@
         <v>134</v>
       </c>
       <c r="P14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q14">
         <v>5</v>
@@ -20335,7 +20350,7 @@
         <v>50</v>
       </c>
       <c r="F15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G15">
         <v>87.3</v>
@@ -20353,7 +20368,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M15">
         <v>85.5</v>
@@ -20365,7 +20380,7 @@
         <v>134</v>
       </c>
       <c r="P15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -20388,7 +20403,7 @@
         <v>50</v>
       </c>
       <c r="F16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G16">
         <v>84.7</v>
@@ -20406,7 +20421,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M16">
         <v>85.2</v>
@@ -20418,7 +20433,7 @@
         <v>134</v>
       </c>
       <c r="P16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q16">
         <v>5</v>
